--- a/Data/Output/stress_1000_enriched.xlsx
+++ b/Data/Output/stress_1000_enriched.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1001"/>
+  <dimension ref="A1:E1001"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,11 +447,6 @@
           <t>distance</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>distance_road_km</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -500,7 +495,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>12305</v>
+        <v>12306</v>
       </c>
     </row>
     <row r="4">
@@ -1000,7 +995,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6822</v>
+        <v>6821</v>
       </c>
     </row>
     <row r="24">
@@ -1375,7 +1370,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1702</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="39">
@@ -1950,7 +1945,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1656</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="62">
@@ -3750,7 +3745,7 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5127</v>
+        <v>5132</v>
       </c>
     </row>
     <row r="134">
@@ -3950,7 +3945,7 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>9196</v>
+        <v>9195</v>
       </c>
     </row>
     <row r="142">
@@ -4250,7 +4245,7 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1075</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="154">
@@ -4850,7 +4845,7 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>9083</v>
+        <v>9082</v>
       </c>
     </row>
     <row r="178">
@@ -4925,7 +4920,7 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>2922</v>
+        <v>2920</v>
       </c>
     </row>
     <row r="181">
@@ -5250,7 +5245,7 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>679</v>
+        <v>661</v>
       </c>
     </row>
     <row r="194">
@@ -5500,7 +5495,7 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>2300</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="204">
@@ -5550,7 +5545,7 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>9648</v>
+        <v>9652</v>
       </c>
     </row>
     <row r="206">
@@ -6825,7 +6820,7 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>3091</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="257">
@@ -7275,7 +7270,7 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>2107</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="275">
@@ -8050,7 +8045,7 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>10139</v>
+        <v>10141</v>
       </c>
     </row>
     <row r="306">
@@ -8350,7 +8345,7 @@
         </is>
       </c>
       <c r="E317" t="n">
-        <v>3160</v>
+        <v>3151</v>
       </c>
     </row>
     <row r="318">
@@ -9625,7 +9620,7 @@
         </is>
       </c>
       <c r="E368" t="n">
-        <v>943</v>
+        <v>952</v>
       </c>
     </row>
     <row r="369">
@@ -11450,7 +11445,7 @@
         </is>
       </c>
       <c r="E441" t="n">
-        <v>4529</v>
+        <v>4511</v>
       </c>
     </row>
     <row r="442">
@@ -11625,7 +11620,7 @@
         </is>
       </c>
       <c r="E448" t="n">
-        <v>7056</v>
+        <v>7054</v>
       </c>
     </row>
     <row r="449">
@@ -11650,7 +11645,7 @@
         </is>
       </c>
       <c r="E449" t="n">
-        <v>2304</v>
+        <v>2303</v>
       </c>
     </row>
     <row r="450">
@@ -13225,7 +13220,7 @@
         </is>
       </c>
       <c r="E512" t="n">
-        <v>856</v>
+        <v>848</v>
       </c>
     </row>
     <row r="513">
@@ -13275,7 +13270,7 @@
         </is>
       </c>
       <c r="E514" t="n">
-        <v>2413</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="515">
@@ -14975,7 +14970,7 @@
         </is>
       </c>
       <c r="E582" t="n">
-        <v>1429</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="583">
@@ -15100,7 +15095,7 @@
         </is>
       </c>
       <c r="E587" t="n">
-        <v>11299</v>
+        <v>11300</v>
       </c>
     </row>
     <row r="588">
@@ -15200,7 +15195,7 @@
         </is>
       </c>
       <c r="E591" t="n">
-        <v>8944</v>
+        <v>8949</v>
       </c>
     </row>
     <row r="592">
@@ -15925,7 +15920,7 @@
         </is>
       </c>
       <c r="E620" t="n">
-        <v>1298</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="621">
@@ -16325,7 +16320,7 @@
         </is>
       </c>
       <c r="E636" t="n">
-        <v>10546</v>
+        <v>10542</v>
       </c>
     </row>
     <row r="637">
@@ -16825,7 +16820,7 @@
         </is>
       </c>
       <c r="E656" t="n">
-        <v>12271</v>
+        <v>12272</v>
       </c>
     </row>
     <row r="657">
@@ -16875,7 +16870,7 @@
         </is>
       </c>
       <c r="E658" t="n">
-        <v>3880</v>
+        <v>3881</v>
       </c>
     </row>
     <row r="659">
@@ -17575,7 +17570,7 @@
         </is>
       </c>
       <c r="E686" t="n">
-        <v>10447</v>
+        <v>10449</v>
       </c>
     </row>
     <row r="687">
@@ -18075,7 +18070,7 @@
         </is>
       </c>
       <c r="E706" t="n">
-        <v>4736</v>
+        <v>4731</v>
       </c>
     </row>
     <row r="707">
@@ -18400,7 +18395,7 @@
         </is>
       </c>
       <c r="E719" t="n">
-        <v>3057</v>
+        <v>3049</v>
       </c>
     </row>
     <row r="720">
@@ -18425,7 +18420,7 @@
         </is>
       </c>
       <c r="E720" t="n">
-        <v>591</v>
+        <v>601</v>
       </c>
     </row>
     <row r="721">
@@ -22450,7 +22445,7 @@
         </is>
       </c>
       <c r="E881" t="n">
-        <v>2807</v>
+        <v>2806</v>
       </c>
     </row>
     <row r="882">
@@ -22800,7 +22795,7 @@
         </is>
       </c>
       <c r="E895" t="n">
-        <v>4952</v>
+        <v>4935</v>
       </c>
     </row>
     <row r="896">
@@ -23100,7 +23095,7 @@
         </is>
       </c>
       <c r="E907" t="n">
-        <v>3037</v>
+        <v>3027</v>
       </c>
     </row>
     <row r="908">
@@ -24900,7 +24895,7 @@
         </is>
       </c>
       <c r="E979" t="n">
-        <v>2688</v>
+        <v>2687</v>
       </c>
     </row>
     <row r="980">
@@ -25589,7 +25584,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -25605,7 +25600,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12305</v>
+        <v>12306</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -25641,7 +25636,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -25693,7 +25688,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -25745,7 +25740,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -25797,7 +25792,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -25849,7 +25844,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -25901,7 +25896,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -25953,7 +25948,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -26005,7 +26000,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -26057,7 +26052,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -26109,7 +26104,7 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -26161,7 +26156,7 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -26213,7 +26208,7 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -26265,7 +26260,7 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -26317,7 +26312,7 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -26369,7 +26364,7 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -26421,7 +26416,7 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -26473,7 +26468,7 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -26525,7 +26520,7 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -26577,7 +26572,7 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -26629,7 +26624,7 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -26645,7 +26640,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6822</v>
+        <v>6821</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -26681,7 +26676,7 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -26733,7 +26728,7 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -26785,7 +26780,7 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -26837,7 +26832,7 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -26889,7 +26884,7 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -26941,7 +26936,7 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -26993,7 +26988,7 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -27045,7 +27040,7 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -27097,7 +27092,7 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -27149,7 +27144,7 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -27201,7 +27196,7 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -27253,7 +27248,7 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -27305,7 +27300,7 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -27357,7 +27352,7 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -27409,7 +27404,7 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -27425,7 +27420,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -27461,7 +27456,7 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -27513,7 +27508,7 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -27565,7 +27560,7 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -27617,7 +27612,7 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -27669,7 +27664,7 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -27721,7 +27716,7 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -27773,7 +27768,7 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -27825,7 +27820,7 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -27877,7 +27872,7 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -27929,7 +27924,7 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -27981,7 +27976,7 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -28033,7 +28028,7 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -28085,7 +28080,7 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -28137,7 +28132,7 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -28189,7 +28184,7 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -28241,7 +28236,7 @@
         </is>
       </c>
       <c r="K53" t="n">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -28293,7 +28288,7 @@
         </is>
       </c>
       <c r="K54" t="n">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -28345,7 +28340,7 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -28397,7 +28392,7 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -28449,7 +28444,7 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -28501,7 +28496,7 @@
         </is>
       </c>
       <c r="K58" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -28553,7 +28548,7 @@
         </is>
       </c>
       <c r="K59" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -28605,7 +28600,7 @@
         </is>
       </c>
       <c r="K60" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -28621,7 +28616,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1656</v>
+        <v>1670</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -28635,7 +28630,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q1757 ; http://www.wikidata.org/entity/Q32</t>
+          <t>http://www.wikidata.org/entity/Q1757 ; http://www.wikidata.org/entity/Q1842</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -28657,7 +28652,7 @@
         </is>
       </c>
       <c r="K61" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -28709,7 +28704,7 @@
         </is>
       </c>
       <c r="K62" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -28761,7 +28756,7 @@
         </is>
       </c>
       <c r="K63" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -28813,7 +28808,7 @@
         </is>
       </c>
       <c r="K64" t="n">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -28865,7 +28860,7 @@
         </is>
       </c>
       <c r="K65" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -28917,7 +28912,7 @@
         </is>
       </c>
       <c r="K66" t="n">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -28969,7 +28964,7 @@
         </is>
       </c>
       <c r="K67" t="n">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -29021,7 +29016,7 @@
         </is>
       </c>
       <c r="K68" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -29073,7 +29068,7 @@
         </is>
       </c>
       <c r="K69" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -29125,7 +29120,7 @@
         </is>
       </c>
       <c r="K70" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -29177,7 +29172,7 @@
         </is>
       </c>
       <c r="K71" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
@@ -29229,7 +29224,7 @@
         </is>
       </c>
       <c r="K72" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
@@ -29281,7 +29276,7 @@
         </is>
       </c>
       <c r="K73" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -29333,7 +29328,7 @@
         </is>
       </c>
       <c r="K74" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
@@ -29385,7 +29380,7 @@
         </is>
       </c>
       <c r="K75" t="n">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -29437,7 +29432,7 @@
         </is>
       </c>
       <c r="K76" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
@@ -29489,7 +29484,7 @@
         </is>
       </c>
       <c r="K77" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -29541,7 +29536,7 @@
         </is>
       </c>
       <c r="K78" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -29593,7 +29588,7 @@
         </is>
       </c>
       <c r="K79" t="n">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
@@ -29645,7 +29640,7 @@
         </is>
       </c>
       <c r="K80" t="n">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -29697,7 +29692,7 @@
         </is>
       </c>
       <c r="K81" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -29749,7 +29744,7 @@
         </is>
       </c>
       <c r="K82" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -29801,7 +29796,7 @@
         </is>
       </c>
       <c r="K83" t="n">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -29853,7 +29848,7 @@
         </is>
       </c>
       <c r="K84" t="n">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
@@ -29905,7 +29900,7 @@
         </is>
       </c>
       <c r="K85" t="n">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -29957,7 +29952,7 @@
         </is>
       </c>
       <c r="K86" t="n">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
@@ -30009,7 +30004,7 @@
         </is>
       </c>
       <c r="K87" t="n">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -30061,7 +30056,7 @@
         </is>
       </c>
       <c r="K88" t="n">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -30113,7 +30108,7 @@
         </is>
       </c>
       <c r="K89" t="n">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
@@ -30165,7 +30160,7 @@
         </is>
       </c>
       <c r="K90" t="n">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -30217,7 +30212,7 @@
         </is>
       </c>
       <c r="K91" t="n">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="L91" t="n">
         <v>0</v>
@@ -30269,7 +30264,7 @@
         </is>
       </c>
       <c r="K92" t="n">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
@@ -30321,7 +30316,7 @@
         </is>
       </c>
       <c r="K93" t="n">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
@@ -30373,7 +30368,7 @@
         </is>
       </c>
       <c r="K94" t="n">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="L94" t="n">
         <v>0</v>
@@ -30425,7 +30420,7 @@
         </is>
       </c>
       <c r="K95" t="n">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="L95" t="n">
         <v>0</v>
@@ -30477,7 +30472,7 @@
         </is>
       </c>
       <c r="K96" t="n">
-        <v>72</v>
+        <v>39</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
@@ -30529,7 +30524,7 @@
         </is>
       </c>
       <c r="K97" t="n">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
@@ -30581,7 +30576,7 @@
         </is>
       </c>
       <c r="K98" t="n">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
@@ -30633,7 +30628,7 @@
         </is>
       </c>
       <c r="K99" t="n">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
@@ -30685,7 +30680,7 @@
         </is>
       </c>
       <c r="K100" t="n">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>
@@ -30737,7 +30732,7 @@
         </is>
       </c>
       <c r="K101" t="n">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="L101" t="n">
         <v>0</v>
@@ -30789,7 +30784,7 @@
         </is>
       </c>
       <c r="K102" t="n">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="L102" t="n">
         <v>0</v>
@@ -30841,7 +30836,7 @@
         </is>
       </c>
       <c r="K103" t="n">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="L103" t="n">
         <v>0</v>
@@ -30893,7 +30888,7 @@
         </is>
       </c>
       <c r="K104" t="n">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
@@ -30945,7 +30940,7 @@
         </is>
       </c>
       <c r="K105" t="n">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="L105" t="n">
         <v>0</v>
@@ -30997,7 +30992,7 @@
         </is>
       </c>
       <c r="K106" t="n">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
@@ -31049,7 +31044,7 @@
         </is>
       </c>
       <c r="K107" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="L107" t="n">
         <v>0</v>
@@ -31101,7 +31096,7 @@
         </is>
       </c>
       <c r="K108" t="n">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
@@ -31153,7 +31148,7 @@
         </is>
       </c>
       <c r="K109" t="n">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
@@ -31205,7 +31200,7 @@
         </is>
       </c>
       <c r="K110" t="n">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="L110" t="n">
         <v>0</v>
@@ -31257,7 +31252,7 @@
         </is>
       </c>
       <c r="K111" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="L111" t="n">
         <v>0</v>
@@ -31309,7 +31304,7 @@
         </is>
       </c>
       <c r="K112" t="n">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
@@ -31361,7 +31356,7 @@
         </is>
       </c>
       <c r="K113" t="n">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
@@ -31413,7 +31408,7 @@
         </is>
       </c>
       <c r="K114" t="n">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
@@ -31465,7 +31460,7 @@
         </is>
       </c>
       <c r="K115" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="L115" t="n">
         <v>0</v>
@@ -31517,7 +31512,7 @@
         </is>
       </c>
       <c r="K116" t="n">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
@@ -31569,7 +31564,7 @@
         </is>
       </c>
       <c r="K117" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
@@ -31621,7 +31616,7 @@
         </is>
       </c>
       <c r="K118" t="n">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
@@ -31673,7 +31668,7 @@
         </is>
       </c>
       <c r="K119" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
@@ -31725,7 +31720,7 @@
         </is>
       </c>
       <c r="K120" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="L120" t="n">
         <v>0</v>
@@ -31777,7 +31772,7 @@
         </is>
       </c>
       <c r="K121" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="L121" t="n">
         <v>0</v>
@@ -31829,7 +31824,7 @@
         </is>
       </c>
       <c r="K122" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="L122" t="n">
         <v>0</v>
@@ -31881,7 +31876,7 @@
         </is>
       </c>
       <c r="K123" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="L123" t="n">
         <v>0</v>
@@ -31933,7 +31928,7 @@
         </is>
       </c>
       <c r="K124" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
@@ -31985,7 +31980,7 @@
         </is>
       </c>
       <c r="K125" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="L125" t="n">
         <v>0</v>
@@ -32037,7 +32032,7 @@
         </is>
       </c>
       <c r="K126" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="L126" t="n">
         <v>0</v>
@@ -32089,7 +32084,7 @@
         </is>
       </c>
       <c r="K127" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="L127" t="n">
         <v>0</v>
@@ -32141,7 +32136,7 @@
         </is>
       </c>
       <c r="K128" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="L128" t="n">
         <v>0</v>
@@ -32193,7 +32188,7 @@
         </is>
       </c>
       <c r="K129" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="L129" t="n">
         <v>0</v>
@@ -32245,7 +32240,7 @@
         </is>
       </c>
       <c r="K130" t="n">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="L130" t="n">
         <v>0</v>
@@ -32297,7 +32292,7 @@
         </is>
       </c>
       <c r="K131" t="n">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="L131" t="n">
         <v>0</v>
@@ -32349,7 +32344,7 @@
         </is>
       </c>
       <c r="K132" t="n">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="L132" t="n">
         <v>0</v>
@@ -32365,7 +32360,7 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>5127</v>
+        <v>5132</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -32379,7 +32374,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q32 ; http://www.wikidata.org/entity/Q9361</t>
+          <t>http://www.wikidata.org/entity/Q1842 ; http://www.wikidata.org/entity/Q9361</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -32401,7 +32396,7 @@
         </is>
       </c>
       <c r="K133" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="L133" t="n">
         <v>0</v>
@@ -32453,7 +32448,7 @@
         </is>
       </c>
       <c r="K134" t="n">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="L134" t="n">
         <v>0</v>
@@ -32505,7 +32500,7 @@
         </is>
       </c>
       <c r="K135" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="L135" t="n">
         <v>0</v>
@@ -32557,7 +32552,7 @@
         </is>
       </c>
       <c r="K136" t="n">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="L136" t="n">
         <v>0</v>
@@ -32609,7 +32604,7 @@
         </is>
       </c>
       <c r="K137" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="L137" t="n">
         <v>0</v>
@@ -32661,7 +32656,7 @@
         </is>
       </c>
       <c r="K138" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="L138" t="n">
         <v>0</v>
@@ -32713,7 +32708,7 @@
         </is>
       </c>
       <c r="K139" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
@@ -32765,7 +32760,7 @@
         </is>
       </c>
       <c r="K140" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
@@ -32781,7 +32776,7 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>9196</v>
+        <v>9195</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -32817,7 +32812,7 @@
         </is>
       </c>
       <c r="K141" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
@@ -32869,7 +32864,7 @@
         </is>
       </c>
       <c r="K142" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="L142" t="n">
         <v>0</v>
@@ -32921,7 +32916,7 @@
         </is>
       </c>
       <c r="K143" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="L143" t="n">
         <v>0</v>
@@ -32973,7 +32968,7 @@
         </is>
       </c>
       <c r="K144" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="L144" t="n">
         <v>0</v>
@@ -33025,7 +33020,7 @@
         </is>
       </c>
       <c r="K145" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="L145" t="n">
         <v>0</v>
@@ -33077,7 +33072,7 @@
         </is>
       </c>
       <c r="K146" t="n">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="L146" t="n">
         <v>0</v>
@@ -33129,7 +33124,7 @@
         </is>
       </c>
       <c r="K147" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="L147" t="n">
         <v>0</v>
@@ -33181,7 +33176,7 @@
         </is>
       </c>
       <c r="K148" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="L148" t="n">
         <v>0</v>
@@ -33233,7 +33228,7 @@
         </is>
       </c>
       <c r="K149" t="n">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="L149" t="n">
         <v>0</v>
@@ -33285,7 +33280,7 @@
         </is>
       </c>
       <c r="K150" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="L150" t="n">
         <v>0</v>
@@ -33337,7 +33332,7 @@
         </is>
       </c>
       <c r="K151" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="L151" t="n">
         <v>0</v>
@@ -33389,7 +33384,7 @@
         </is>
       </c>
       <c r="K152" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="L152" t="n">
         <v>0</v>
@@ -33405,7 +33400,7 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1075</v>
+        <v>1081</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -33419,7 +33414,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q270 ; http://www.wikidata.org/entity/Q32</t>
+          <t>http://www.wikidata.org/entity/Q270 ; http://www.wikidata.org/entity/Q1842</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -33441,7 +33436,7 @@
         </is>
       </c>
       <c r="K153" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="L153" t="n">
         <v>0</v>
@@ -33493,7 +33488,7 @@
         </is>
       </c>
       <c r="K154" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="L154" t="n">
         <v>0</v>
@@ -33545,7 +33540,7 @@
         </is>
       </c>
       <c r="K155" t="n">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="L155" t="n">
         <v>0</v>
@@ -33597,7 +33592,7 @@
         </is>
       </c>
       <c r="K156" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="L156" t="n">
         <v>0</v>
@@ -33649,7 +33644,7 @@
         </is>
       </c>
       <c r="K157" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="L157" t="n">
         <v>0</v>
@@ -33701,7 +33696,7 @@
         </is>
       </c>
       <c r="K158" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="L158" t="n">
         <v>0</v>
@@ -33753,7 +33748,7 @@
         </is>
       </c>
       <c r="K159" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="L159" t="n">
         <v>0</v>
@@ -33805,7 +33800,7 @@
         </is>
       </c>
       <c r="K160" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="L160" t="n">
         <v>0</v>
@@ -33857,7 +33852,7 @@
         </is>
       </c>
       <c r="K161" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="L161" t="n">
         <v>0</v>
@@ -33909,7 +33904,7 @@
         </is>
       </c>
       <c r="K162" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="L162" t="n">
         <v>0</v>
@@ -33961,7 +33956,7 @@
         </is>
       </c>
       <c r="K163" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="L163" t="n">
         <v>0</v>
@@ -34013,7 +34008,7 @@
         </is>
       </c>
       <c r="K164" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="L164" t="n">
         <v>0</v>
@@ -34065,7 +34060,7 @@
         </is>
       </c>
       <c r="K165" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="L165" t="n">
         <v>0</v>
@@ -34117,7 +34112,7 @@
         </is>
       </c>
       <c r="K166" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="L166" t="n">
         <v>0</v>
@@ -34169,7 +34164,7 @@
         </is>
       </c>
       <c r="K167" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="L167" t="n">
         <v>0</v>
@@ -34221,7 +34216,7 @@
         </is>
       </c>
       <c r="K168" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="L168" t="n">
         <v>0</v>
@@ -34273,7 +34268,7 @@
         </is>
       </c>
       <c r="K169" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="L169" t="n">
         <v>0</v>
@@ -34325,7 +34320,7 @@
         </is>
       </c>
       <c r="K170" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="L170" t="n">
         <v>0</v>
@@ -34377,7 +34372,7 @@
         </is>
       </c>
       <c r="K171" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="L171" t="n">
         <v>0</v>
@@ -34429,7 +34424,7 @@
         </is>
       </c>
       <c r="K172" t="n">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="L172" t="n">
         <v>0</v>
@@ -34481,7 +34476,7 @@
         </is>
       </c>
       <c r="K173" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="L173" t="n">
         <v>0</v>
@@ -34533,7 +34528,7 @@
         </is>
       </c>
       <c r="K174" t="n">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="L174" t="n">
         <v>0</v>
@@ -34585,7 +34580,7 @@
         </is>
       </c>
       <c r="K175" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="L175" t="n">
         <v>0</v>
@@ -34637,7 +34632,7 @@
         </is>
       </c>
       <c r="K176" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="L176" t="n">
         <v>0</v>
@@ -34653,7 +34648,7 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>9083</v>
+        <v>9082</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -34689,7 +34684,7 @@
         </is>
       </c>
       <c r="K177" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="L177" t="n">
         <v>0</v>
@@ -34741,7 +34736,7 @@
         </is>
       </c>
       <c r="K178" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="L178" t="n">
         <v>0</v>
@@ -34793,7 +34788,7 @@
         </is>
       </c>
       <c r="K179" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="L179" t="n">
         <v>0</v>
@@ -34809,7 +34804,7 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>2922</v>
+        <v>2920</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -34845,7 +34840,7 @@
         </is>
       </c>
       <c r="K180" t="n">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="L180" t="n">
         <v>0</v>
@@ -34897,7 +34892,7 @@
         </is>
       </c>
       <c r="K181" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="L181" t="n">
         <v>0</v>
@@ -34949,7 +34944,7 @@
         </is>
       </c>
       <c r="K182" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="L182" t="n">
         <v>0</v>
@@ -35001,7 +34996,7 @@
         </is>
       </c>
       <c r="K183" t="n">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="L183" t="n">
         <v>0</v>
@@ -35053,7 +35048,7 @@
         </is>
       </c>
       <c r="K184" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="L184" t="n">
         <v>0</v>
@@ -35105,7 +35100,7 @@
         </is>
       </c>
       <c r="K185" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="L185" t="n">
         <v>0</v>
@@ -35157,7 +35152,7 @@
         </is>
       </c>
       <c r="K186" t="n">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="L186" t="n">
         <v>0</v>
@@ -35209,7 +35204,7 @@
         </is>
       </c>
       <c r="K187" t="n">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="L187" t="n">
         <v>0</v>
@@ -35261,7 +35256,7 @@
         </is>
       </c>
       <c r="K188" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="L188" t="n">
         <v>0</v>
@@ -35313,7 +35308,7 @@
         </is>
       </c>
       <c r="K189" t="n">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="L189" t="n">
         <v>0</v>
@@ -35365,7 +35360,7 @@
         </is>
       </c>
       <c r="K190" t="n">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="L190" t="n">
         <v>0</v>
@@ -35417,7 +35412,7 @@
         </is>
       </c>
       <c r="K191" t="n">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="L191" t="n">
         <v>0</v>
@@ -35469,7 +35464,7 @@
         </is>
       </c>
       <c r="K192" t="n">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="L192" t="n">
         <v>0</v>
@@ -35485,7 +35480,7 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>679</v>
+        <v>661</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -35499,7 +35494,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q32 ; http://www.wikidata.org/entity/Q235</t>
+          <t>http://www.wikidata.org/entity/Q1842 ; http://www.wikidata.org/entity/Q235</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -35521,7 +35516,7 @@
         </is>
       </c>
       <c r="K193" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="L193" t="n">
         <v>0</v>
@@ -35573,7 +35568,7 @@
         </is>
       </c>
       <c r="K194" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="L194" t="n">
         <v>0</v>
@@ -35625,7 +35620,7 @@
         </is>
       </c>
       <c r="K195" t="n">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="L195" t="n">
         <v>0</v>
@@ -35677,7 +35672,7 @@
         </is>
       </c>
       <c r="K196" t="n">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="L196" t="n">
         <v>0</v>
@@ -35729,7 +35724,7 @@
         </is>
       </c>
       <c r="K197" t="n">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="L197" t="n">
         <v>0</v>
@@ -35781,7 +35776,7 @@
         </is>
       </c>
       <c r="K198" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="L198" t="n">
         <v>0</v>
@@ -35833,7 +35828,7 @@
         </is>
       </c>
       <c r="K199" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="L199" t="n">
         <v>0</v>
@@ -35885,7 +35880,7 @@
         </is>
       </c>
       <c r="K200" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="L200" t="n">
         <v>0</v>
@@ -35937,7 +35932,7 @@
         </is>
       </c>
       <c r="K201" t="n">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="L201" t="n">
         <v>0</v>
@@ -35989,7 +35984,7 @@
         </is>
       </c>
       <c r="K202" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="L202" t="n">
         <v>0</v>
@@ -36005,7 +36000,7 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>2300</v>
+        <v>2314</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -36019,7 +36014,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q1764 ; http://www.wikidata.org/entity/Q32</t>
+          <t>http://www.wikidata.org/entity/Q1764 ; http://www.wikidata.org/entity/Q1842</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -36041,7 +36036,7 @@
         </is>
       </c>
       <c r="K203" t="n">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="L203" t="n">
         <v>0</v>
@@ -36093,7 +36088,7 @@
         </is>
       </c>
       <c r="K204" t="n">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="L204" t="n">
         <v>0</v>
@@ -36109,7 +36104,7 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>9648</v>
+        <v>9652</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -36123,7 +36118,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q32 ; http://www.wikidata.org/entity/Q1850</t>
+          <t>http://www.wikidata.org/entity/Q1842 ; http://www.wikidata.org/entity/Q1850</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -36145,7 +36140,7 @@
         </is>
       </c>
       <c r="K205" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="L205" t="n">
         <v>0</v>
@@ -36197,7 +36192,7 @@
         </is>
       </c>
       <c r="K206" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="L206" t="n">
         <v>0</v>
@@ -36249,7 +36244,7 @@
         </is>
       </c>
       <c r="K207" t="n">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="L207" t="n">
         <v>0</v>
@@ -36301,7 +36296,7 @@
         </is>
       </c>
       <c r="K208" t="n">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="L208" t="n">
         <v>0</v>
@@ -36353,7 +36348,7 @@
         </is>
       </c>
       <c r="K209" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="L209" t="n">
         <v>0</v>
@@ -36405,7 +36400,7 @@
         </is>
       </c>
       <c r="K210" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="L210" t="n">
         <v>0</v>
@@ -36457,7 +36452,7 @@
         </is>
       </c>
       <c r="K211" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="L211" t="n">
         <v>0</v>
@@ -36509,7 +36504,7 @@
         </is>
       </c>
       <c r="K212" t="n">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="L212" t="n">
         <v>0</v>
@@ -36561,7 +36556,7 @@
         </is>
       </c>
       <c r="K213" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="L213" t="n">
         <v>0</v>
@@ -36613,7 +36608,7 @@
         </is>
       </c>
       <c r="K214" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="L214" t="n">
         <v>0</v>
@@ -36665,7 +36660,7 @@
         </is>
       </c>
       <c r="K215" t="n">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="L215" t="n">
         <v>0</v>
@@ -36717,7 +36712,7 @@
         </is>
       </c>
       <c r="K216" t="n">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="L216" t="n">
         <v>0</v>
@@ -36769,7 +36764,7 @@
         </is>
       </c>
       <c r="K217" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="L217" t="n">
         <v>0</v>
@@ -36821,7 +36816,7 @@
         </is>
       </c>
       <c r="K218" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="L218" t="n">
         <v>0</v>
@@ -36873,7 +36868,7 @@
         </is>
       </c>
       <c r="K219" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="L219" t="n">
         <v>0</v>
@@ -36925,7 +36920,7 @@
         </is>
       </c>
       <c r="K220" t="n">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="L220" t="n">
         <v>0</v>
@@ -36977,7 +36972,7 @@
         </is>
       </c>
       <c r="K221" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="L221" t="n">
         <v>0</v>
@@ -37029,7 +37024,7 @@
         </is>
       </c>
       <c r="K222" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="L222" t="n">
         <v>0</v>
@@ -37081,7 +37076,7 @@
         </is>
       </c>
       <c r="K223" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="L223" t="n">
         <v>0</v>
@@ -37133,7 +37128,7 @@
         </is>
       </c>
       <c r="K224" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="L224" t="n">
         <v>0</v>
@@ -37185,7 +37180,7 @@
         </is>
       </c>
       <c r="K225" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="L225" t="n">
         <v>0</v>
@@ -37237,7 +37232,7 @@
         </is>
       </c>
       <c r="K226" t="n">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="L226" t="n">
         <v>0</v>
@@ -37289,7 +37284,7 @@
         </is>
       </c>
       <c r="K227" t="n">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="L227" t="n">
         <v>0</v>
@@ -37341,7 +37336,7 @@
         </is>
       </c>
       <c r="K228" t="n">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="L228" t="n">
         <v>0</v>
@@ -37393,7 +37388,7 @@
         </is>
       </c>
       <c r="K229" t="n">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="L229" t="n">
         <v>0</v>
@@ -37445,7 +37440,7 @@
         </is>
       </c>
       <c r="K230" t="n">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="L230" t="n">
         <v>0</v>
@@ -37497,7 +37492,7 @@
         </is>
       </c>
       <c r="K231" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="L231" t="n">
         <v>0</v>
@@ -37549,7 +37544,7 @@
         </is>
       </c>
       <c r="K232" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="L232" t="n">
         <v>0</v>
@@ -37601,7 +37596,7 @@
         </is>
       </c>
       <c r="K233" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="L233" t="n">
         <v>0</v>
@@ -37653,7 +37648,7 @@
         </is>
       </c>
       <c r="K234" t="n">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="L234" t="n">
         <v>0</v>
@@ -37705,7 +37700,7 @@
         </is>
       </c>
       <c r="K235" t="n">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="L235" t="n">
         <v>0</v>
@@ -37757,7 +37752,7 @@
         </is>
       </c>
       <c r="K236" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="L236" t="n">
         <v>0</v>
@@ -37809,7 +37804,7 @@
         </is>
       </c>
       <c r="K237" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="L237" t="n">
         <v>0</v>
@@ -37861,7 +37856,7 @@
         </is>
       </c>
       <c r="K238" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="L238" t="n">
         <v>0</v>
@@ -37913,7 +37908,7 @@
         </is>
       </c>
       <c r="K239" t="n">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="L239" t="n">
         <v>0</v>
@@ -37965,7 +37960,7 @@
         </is>
       </c>
       <c r="K240" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="L240" t="n">
         <v>0</v>
@@ -38017,7 +38012,7 @@
         </is>
       </c>
       <c r="K241" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="L241" t="n">
         <v>0</v>
@@ -38069,7 +38064,7 @@
         </is>
       </c>
       <c r="K242" t="n">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="L242" t="n">
         <v>0</v>
@@ -38121,7 +38116,7 @@
         </is>
       </c>
       <c r="K243" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="L243" t="n">
         <v>0</v>
@@ -38173,7 +38168,7 @@
         </is>
       </c>
       <c r="K244" t="n">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="L244" t="n">
         <v>0</v>
@@ -38225,7 +38220,7 @@
         </is>
       </c>
       <c r="K245" t="n">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="L245" t="n">
         <v>0</v>
@@ -38277,7 +38272,7 @@
         </is>
       </c>
       <c r="K246" t="n">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="L246" t="n">
         <v>0</v>
@@ -38329,7 +38324,7 @@
         </is>
       </c>
       <c r="K247" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="L247" t="n">
         <v>0</v>
@@ -38381,7 +38376,7 @@
         </is>
       </c>
       <c r="K248" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="L248" t="n">
         <v>0</v>
@@ -38433,7 +38428,7 @@
         </is>
       </c>
       <c r="K249" t="n">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="L249" t="n">
         <v>0</v>
@@ -38485,7 +38480,7 @@
         </is>
       </c>
       <c r="K250" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="L250" t="n">
         <v>0</v>
@@ -38537,7 +38532,7 @@
         </is>
       </c>
       <c r="K251" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="L251" t="n">
         <v>0</v>
@@ -38589,7 +38584,7 @@
         </is>
       </c>
       <c r="K252" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="L252" t="n">
         <v>0</v>
@@ -38641,7 +38636,7 @@
         </is>
       </c>
       <c r="K253" t="n">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="L253" t="n">
         <v>0</v>
@@ -38693,7 +38688,7 @@
         </is>
       </c>
       <c r="K254" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="L254" t="n">
         <v>0</v>
@@ -38745,7 +38740,7 @@
         </is>
       </c>
       <c r="K255" t="n">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="L255" t="n">
         <v>0</v>
@@ -38761,7 +38756,7 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>3091</v>
+        <v>3090</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -38797,7 +38792,7 @@
         </is>
       </c>
       <c r="K256" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="L256" t="n">
         <v>0</v>
@@ -38849,7 +38844,7 @@
         </is>
       </c>
       <c r="K257" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="L257" t="n">
         <v>0</v>
@@ -38901,7 +38896,7 @@
         </is>
       </c>
       <c r="K258" t="n">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="L258" t="n">
         <v>0</v>
@@ -38953,7 +38948,7 @@
         </is>
       </c>
       <c r="K259" t="n">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="L259" t="n">
         <v>0</v>
@@ -39005,7 +39000,7 @@
         </is>
       </c>
       <c r="K260" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="L260" t="n">
         <v>0</v>
@@ -39057,7 +39052,7 @@
         </is>
       </c>
       <c r="K261" t="n">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="L261" t="n">
         <v>0</v>
@@ -39109,7 +39104,7 @@
         </is>
       </c>
       <c r="K262" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="L262" t="n">
         <v>0</v>
@@ -39161,7 +39156,7 @@
         </is>
       </c>
       <c r="K263" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="L263" t="n">
         <v>0</v>
@@ -39213,7 +39208,7 @@
         </is>
       </c>
       <c r="K264" t="n">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="L264" t="n">
         <v>0</v>
@@ -39265,7 +39260,7 @@
         </is>
       </c>
       <c r="K265" t="n">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="L265" t="n">
         <v>0</v>
@@ -39317,7 +39312,7 @@
         </is>
       </c>
       <c r="K266" t="n">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="L266" t="n">
         <v>0</v>
@@ -39369,7 +39364,7 @@
         </is>
       </c>
       <c r="K267" t="n">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="L267" t="n">
         <v>0</v>
@@ -39421,7 +39416,7 @@
         </is>
       </c>
       <c r="K268" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="L268" t="n">
         <v>0</v>
@@ -39473,7 +39468,7 @@
         </is>
       </c>
       <c r="K269" t="n">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="L269" t="n">
         <v>0</v>
@@ -39525,7 +39520,7 @@
         </is>
       </c>
       <c r="K270" t="n">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="L270" t="n">
         <v>0</v>
@@ -39577,7 +39572,7 @@
         </is>
       </c>
       <c r="K271" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="L271" t="n">
         <v>0</v>
@@ -39629,7 +39624,7 @@
         </is>
       </c>
       <c r="K272" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="L272" t="n">
         <v>0</v>
@@ -39681,7 +39676,7 @@
         </is>
       </c>
       <c r="K273" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="L273" t="n">
         <v>0</v>
@@ -39697,7 +39692,7 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>2107</v>
+        <v>2105</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -39733,7 +39728,7 @@
         </is>
       </c>
       <c r="K274" t="n">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="L274" t="n">
         <v>0</v>
@@ -39785,7 +39780,7 @@
         </is>
       </c>
       <c r="K275" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="L275" t="n">
         <v>0</v>
@@ -39837,7 +39832,7 @@
         </is>
       </c>
       <c r="K276" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="L276" t="n">
         <v>0</v>
@@ -39889,7 +39884,7 @@
         </is>
       </c>
       <c r="K277" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="L277" t="n">
         <v>0</v>
@@ -39941,7 +39936,7 @@
         </is>
       </c>
       <c r="K278" t="n">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="L278" t="n">
         <v>0</v>
@@ -39993,7 +39988,7 @@
         </is>
       </c>
       <c r="K279" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="L279" t="n">
         <v>0</v>
@@ -40045,7 +40040,7 @@
         </is>
       </c>
       <c r="K280" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="L280" t="n">
         <v>0</v>
@@ -40097,7 +40092,7 @@
         </is>
       </c>
       <c r="K281" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="L281" t="n">
         <v>0</v>
@@ -40149,7 +40144,7 @@
         </is>
       </c>
       <c r="K282" t="n">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="L282" t="n">
         <v>0</v>
@@ -40201,7 +40196,7 @@
         </is>
       </c>
       <c r="K283" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="L283" t="n">
         <v>0</v>
@@ -40253,7 +40248,7 @@
         </is>
       </c>
       <c r="K284" t="n">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="L284" t="n">
         <v>0</v>
@@ -40305,7 +40300,7 @@
         </is>
       </c>
       <c r="K285" t="n">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="L285" t="n">
         <v>0</v>
@@ -40357,7 +40352,7 @@
         </is>
       </c>
       <c r="K286" t="n">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="L286" t="n">
         <v>0</v>
@@ -40409,7 +40404,7 @@
         </is>
       </c>
       <c r="K287" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="L287" t="n">
         <v>0</v>
@@ -40461,7 +40456,7 @@
         </is>
       </c>
       <c r="K288" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="L288" t="n">
         <v>0</v>
@@ -40513,7 +40508,7 @@
         </is>
       </c>
       <c r="K289" t="n">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="L289" t="n">
         <v>0</v>
@@ -40565,7 +40560,7 @@
         </is>
       </c>
       <c r="K290" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="L290" t="n">
         <v>0</v>
@@ -40617,7 +40612,7 @@
         </is>
       </c>
       <c r="K291" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="L291" t="n">
         <v>0</v>
@@ -40669,7 +40664,7 @@
         </is>
       </c>
       <c r="K292" t="n">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L292" t="n">
         <v>0</v>
@@ -40721,7 +40716,7 @@
         </is>
       </c>
       <c r="K293" t="n">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="L293" t="n">
         <v>0</v>
@@ -40773,7 +40768,7 @@
         </is>
       </c>
       <c r="K294" t="n">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L294" t="n">
         <v>0</v>
@@ -40825,7 +40820,7 @@
         </is>
       </c>
       <c r="K295" t="n">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="L295" t="n">
         <v>0</v>
@@ -40877,7 +40872,7 @@
         </is>
       </c>
       <c r="K296" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="L296" t="n">
         <v>0</v>
@@ -40929,7 +40924,7 @@
         </is>
       </c>
       <c r="K297" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="L297" t="n">
         <v>0</v>
@@ -40981,7 +40976,7 @@
         </is>
       </c>
       <c r="K298" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="L298" t="n">
         <v>0</v>
@@ -41033,7 +41028,7 @@
         </is>
       </c>
       <c r="K299" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="L299" t="n">
         <v>0</v>
@@ -41085,7 +41080,7 @@
         </is>
       </c>
       <c r="K300" t="n">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L300" t="n">
         <v>0</v>
@@ -41137,7 +41132,7 @@
         </is>
       </c>
       <c r="K301" t="n">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="L301" t="n">
         <v>0</v>
@@ -41189,7 +41184,7 @@
         </is>
       </c>
       <c r="K302" t="n">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="L302" t="n">
         <v>0</v>
@@ -41241,7 +41236,7 @@
         </is>
       </c>
       <c r="K303" t="n">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="L303" t="n">
         <v>0</v>
@@ -41293,7 +41288,7 @@
         </is>
       </c>
       <c r="K304" t="n">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="L304" t="n">
         <v>0</v>
@@ -41309,7 +41304,7 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>10139</v>
+        <v>10141</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -41323,7 +41318,7 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q32 ; http://www.wikidata.org/entity/Q1865</t>
+          <t>http://www.wikidata.org/entity/Q1842 ; http://www.wikidata.org/entity/Q1865</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
@@ -41345,7 +41340,7 @@
         </is>
       </c>
       <c r="K305" t="n">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="L305" t="n">
         <v>0</v>
@@ -41397,7 +41392,7 @@
         </is>
       </c>
       <c r="K306" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="L306" t="n">
         <v>0</v>
@@ -41449,7 +41444,7 @@
         </is>
       </c>
       <c r="K307" t="n">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="L307" t="n">
         <v>0</v>
@@ -41501,7 +41496,7 @@
         </is>
       </c>
       <c r="K308" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="L308" t="n">
         <v>0</v>
@@ -41553,7 +41548,7 @@
         </is>
       </c>
       <c r="K309" t="n">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="L309" t="n">
         <v>0</v>
@@ -41605,7 +41600,7 @@
         </is>
       </c>
       <c r="K310" t="n">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="L310" t="n">
         <v>0</v>
@@ -41657,7 +41652,7 @@
         </is>
       </c>
       <c r="K311" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="L311" t="n">
         <v>0</v>
@@ -41709,7 +41704,7 @@
         </is>
       </c>
       <c r="K312" t="n">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="L312" t="n">
         <v>0</v>
@@ -41761,7 +41756,7 @@
         </is>
       </c>
       <c r="K313" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="L313" t="n">
         <v>0</v>
@@ -41813,7 +41808,7 @@
         </is>
       </c>
       <c r="K314" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="L314" t="n">
         <v>0</v>
@@ -41865,7 +41860,7 @@
         </is>
       </c>
       <c r="K315" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="L315" t="n">
         <v>0</v>
@@ -41917,7 +41912,7 @@
         </is>
       </c>
       <c r="K316" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="L316" t="n">
         <v>0</v>
@@ -41933,7 +41928,7 @@
         </is>
       </c>
       <c r="C317" t="n">
-        <v>3160</v>
+        <v>3151</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -41947,7 +41942,7 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q32 ; http://www.wikidata.org/entity/Q3805</t>
+          <t>http://www.wikidata.org/entity/Q1842 ; http://www.wikidata.org/entity/Q3805</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
@@ -41969,7 +41964,7 @@
         </is>
       </c>
       <c r="K317" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="L317" t="n">
         <v>0</v>
@@ -42021,7 +42016,7 @@
         </is>
       </c>
       <c r="K318" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="L318" t="n">
         <v>0</v>
@@ -42073,7 +42068,7 @@
         </is>
       </c>
       <c r="K319" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="L319" t="n">
         <v>0</v>
@@ -42125,7 +42120,7 @@
         </is>
       </c>
       <c r="K320" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="L320" t="n">
         <v>0</v>
@@ -42177,7 +42172,7 @@
         </is>
       </c>
       <c r="K321" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="L321" t="n">
         <v>0</v>
@@ -42229,7 +42224,7 @@
         </is>
       </c>
       <c r="K322" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="L322" t="n">
         <v>0</v>
@@ -42281,7 +42276,7 @@
         </is>
       </c>
       <c r="K323" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="L323" t="n">
         <v>0</v>
@@ -42333,7 +42328,7 @@
         </is>
       </c>
       <c r="K324" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="L324" t="n">
         <v>0</v>
@@ -42385,7 +42380,7 @@
         </is>
       </c>
       <c r="K325" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="L325" t="n">
         <v>0</v>
@@ -42437,7 +42432,7 @@
         </is>
       </c>
       <c r="K326" t="n">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="L326" t="n">
         <v>0</v>
@@ -42489,7 +42484,7 @@
         </is>
       </c>
       <c r="K327" t="n">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="L327" t="n">
         <v>0</v>
@@ -42541,7 +42536,7 @@
         </is>
       </c>
       <c r="K328" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="L328" t="n">
         <v>0</v>
@@ -42593,7 +42588,7 @@
         </is>
       </c>
       <c r="K329" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="L329" t="n">
         <v>0</v>
@@ -42645,7 +42640,7 @@
         </is>
       </c>
       <c r="K330" t="n">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="L330" t="n">
         <v>0</v>
@@ -42697,7 +42692,7 @@
         </is>
       </c>
       <c r="K331" t="n">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="L331" t="n">
         <v>0</v>
@@ -42749,7 +42744,7 @@
         </is>
       </c>
       <c r="K332" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="L332" t="n">
         <v>0</v>
@@ -42801,7 +42796,7 @@
         </is>
       </c>
       <c r="K333" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="L333" t="n">
         <v>0</v>
@@ -42853,7 +42848,7 @@
         </is>
       </c>
       <c r="K334" t="n">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="L334" t="n">
         <v>0</v>
@@ -42905,7 +42900,7 @@
         </is>
       </c>
       <c r="K335" t="n">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="L335" t="n">
         <v>0</v>
@@ -42957,7 +42952,7 @@
         </is>
       </c>
       <c r="K336" t="n">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="L336" t="n">
         <v>0</v>
@@ -43009,7 +43004,7 @@
         </is>
       </c>
       <c r="K337" t="n">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="L337" t="n">
         <v>0</v>
@@ -43061,7 +43056,7 @@
         </is>
       </c>
       <c r="K338" t="n">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="L338" t="n">
         <v>0</v>
@@ -43113,7 +43108,7 @@
         </is>
       </c>
       <c r="K339" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="L339" t="n">
         <v>0</v>
@@ -43165,7 +43160,7 @@
         </is>
       </c>
       <c r="K340" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="L340" t="n">
         <v>0</v>
@@ -43217,7 +43212,7 @@
         </is>
       </c>
       <c r="K341" t="n">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="L341" t="n">
         <v>0</v>
@@ -43269,7 +43264,7 @@
         </is>
       </c>
       <c r="K342" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="L342" t="n">
         <v>0</v>
@@ -43321,7 +43316,7 @@
         </is>
       </c>
       <c r="K343" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="L343" t="n">
         <v>0</v>
@@ -43373,7 +43368,7 @@
         </is>
       </c>
       <c r="K344" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="L344" t="n">
         <v>0</v>
@@ -43425,7 +43420,7 @@
         </is>
       </c>
       <c r="K345" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="L345" t="n">
         <v>0</v>
@@ -43477,7 +43472,7 @@
         </is>
       </c>
       <c r="K346" t="n">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="L346" t="n">
         <v>0</v>
@@ -43529,7 +43524,7 @@
         </is>
       </c>
       <c r="K347" t="n">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="L347" t="n">
         <v>0</v>
@@ -43581,7 +43576,7 @@
         </is>
       </c>
       <c r="K348" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="L348" t="n">
         <v>0</v>
@@ -43633,7 +43628,7 @@
         </is>
       </c>
       <c r="K349" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="L349" t="n">
         <v>0</v>
@@ -43685,7 +43680,7 @@
         </is>
       </c>
       <c r="K350" t="n">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="L350" t="n">
         <v>0</v>
@@ -43737,7 +43732,7 @@
         </is>
       </c>
       <c r="K351" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="L351" t="n">
         <v>0</v>
@@ -43789,7 +43784,7 @@
         </is>
       </c>
       <c r="K352" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="L352" t="n">
         <v>0</v>
@@ -43841,7 +43836,7 @@
         </is>
       </c>
       <c r="K353" t="n">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="L353" t="n">
         <v>0</v>
@@ -43893,7 +43888,7 @@
         </is>
       </c>
       <c r="K354" t="n">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="L354" t="n">
         <v>0</v>
@@ -43945,7 +43940,7 @@
         </is>
       </c>
       <c r="K355" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="L355" t="n">
         <v>0</v>
@@ -43997,7 +43992,7 @@
         </is>
       </c>
       <c r="K356" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="L356" t="n">
         <v>0</v>
@@ -44049,7 +44044,7 @@
         </is>
       </c>
       <c r="K357" t="n">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="L357" t="n">
         <v>0</v>
@@ -44101,7 +44096,7 @@
         </is>
       </c>
       <c r="K358" t="n">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="L358" t="n">
         <v>0</v>
@@ -44153,7 +44148,7 @@
         </is>
       </c>
       <c r="K359" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="L359" t="n">
         <v>0</v>
@@ -44205,7 +44200,7 @@
         </is>
       </c>
       <c r="K360" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="L360" t="n">
         <v>0</v>
@@ -44257,7 +44252,7 @@
         </is>
       </c>
       <c r="K361" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="L361" t="n">
         <v>0</v>
@@ -44309,7 +44304,7 @@
         </is>
       </c>
       <c r="K362" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="L362" t="n">
         <v>0</v>
@@ -44361,7 +44356,7 @@
         </is>
       </c>
       <c r="K363" t="n">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="L363" t="n">
         <v>0</v>
@@ -44413,7 +44408,7 @@
         </is>
       </c>
       <c r="K364" t="n">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="L364" t="n">
         <v>0</v>
@@ -44465,7 +44460,7 @@
         </is>
       </c>
       <c r="K365" t="n">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="L365" t="n">
         <v>0</v>
@@ -44517,7 +44512,7 @@
         </is>
       </c>
       <c r="K366" t="n">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="L366" t="n">
         <v>0</v>
@@ -44569,7 +44564,7 @@
         </is>
       </c>
       <c r="K367" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="L367" t="n">
         <v>0</v>
@@ -44585,7 +44580,7 @@
         </is>
       </c>
       <c r="C368" t="n">
-        <v>943</v>
+        <v>952</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -44599,7 +44594,7 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q1761 ; http://www.wikidata.org/entity/Q32</t>
+          <t>http://www.wikidata.org/entity/Q1761 ; http://www.wikidata.org/entity/Q1842</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
@@ -44621,7 +44616,7 @@
         </is>
       </c>
       <c r="K368" t="n">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="L368" t="n">
         <v>0</v>
@@ -44673,7 +44668,7 @@
         </is>
       </c>
       <c r="K369" t="n">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="L369" t="n">
         <v>0</v>
@@ -44725,7 +44720,7 @@
         </is>
       </c>
       <c r="K370" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="L370" t="n">
         <v>0</v>
@@ -44777,7 +44772,7 @@
         </is>
       </c>
       <c r="K371" t="n">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="L371" t="n">
         <v>0</v>
@@ -44829,7 +44824,7 @@
         </is>
       </c>
       <c r="K372" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="L372" t="n">
         <v>0</v>
@@ -44881,7 +44876,7 @@
         </is>
       </c>
       <c r="K373" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="L373" t="n">
         <v>0</v>
@@ -44933,7 +44928,7 @@
         </is>
       </c>
       <c r="K374" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="L374" t="n">
         <v>0</v>
@@ -44985,7 +44980,7 @@
         </is>
       </c>
       <c r="K375" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="L375" t="n">
         <v>0</v>
@@ -45037,7 +45032,7 @@
         </is>
       </c>
       <c r="K376" t="n">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="L376" t="n">
         <v>0</v>
@@ -45089,7 +45084,7 @@
         </is>
       </c>
       <c r="K377" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="L377" t="n">
         <v>0</v>
@@ -45141,7 +45136,7 @@
         </is>
       </c>
       <c r="K378" t="n">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="L378" t="n">
         <v>0</v>
@@ -45193,7 +45188,7 @@
         </is>
       </c>
       <c r="K379" t="n">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="L379" t="n">
         <v>0</v>
@@ -45245,7 +45240,7 @@
         </is>
       </c>
       <c r="K380" t="n">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="L380" t="n">
         <v>0</v>
@@ -45297,7 +45292,7 @@
         </is>
       </c>
       <c r="K381" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="L381" t="n">
         <v>0</v>
@@ -45349,7 +45344,7 @@
         </is>
       </c>
       <c r="K382" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="L382" t="n">
         <v>0</v>
@@ -45401,7 +45396,7 @@
         </is>
       </c>
       <c r="K383" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="L383" t="n">
         <v>0</v>
@@ -45453,7 +45448,7 @@
         </is>
       </c>
       <c r="K384" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="L384" t="n">
         <v>0</v>
@@ -45505,7 +45500,7 @@
         </is>
       </c>
       <c r="K385" t="n">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="L385" t="n">
         <v>0</v>
@@ -45557,7 +45552,7 @@
         </is>
       </c>
       <c r="K386" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="L386" t="n">
         <v>0</v>
@@ -45609,7 +45604,7 @@
         </is>
       </c>
       <c r="K387" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="L387" t="n">
         <v>0</v>
@@ -45661,7 +45656,7 @@
         </is>
       </c>
       <c r="K388" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="L388" t="n">
         <v>0</v>
@@ -45713,7 +45708,7 @@
         </is>
       </c>
       <c r="K389" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="L389" t="n">
         <v>0</v>
@@ -45765,7 +45760,7 @@
         </is>
       </c>
       <c r="K390" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="L390" t="n">
         <v>0</v>
@@ -45817,7 +45812,7 @@
         </is>
       </c>
       <c r="K391" t="n">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="L391" t="n">
         <v>0</v>
@@ -45869,7 +45864,7 @@
         </is>
       </c>
       <c r="K392" t="n">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="L392" t="n">
         <v>0</v>
@@ -45921,7 +45916,7 @@
         </is>
       </c>
       <c r="K393" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="L393" t="n">
         <v>0</v>
@@ -45973,7 +45968,7 @@
         </is>
       </c>
       <c r="K394" t="n">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="L394" t="n">
         <v>0</v>
@@ -46025,7 +46020,7 @@
         </is>
       </c>
       <c r="K395" t="n">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="L395" t="n">
         <v>0</v>
@@ -46077,7 +46072,7 @@
         </is>
       </c>
       <c r="K396" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="L396" t="n">
         <v>0</v>
@@ -46129,7 +46124,7 @@
         </is>
       </c>
       <c r="K397" t="n">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="L397" t="n">
         <v>0</v>
@@ -46181,7 +46176,7 @@
         </is>
       </c>
       <c r="K398" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="L398" t="n">
         <v>0</v>
@@ -46233,7 +46228,7 @@
         </is>
       </c>
       <c r="K399" t="n">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="L399" t="n">
         <v>0</v>
@@ -46285,7 +46280,7 @@
         </is>
       </c>
       <c r="K400" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="L400" t="n">
         <v>0</v>
@@ -46337,7 +46332,7 @@
         </is>
       </c>
       <c r="K401" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="L401" t="n">
         <v>0</v>
@@ -46389,7 +46384,7 @@
         </is>
       </c>
       <c r="K402" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="L402" t="n">
         <v>0</v>
@@ -46441,7 +46436,7 @@
         </is>
       </c>
       <c r="K403" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="L403" t="n">
         <v>0</v>
@@ -46493,7 +46488,7 @@
         </is>
       </c>
       <c r="K404" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="L404" t="n">
         <v>0</v>
@@ -46545,7 +46540,7 @@
         </is>
       </c>
       <c r="K405" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="L405" t="n">
         <v>0</v>
@@ -46597,7 +46592,7 @@
         </is>
       </c>
       <c r="K406" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="L406" t="n">
         <v>0</v>
@@ -46649,7 +46644,7 @@
         </is>
       </c>
       <c r="K407" t="n">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="L407" t="n">
         <v>0</v>
@@ -46701,7 +46696,7 @@
         </is>
       </c>
       <c r="K408" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="L408" t="n">
         <v>0</v>
@@ -46753,7 +46748,7 @@
         </is>
       </c>
       <c r="K409" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="L409" t="n">
         <v>0</v>
@@ -46805,7 +46800,7 @@
         </is>
       </c>
       <c r="K410" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="L410" t="n">
         <v>0</v>
@@ -46857,7 +46852,7 @@
         </is>
       </c>
       <c r="K411" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="L411" t="n">
         <v>0</v>
@@ -46909,7 +46904,7 @@
         </is>
       </c>
       <c r="K412" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="L412" t="n">
         <v>0</v>
@@ -46961,7 +46956,7 @@
         </is>
       </c>
       <c r="K413" t="n">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="L413" t="n">
         <v>0</v>
@@ -47013,7 +47008,7 @@
         </is>
       </c>
       <c r="K414" t="n">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="L414" t="n">
         <v>0</v>
@@ -47065,7 +47060,7 @@
         </is>
       </c>
       <c r="K415" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="L415" t="n">
         <v>0</v>
@@ -47117,7 +47112,7 @@
         </is>
       </c>
       <c r="K416" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="L416" t="n">
         <v>0</v>
@@ -47169,7 +47164,7 @@
         </is>
       </c>
       <c r="K417" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="L417" t="n">
         <v>0</v>
@@ -47221,7 +47216,7 @@
         </is>
       </c>
       <c r="K418" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="L418" t="n">
         <v>0</v>
@@ -47273,7 +47268,7 @@
         </is>
       </c>
       <c r="K419" t="n">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="L419" t="n">
         <v>0</v>
@@ -47325,7 +47320,7 @@
         </is>
       </c>
       <c r="K420" t="n">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="L420" t="n">
         <v>0</v>
@@ -47377,7 +47372,7 @@
         </is>
       </c>
       <c r="K421" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="L421" t="n">
         <v>0</v>
@@ -47429,7 +47424,7 @@
         </is>
       </c>
       <c r="K422" t="n">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="L422" t="n">
         <v>0</v>
@@ -47481,7 +47476,7 @@
         </is>
       </c>
       <c r="K423" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="L423" t="n">
         <v>0</v>
@@ -47533,7 +47528,7 @@
         </is>
       </c>
       <c r="K424" t="n">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="L424" t="n">
         <v>0</v>
@@ -47585,7 +47580,7 @@
         </is>
       </c>
       <c r="K425" t="n">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="L425" t="n">
         <v>0</v>
@@ -47637,7 +47632,7 @@
         </is>
       </c>
       <c r="K426" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="L426" t="n">
         <v>0</v>
@@ -47689,7 +47684,7 @@
         </is>
       </c>
       <c r="K427" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="L427" t="n">
         <v>0</v>
@@ -47741,7 +47736,7 @@
         </is>
       </c>
       <c r="K428" t="n">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="L428" t="n">
         <v>0</v>
@@ -47793,7 +47788,7 @@
         </is>
       </c>
       <c r="K429" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="L429" t="n">
         <v>0</v>
@@ -47845,7 +47840,7 @@
         </is>
       </c>
       <c r="K430" t="n">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="L430" t="n">
         <v>0</v>
@@ -47897,7 +47892,7 @@
         </is>
       </c>
       <c r="K431" t="n">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="L431" t="n">
         <v>0</v>
@@ -47949,7 +47944,7 @@
         </is>
       </c>
       <c r="K432" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="L432" t="n">
         <v>0</v>
@@ -48001,7 +47996,7 @@
         </is>
       </c>
       <c r="K433" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="L433" t="n">
         <v>0</v>
@@ -48053,7 +48048,7 @@
         </is>
       </c>
       <c r="K434" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="L434" t="n">
         <v>0</v>
@@ -48105,7 +48100,7 @@
         </is>
       </c>
       <c r="K435" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="L435" t="n">
         <v>0</v>
@@ -48157,7 +48152,7 @@
         </is>
       </c>
       <c r="K436" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="L436" t="n">
         <v>0</v>
@@ -48209,7 +48204,7 @@
         </is>
       </c>
       <c r="K437" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="L437" t="n">
         <v>0</v>
@@ -48261,7 +48256,7 @@
         </is>
       </c>
       <c r="K438" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="L438" t="n">
         <v>0</v>
@@ -48313,7 +48308,7 @@
         </is>
       </c>
       <c r="K439" t="n">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="L439" t="n">
         <v>0</v>
@@ -48365,7 +48360,7 @@
         </is>
       </c>
       <c r="K440" t="n">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="L440" t="n">
         <v>0</v>
@@ -48381,7 +48376,7 @@
         </is>
       </c>
       <c r="C441" t="n">
-        <v>4529</v>
+        <v>4511</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -48395,7 +48390,7 @@
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q32 ; http://www.wikidata.org/entity/Q3787</t>
+          <t>http://www.wikidata.org/entity/Q1842 ; http://www.wikidata.org/entity/Q3787</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
@@ -48417,7 +48412,7 @@
         </is>
       </c>
       <c r="K441" t="n">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="L441" t="n">
         <v>0</v>
@@ -48469,7 +48464,7 @@
         </is>
       </c>
       <c r="K442" t="n">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="L442" t="n">
         <v>0</v>
@@ -48521,7 +48516,7 @@
         </is>
       </c>
       <c r="K443" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="L443" t="n">
         <v>0</v>
@@ -48573,7 +48568,7 @@
         </is>
       </c>
       <c r="K444" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="L444" t="n">
         <v>0</v>
@@ -48625,7 +48620,7 @@
         </is>
       </c>
       <c r="K445" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="L445" t="n">
         <v>0</v>
@@ -48677,7 +48672,7 @@
         </is>
       </c>
       <c r="K446" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="L446" t="n">
         <v>0</v>
@@ -48729,7 +48724,7 @@
         </is>
       </c>
       <c r="K447" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="L447" t="n">
         <v>0</v>
@@ -48745,7 +48740,7 @@
         </is>
       </c>
       <c r="C448" t="n">
-        <v>7056</v>
+        <v>7054</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -48781,7 +48776,7 @@
         </is>
       </c>
       <c r="K448" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="L448" t="n">
         <v>0</v>
@@ -48797,7 +48792,7 @@
         </is>
       </c>
       <c r="C449" t="n">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -48833,7 +48828,7 @@
         </is>
       </c>
       <c r="K449" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="L449" t="n">
         <v>0</v>
@@ -48885,7 +48880,7 @@
         </is>
       </c>
       <c r="K450" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="L450" t="n">
         <v>0</v>
@@ -48937,7 +48932,7 @@
         </is>
       </c>
       <c r="K451" t="n">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="L451" t="n">
         <v>0</v>
@@ -48989,7 +48984,7 @@
         </is>
       </c>
       <c r="K452" t="n">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="L452" t="n">
         <v>0</v>
@@ -49041,7 +49036,7 @@
         </is>
       </c>
       <c r="K453" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="L453" t="n">
         <v>0</v>
@@ -49093,7 +49088,7 @@
         </is>
       </c>
       <c r="K454" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="L454" t="n">
         <v>0</v>
@@ -49145,7 +49140,7 @@
         </is>
       </c>
       <c r="K455" t="n">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="L455" t="n">
         <v>0</v>
@@ -49197,7 +49192,7 @@
         </is>
       </c>
       <c r="K456" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="L456" t="n">
         <v>0</v>
@@ -49249,7 +49244,7 @@
         </is>
       </c>
       <c r="K457" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="L457" t="n">
         <v>0</v>
@@ -49301,7 +49296,7 @@
         </is>
       </c>
       <c r="K458" t="n">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="L458" t="n">
         <v>0</v>
@@ -49353,7 +49348,7 @@
         </is>
       </c>
       <c r="K459" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="L459" t="n">
         <v>0</v>
@@ -49405,7 +49400,7 @@
         </is>
       </c>
       <c r="K460" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="L460" t="n">
         <v>0</v>
@@ -49457,7 +49452,7 @@
         </is>
       </c>
       <c r="K461" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="L461" t="n">
         <v>0</v>
@@ -49509,7 +49504,7 @@
         </is>
       </c>
       <c r="K462" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="L462" t="n">
         <v>0</v>
@@ -49561,7 +49556,7 @@
         </is>
       </c>
       <c r="K463" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="L463" t="n">
         <v>0</v>
@@ -49613,7 +49608,7 @@
         </is>
       </c>
       <c r="K464" t="n">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="L464" t="n">
         <v>0</v>
@@ -49665,7 +49660,7 @@
         </is>
       </c>
       <c r="K465" t="n">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="L465" t="n">
         <v>0</v>
@@ -49717,7 +49712,7 @@
         </is>
       </c>
       <c r="K466" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="L466" t="n">
         <v>0</v>
@@ -49769,7 +49764,7 @@
         </is>
       </c>
       <c r="K467" t="n">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="L467" t="n">
         <v>0</v>
@@ -49821,7 +49816,7 @@
         </is>
       </c>
       <c r="K468" t="n">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="L468" t="n">
         <v>0</v>
@@ -49873,7 +49868,7 @@
         </is>
       </c>
       <c r="K469" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="L469" t="n">
         <v>0</v>
@@ -49925,7 +49920,7 @@
         </is>
       </c>
       <c r="K470" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="L470" t="n">
         <v>0</v>
@@ -49977,7 +49972,7 @@
         </is>
       </c>
       <c r="K471" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="L471" t="n">
         <v>0</v>
@@ -50029,7 +50024,7 @@
         </is>
       </c>
       <c r="K472" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="L472" t="n">
         <v>0</v>
@@ -50081,7 +50076,7 @@
         </is>
       </c>
       <c r="K473" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="L473" t="n">
         <v>0</v>
@@ -50133,7 +50128,7 @@
         </is>
       </c>
       <c r="K474" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="L474" t="n">
         <v>0</v>
@@ -50185,7 +50180,7 @@
         </is>
       </c>
       <c r="K475" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="L475" t="n">
         <v>0</v>
@@ -50237,7 +50232,7 @@
         </is>
       </c>
       <c r="K476" t="n">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="L476" t="n">
         <v>0</v>
@@ -50289,7 +50284,7 @@
         </is>
       </c>
       <c r="K477" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="L477" t="n">
         <v>0</v>
@@ -50341,7 +50336,7 @@
         </is>
       </c>
       <c r="K478" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="L478" t="n">
         <v>0</v>
@@ -50393,7 +50388,7 @@
         </is>
       </c>
       <c r="K479" t="n">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="L479" t="n">
         <v>0</v>
@@ -50445,7 +50440,7 @@
         </is>
       </c>
       <c r="K480" t="n">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="L480" t="n">
         <v>0</v>
@@ -50497,7 +50492,7 @@
         </is>
       </c>
       <c r="K481" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="L481" t="n">
         <v>0</v>
@@ -50549,7 +50544,7 @@
         </is>
       </c>
       <c r="K482" t="n">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="L482" t="n">
         <v>0</v>
@@ -50601,7 +50596,7 @@
         </is>
       </c>
       <c r="K483" t="n">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="L483" t="n">
         <v>0</v>
@@ -50653,7 +50648,7 @@
         </is>
       </c>
       <c r="K484" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="L484" t="n">
         <v>0</v>
@@ -50705,7 +50700,7 @@
         </is>
       </c>
       <c r="K485" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="L485" t="n">
         <v>0</v>
@@ -50757,7 +50752,7 @@
         </is>
       </c>
       <c r="K486" t="n">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="L486" t="n">
         <v>0</v>
@@ -50809,7 +50804,7 @@
         </is>
       </c>
       <c r="K487" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="L487" t="n">
         <v>0</v>
@@ -50861,7 +50856,7 @@
         </is>
       </c>
       <c r="K488" t="n">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="L488" t="n">
         <v>0</v>
@@ -50913,7 +50908,7 @@
         </is>
       </c>
       <c r="K489" t="n">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="L489" t="n">
         <v>0</v>
@@ -50965,7 +50960,7 @@
         </is>
       </c>
       <c r="K490" t="n">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="L490" t="n">
         <v>0</v>
@@ -51017,7 +51012,7 @@
         </is>
       </c>
       <c r="K491" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="L491" t="n">
         <v>0</v>
@@ -51069,7 +51064,7 @@
         </is>
       </c>
       <c r="K492" t="n">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="L492" t="n">
         <v>0</v>
@@ -51121,7 +51116,7 @@
         </is>
       </c>
       <c r="K493" t="n">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="L493" t="n">
         <v>0</v>
@@ -51173,7 +51168,7 @@
         </is>
       </c>
       <c r="K494" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="L494" t="n">
         <v>0</v>
@@ -51225,7 +51220,7 @@
         </is>
       </c>
       <c r="K495" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="L495" t="n">
         <v>0</v>
@@ -51277,7 +51272,7 @@
         </is>
       </c>
       <c r="K496" t="n">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="L496" t="n">
         <v>0</v>
@@ -51329,7 +51324,7 @@
         </is>
       </c>
       <c r="K497" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="L497" t="n">
         <v>0</v>
@@ -51381,7 +51376,7 @@
         </is>
       </c>
       <c r="K498" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="L498" t="n">
         <v>0</v>
@@ -51433,7 +51428,7 @@
         </is>
       </c>
       <c r="K499" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="L499" t="n">
         <v>0</v>
@@ -51485,7 +51480,7 @@
         </is>
       </c>
       <c r="K500" t="n">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="L500" t="n">
         <v>0</v>
@@ -51537,7 +51532,7 @@
         </is>
       </c>
       <c r="K501" t="n">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="L501" t="n">
         <v>0</v>
@@ -51589,7 +51584,7 @@
         </is>
       </c>
       <c r="K502" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="L502" t="n">
         <v>0</v>
@@ -51641,7 +51636,7 @@
         </is>
       </c>
       <c r="K503" t="n">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="L503" t="n">
         <v>0</v>
@@ -51693,7 +51688,7 @@
         </is>
       </c>
       <c r="K504" t="n">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="L504" t="n">
         <v>0</v>
@@ -51745,7 +51740,7 @@
         </is>
       </c>
       <c r="K505" t="n">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="L505" t="n">
         <v>0</v>
@@ -51797,7 +51792,7 @@
         </is>
       </c>
       <c r="K506" t="n">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="L506" t="n">
         <v>0</v>
@@ -51849,7 +51844,7 @@
         </is>
       </c>
       <c r="K507" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="L507" t="n">
         <v>0</v>
@@ -51901,7 +51896,7 @@
         </is>
       </c>
       <c r="K508" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="L508" t="n">
         <v>0</v>
@@ -51953,7 +51948,7 @@
         </is>
       </c>
       <c r="K509" t="n">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="L509" t="n">
         <v>0</v>
@@ -52005,7 +52000,7 @@
         </is>
       </c>
       <c r="K510" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="L510" t="n">
         <v>0</v>
@@ -52057,7 +52052,7 @@
         </is>
       </c>
       <c r="K511" t="n">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="L511" t="n">
         <v>0</v>
@@ -52073,7 +52068,7 @@
         </is>
       </c>
       <c r="C512" t="n">
-        <v>856</v>
+        <v>848</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -52087,7 +52082,7 @@
       </c>
       <c r="F512" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q1435 ; http://www.wikidata.org/entity/Q32</t>
+          <t>http://www.wikidata.org/entity/Q1435 ; http://www.wikidata.org/entity/Q1842</t>
         </is>
       </c>
       <c r="G512" t="inlineStr">
@@ -52109,7 +52104,7 @@
         </is>
       </c>
       <c r="K512" t="n">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="L512" t="n">
         <v>0</v>
@@ -52161,7 +52156,7 @@
         </is>
       </c>
       <c r="K513" t="n">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="L513" t="n">
         <v>0</v>
@@ -52177,7 +52172,7 @@
         </is>
       </c>
       <c r="C514" t="n">
-        <v>2413</v>
+        <v>2412</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -52213,7 +52208,7 @@
         </is>
       </c>
       <c r="K514" t="n">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="L514" t="n">
         <v>0</v>
@@ -52265,7 +52260,7 @@
         </is>
       </c>
       <c r="K515" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="L515" t="n">
         <v>0</v>
@@ -52317,7 +52312,7 @@
         </is>
       </c>
       <c r="K516" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="L516" t="n">
         <v>0</v>
@@ -52369,7 +52364,7 @@
         </is>
       </c>
       <c r="K517" t="n">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="L517" t="n">
         <v>0</v>
@@ -52421,7 +52416,7 @@
         </is>
       </c>
       <c r="K518" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="L518" t="n">
         <v>0</v>
@@ -52473,7 +52468,7 @@
         </is>
       </c>
       <c r="K519" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="L519" t="n">
         <v>0</v>
@@ -52525,7 +52520,7 @@
         </is>
       </c>
       <c r="K520" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="L520" t="n">
         <v>0</v>
@@ -52577,7 +52572,7 @@
         </is>
       </c>
       <c r="K521" t="n">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="L521" t="n">
         <v>0</v>
@@ -52629,7 +52624,7 @@
         </is>
       </c>
       <c r="K522" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="L522" t="n">
         <v>0</v>
@@ -52681,7 +52676,7 @@
         </is>
       </c>
       <c r="K523" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="L523" t="n">
         <v>0</v>
@@ -52733,7 +52728,7 @@
         </is>
       </c>
       <c r="K524" t="n">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="L524" t="n">
         <v>0</v>
@@ -52785,7 +52780,7 @@
         </is>
       </c>
       <c r="K525" t="n">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="L525" t="n">
         <v>0</v>
@@ -52837,7 +52832,7 @@
         </is>
       </c>
       <c r="K526" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="L526" t="n">
         <v>0</v>
@@ -52889,7 +52884,7 @@
         </is>
       </c>
       <c r="K527" t="n">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="L527" t="n">
         <v>0</v>
@@ -52941,7 +52936,7 @@
         </is>
       </c>
       <c r="K528" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="L528" t="n">
         <v>0</v>
@@ -52993,7 +52988,7 @@
         </is>
       </c>
       <c r="K529" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="L529" t="n">
         <v>0</v>
@@ -53045,7 +53040,7 @@
         </is>
       </c>
       <c r="K530" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="L530" t="n">
         <v>0</v>
@@ -53097,7 +53092,7 @@
         </is>
       </c>
       <c r="K531" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="L531" t="n">
         <v>0</v>
@@ -53149,7 +53144,7 @@
         </is>
       </c>
       <c r="K532" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="L532" t="n">
         <v>0</v>
@@ -53201,7 +53196,7 @@
         </is>
       </c>
       <c r="K533" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="L533" t="n">
         <v>0</v>
@@ -53253,7 +53248,7 @@
         </is>
       </c>
       <c r="K534" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="L534" t="n">
         <v>0</v>
@@ -53305,7 +53300,7 @@
         </is>
       </c>
       <c r="K535" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="L535" t="n">
         <v>0</v>
@@ -53357,7 +53352,7 @@
         </is>
       </c>
       <c r="K536" t="n">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="L536" t="n">
         <v>0</v>
@@ -53409,7 +53404,7 @@
         </is>
       </c>
       <c r="K537" t="n">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="L537" t="n">
         <v>0</v>
@@ -53461,7 +53456,7 @@
         </is>
       </c>
       <c r="K538" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="L538" t="n">
         <v>0</v>
@@ -53513,7 +53508,7 @@
         </is>
       </c>
       <c r="K539" t="n">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="L539" t="n">
         <v>0</v>
@@ -53565,7 +53560,7 @@
         </is>
       </c>
       <c r="K540" t="n">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="L540" t="n">
         <v>0</v>
@@ -53617,7 +53612,7 @@
         </is>
       </c>
       <c r="K541" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="L541" t="n">
         <v>0</v>
@@ -53669,7 +53664,7 @@
         </is>
       </c>
       <c r="K542" t="n">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="L542" t="n">
         <v>0</v>
@@ -53721,7 +53716,7 @@
         </is>
       </c>
       <c r="K543" t="n">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="L543" t="n">
         <v>0</v>
@@ -53773,7 +53768,7 @@
         </is>
       </c>
       <c r="K544" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="L544" t="n">
         <v>0</v>
@@ -53825,7 +53820,7 @@
         </is>
       </c>
       <c r="K545" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="L545" t="n">
         <v>0</v>
@@ -53877,7 +53872,7 @@
         </is>
       </c>
       <c r="K546" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="L546" t="n">
         <v>0</v>
@@ -53929,7 +53924,7 @@
         </is>
       </c>
       <c r="K547" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="L547" t="n">
         <v>0</v>
@@ -53981,7 +53976,7 @@
         </is>
       </c>
       <c r="K548" t="n">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="L548" t="n">
         <v>0</v>
@@ -54033,7 +54028,7 @@
         </is>
       </c>
       <c r="K549" t="n">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="L549" t="n">
         <v>0</v>
@@ -54085,7 +54080,7 @@
         </is>
       </c>
       <c r="K550" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="L550" t="n">
         <v>0</v>
@@ -54137,7 +54132,7 @@
         </is>
       </c>
       <c r="K551" t="n">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="L551" t="n">
         <v>0</v>
@@ -54189,7 +54184,7 @@
         </is>
       </c>
       <c r="K552" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="L552" t="n">
         <v>0</v>
@@ -54241,7 +54236,7 @@
         </is>
       </c>
       <c r="K553" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="L553" t="n">
         <v>0</v>
@@ -54293,7 +54288,7 @@
         </is>
       </c>
       <c r="K554" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="L554" t="n">
         <v>0</v>
@@ -54345,7 +54340,7 @@
         </is>
       </c>
       <c r="K555" t="n">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="L555" t="n">
         <v>0</v>
@@ -54397,7 +54392,7 @@
         </is>
       </c>
       <c r="K556" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="L556" t="n">
         <v>0</v>
@@ -54449,7 +54444,7 @@
         </is>
       </c>
       <c r="K557" t="n">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="L557" t="n">
         <v>0</v>
@@ -54501,7 +54496,7 @@
         </is>
       </c>
       <c r="K558" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="L558" t="n">
         <v>0</v>
@@ -54553,7 +54548,7 @@
         </is>
       </c>
       <c r="K559" t="n">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="L559" t="n">
         <v>0</v>
@@ -54605,7 +54600,7 @@
         </is>
       </c>
       <c r="K560" t="n">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="L560" t="n">
         <v>0</v>
@@ -54657,7 +54652,7 @@
         </is>
       </c>
       <c r="K561" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="L561" t="n">
         <v>0</v>
@@ -54709,7 +54704,7 @@
         </is>
       </c>
       <c r="K562" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="L562" t="n">
         <v>0</v>
@@ -54761,7 +54756,7 @@
         </is>
       </c>
       <c r="K563" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="L563" t="n">
         <v>0</v>
@@ -54813,7 +54808,7 @@
         </is>
       </c>
       <c r="K564" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="L564" t="n">
         <v>0</v>
@@ -54865,7 +54860,7 @@
         </is>
       </c>
       <c r="K565" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="L565" t="n">
         <v>0</v>
@@ -54917,7 +54912,7 @@
         </is>
       </c>
       <c r="K566" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="L566" t="n">
         <v>0</v>
@@ -54969,7 +54964,7 @@
         </is>
       </c>
       <c r="K567" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="L567" t="n">
         <v>0</v>
@@ -55021,7 +55016,7 @@
         </is>
       </c>
       <c r="K568" t="n">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="L568" t="n">
         <v>0</v>
@@ -55073,7 +55068,7 @@
         </is>
       </c>
       <c r="K569" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="L569" t="n">
         <v>0</v>
@@ -55125,7 +55120,7 @@
         </is>
       </c>
       <c r="K570" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="L570" t="n">
         <v>0</v>
@@ -55177,7 +55172,7 @@
         </is>
       </c>
       <c r="K571" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="L571" t="n">
         <v>0</v>
@@ -55229,7 +55224,7 @@
         </is>
       </c>
       <c r="K572" t="n">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="L572" t="n">
         <v>0</v>
@@ -55281,7 +55276,7 @@
         </is>
       </c>
       <c r="K573" t="n">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="L573" t="n">
         <v>0</v>
@@ -55333,7 +55328,7 @@
         </is>
       </c>
       <c r="K574" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="L574" t="n">
         <v>0</v>
@@ -55385,7 +55380,7 @@
         </is>
       </c>
       <c r="K575" t="n">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="L575" t="n">
         <v>0</v>
@@ -55437,7 +55432,7 @@
         </is>
       </c>
       <c r="K576" t="n">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="L576" t="n">
         <v>0</v>
@@ -55489,7 +55484,7 @@
         </is>
       </c>
       <c r="K577" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="L577" t="n">
         <v>0</v>
@@ -55541,7 +55536,7 @@
         </is>
       </c>
       <c r="K578" t="n">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="L578" t="n">
         <v>0</v>
@@ -55593,7 +55588,7 @@
         </is>
       </c>
       <c r="K579" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="L579" t="n">
         <v>0</v>
@@ -55645,7 +55640,7 @@
         </is>
       </c>
       <c r="K580" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="L580" t="n">
         <v>0</v>
@@ -55697,7 +55692,7 @@
         </is>
       </c>
       <c r="K581" t="n">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="L581" t="n">
         <v>0</v>
@@ -55713,7 +55708,7 @@
         </is>
       </c>
       <c r="C582" t="n">
-        <v>1429</v>
+        <v>1440</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -55727,7 +55722,7 @@
       </c>
       <c r="F582" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q1773 ; http://www.wikidata.org/entity/Q32</t>
+          <t>http://www.wikidata.org/entity/Q1773 ; http://www.wikidata.org/entity/Q1842</t>
         </is>
       </c>
       <c r="G582" t="inlineStr">
@@ -55749,7 +55744,7 @@
         </is>
       </c>
       <c r="K582" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="L582" t="n">
         <v>0</v>
@@ -55801,7 +55796,7 @@
         </is>
       </c>
       <c r="K583" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="L583" t="n">
         <v>0</v>
@@ -55853,7 +55848,7 @@
         </is>
       </c>
       <c r="K584" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="L584" t="n">
         <v>0</v>
@@ -55905,7 +55900,7 @@
         </is>
       </c>
       <c r="K585" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="L585" t="n">
         <v>0</v>
@@ -55957,7 +55952,7 @@
         </is>
       </c>
       <c r="K586" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="L586" t="n">
         <v>0</v>
@@ -55973,7 +55968,7 @@
         </is>
       </c>
       <c r="C587" t="n">
-        <v>11299</v>
+        <v>11300</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -55987,7 +55982,7 @@
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q32 ; http://www.wikidata.org/entity/Q3630</t>
+          <t>http://www.wikidata.org/entity/Q1842 ; http://www.wikidata.org/entity/Q3630</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
@@ -56009,7 +56004,7 @@
         </is>
       </c>
       <c r="K587" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="L587" t="n">
         <v>0</v>
@@ -56061,7 +56056,7 @@
         </is>
       </c>
       <c r="K588" t="n">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="L588" t="n">
         <v>0</v>
@@ -56113,7 +56108,7 @@
         </is>
       </c>
       <c r="K589" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="L589" t="n">
         <v>0</v>
@@ -56165,7 +56160,7 @@
         </is>
       </c>
       <c r="K590" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="L590" t="n">
         <v>0</v>
@@ -56181,7 +56176,7 @@
         </is>
       </c>
       <c r="C591" t="n">
-        <v>8944</v>
+        <v>8949</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -56195,7 +56190,7 @@
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q32 ; http://www.wikidata.org/entity/Q9326</t>
+          <t>http://www.wikidata.org/entity/Q1842 ; http://www.wikidata.org/entity/Q9326</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
@@ -56217,7 +56212,7 @@
         </is>
       </c>
       <c r="K591" t="n">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="L591" t="n">
         <v>0</v>
@@ -56269,7 +56264,7 @@
         </is>
       </c>
       <c r="K592" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="L592" t="n">
         <v>0</v>
@@ -56321,7 +56316,7 @@
         </is>
       </c>
       <c r="K593" t="n">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="L593" t="n">
         <v>0</v>
@@ -56373,7 +56368,7 @@
         </is>
       </c>
       <c r="K594" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="L594" t="n">
         <v>0</v>
@@ -56425,7 +56420,7 @@
         </is>
       </c>
       <c r="K595" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="L595" t="n">
         <v>0</v>
@@ -56477,7 +56472,7 @@
         </is>
       </c>
       <c r="K596" t="n">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="L596" t="n">
         <v>0</v>
@@ -56529,7 +56524,7 @@
         </is>
       </c>
       <c r="K597" t="n">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="L597" t="n">
         <v>0</v>
@@ -56581,7 +56576,7 @@
         </is>
       </c>
       <c r="K598" t="n">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="L598" t="n">
         <v>0</v>
@@ -56633,7 +56628,7 @@
         </is>
       </c>
       <c r="K599" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="L599" t="n">
         <v>0</v>
@@ -56685,7 +56680,7 @@
         </is>
       </c>
       <c r="K600" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="L600" t="n">
         <v>0</v>
@@ -56737,7 +56732,7 @@
         </is>
       </c>
       <c r="K601" t="n">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="L601" t="n">
         <v>0</v>
@@ -56789,7 +56784,7 @@
         </is>
       </c>
       <c r="K602" t="n">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="L602" t="n">
         <v>0</v>
@@ -56841,7 +56836,7 @@
         </is>
       </c>
       <c r="K603" t="n">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="L603" t="n">
         <v>0</v>
@@ -56893,7 +56888,7 @@
         </is>
       </c>
       <c r="K604" t="n">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="L604" t="n">
         <v>0</v>
@@ -56945,7 +56940,7 @@
         </is>
       </c>
       <c r="K605" t="n">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="L605" t="n">
         <v>0</v>
@@ -56997,7 +56992,7 @@
         </is>
       </c>
       <c r="K606" t="n">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="L606" t="n">
         <v>0</v>
@@ -57049,7 +57044,7 @@
         </is>
       </c>
       <c r="K607" t="n">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="L607" t="n">
         <v>0</v>
@@ -57101,7 +57096,7 @@
         </is>
       </c>
       <c r="K608" t="n">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="L608" t="n">
         <v>0</v>
@@ -57153,7 +57148,7 @@
         </is>
       </c>
       <c r="K609" t="n">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="L609" t="n">
         <v>0</v>
@@ -57205,7 +57200,7 @@
         </is>
       </c>
       <c r="K610" t="n">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="L610" t="n">
         <v>0</v>
@@ -57257,7 +57252,7 @@
         </is>
       </c>
       <c r="K611" t="n">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="L611" t="n">
         <v>0</v>
@@ -57309,7 +57304,7 @@
         </is>
       </c>
       <c r="K612" t="n">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="L612" t="n">
         <v>0</v>
@@ -57361,7 +57356,7 @@
         </is>
       </c>
       <c r="K613" t="n">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="L613" t="n">
         <v>0</v>
@@ -57413,7 +57408,7 @@
         </is>
       </c>
       <c r="K614" t="n">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="L614" t="n">
         <v>0</v>
@@ -57465,7 +57460,7 @@
         </is>
       </c>
       <c r="K615" t="n">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="L615" t="n">
         <v>0</v>
@@ -57517,7 +57512,7 @@
         </is>
       </c>
       <c r="K616" t="n">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="L616" t="n">
         <v>0</v>
@@ -57569,7 +57564,7 @@
         </is>
       </c>
       <c r="K617" t="n">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="L617" t="n">
         <v>0</v>
@@ -57621,7 +57616,7 @@
         </is>
       </c>
       <c r="K618" t="n">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="L618" t="n">
         <v>0</v>
@@ -57673,7 +57668,7 @@
         </is>
       </c>
       <c r="K619" t="n">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="L619" t="n">
         <v>0</v>
@@ -57689,7 +57684,7 @@
         </is>
       </c>
       <c r="C620" t="n">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -57725,7 +57720,7 @@
         </is>
       </c>
       <c r="K620" t="n">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="L620" t="n">
         <v>0</v>
@@ -57777,7 +57772,7 @@
         </is>
       </c>
       <c r="K621" t="n">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="L621" t="n">
         <v>0</v>
@@ -57829,7 +57824,7 @@
         </is>
       </c>
       <c r="K622" t="n">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="L622" t="n">
         <v>0</v>
@@ -57881,7 +57876,7 @@
         </is>
       </c>
       <c r="K623" t="n">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="L623" t="n">
         <v>0</v>
@@ -57933,7 +57928,7 @@
         </is>
       </c>
       <c r="K624" t="n">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="L624" t="n">
         <v>0</v>
@@ -57985,7 +57980,7 @@
         </is>
       </c>
       <c r="K625" t="n">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="L625" t="n">
         <v>0</v>
@@ -58037,7 +58032,7 @@
         </is>
       </c>
       <c r="K626" t="n">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="L626" t="n">
         <v>0</v>
@@ -58089,7 +58084,7 @@
         </is>
       </c>
       <c r="K627" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="L627" t="n">
         <v>0</v>
@@ -58141,7 +58136,7 @@
         </is>
       </c>
       <c r="K628" t="n">
-        <v>72</v>
+        <v>39</v>
       </c>
       <c r="L628" t="n">
         <v>0</v>
@@ -58193,7 +58188,7 @@
         </is>
       </c>
       <c r="K629" t="n">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="L629" t="n">
         <v>0</v>
@@ -58245,7 +58240,7 @@
         </is>
       </c>
       <c r="K630" t="n">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="L630" t="n">
         <v>0</v>
@@ -58297,7 +58292,7 @@
         </is>
       </c>
       <c r="K631" t="n">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="L631" t="n">
         <v>0</v>
@@ -58349,7 +58344,7 @@
         </is>
       </c>
       <c r="K632" t="n">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="L632" t="n">
         <v>0</v>
@@ -58401,7 +58396,7 @@
         </is>
       </c>
       <c r="K633" t="n">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="L633" t="n">
         <v>0</v>
@@ -58453,7 +58448,7 @@
         </is>
       </c>
       <c r="K634" t="n">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="L634" t="n">
         <v>0</v>
@@ -58505,7 +58500,7 @@
         </is>
       </c>
       <c r="K635" t="n">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="L635" t="n">
         <v>0</v>
@@ -58521,7 +58516,7 @@
         </is>
       </c>
       <c r="C636" t="n">
-        <v>10546</v>
+        <v>10542</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -58535,7 +58530,7 @@
       </c>
       <c r="F636" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q32 ; http://www.wikidata.org/entity/Q2868</t>
+          <t>http://www.wikidata.org/entity/Q1842 ; http://www.wikidata.org/entity/Q2868</t>
         </is>
       </c>
       <c r="G636" t="inlineStr">
@@ -58557,7 +58552,7 @@
         </is>
       </c>
       <c r="K636" t="n">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="L636" t="n">
         <v>0</v>
@@ -58609,7 +58604,7 @@
         </is>
       </c>
       <c r="K637" t="n">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L637" t="n">
         <v>0</v>
@@ -58661,7 +58656,7 @@
         </is>
       </c>
       <c r="K638" t="n">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="L638" t="n">
         <v>0</v>
@@ -58713,7 +58708,7 @@
         </is>
       </c>
       <c r="K639" t="n">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="L639" t="n">
         <v>0</v>
@@ -58765,7 +58760,7 @@
         </is>
       </c>
       <c r="K640" t="n">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="L640" t="n">
         <v>0</v>
@@ -58817,7 +58812,7 @@
         </is>
       </c>
       <c r="K641" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="L641" t="n">
         <v>0</v>
@@ -58869,7 +58864,7 @@
         </is>
       </c>
       <c r="K642" t="n">
-        <v>106</v>
+        <v>40</v>
       </c>
       <c r="L642" t="n">
         <v>0</v>
@@ -58921,7 +58916,7 @@
         </is>
       </c>
       <c r="K643" t="n">
-        <v>108</v>
+        <v>42</v>
       </c>
       <c r="L643" t="n">
         <v>0</v>
@@ -58973,7 +58968,7 @@
         </is>
       </c>
       <c r="K644" t="n">
-        <v>104</v>
+        <v>41</v>
       </c>
       <c r="L644" t="n">
         <v>0</v>
@@ -59025,7 +59020,7 @@
         </is>
       </c>
       <c r="K645" t="n">
-        <v>107</v>
+        <v>38</v>
       </c>
       <c r="L645" t="n">
         <v>0</v>
@@ -59077,7 +59072,7 @@
         </is>
       </c>
       <c r="K646" t="n">
-        <v>105</v>
+        <v>39</v>
       </c>
       <c r="L646" t="n">
         <v>0</v>
@@ -59129,7 +59124,7 @@
         </is>
       </c>
       <c r="K647" t="n">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="L647" t="n">
         <v>0</v>
@@ -59181,7 +59176,7 @@
         </is>
       </c>
       <c r="K648" t="n">
-        <v>106</v>
+        <v>40</v>
       </c>
       <c r="L648" t="n">
         <v>0</v>
@@ -59233,7 +59228,7 @@
         </is>
       </c>
       <c r="K649" t="n">
-        <v>106</v>
+        <v>39</v>
       </c>
       <c r="L649" t="n">
         <v>0</v>
@@ -59285,7 +59280,7 @@
         </is>
       </c>
       <c r="K650" t="n">
-        <v>106</v>
+        <v>40</v>
       </c>
       <c r="L650" t="n">
         <v>0</v>
@@ -59337,7 +59332,7 @@
         </is>
       </c>
       <c r="K651" t="n">
-        <v>104</v>
+        <v>39</v>
       </c>
       <c r="L651" t="n">
         <v>0</v>
@@ -59389,7 +59384,7 @@
         </is>
       </c>
       <c r="K652" t="n">
-        <v>104</v>
+        <v>40</v>
       </c>
       <c r="L652" t="n">
         <v>0</v>
@@ -59441,7 +59436,7 @@
         </is>
       </c>
       <c r="K653" t="n">
-        <v>106</v>
+        <v>39</v>
       </c>
       <c r="L653" t="n">
         <v>0</v>
@@ -59493,7 +59488,7 @@
         </is>
       </c>
       <c r="K654" t="n">
-        <v>103</v>
+        <v>38</v>
       </c>
       <c r="L654" t="n">
         <v>0</v>
@@ -59545,7 +59540,7 @@
         </is>
       </c>
       <c r="K655" t="n">
-        <v>105</v>
+        <v>38</v>
       </c>
       <c r="L655" t="n">
         <v>0</v>
@@ -59561,7 +59556,7 @@
         </is>
       </c>
       <c r="C656" t="n">
-        <v>12271</v>
+        <v>12272</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -59597,7 +59592,7 @@
         </is>
       </c>
       <c r="K656" t="n">
-        <v>105</v>
+        <v>38</v>
       </c>
       <c r="L656" t="n">
         <v>0</v>
@@ -59649,7 +59644,7 @@
         </is>
       </c>
       <c r="K657" t="n">
-        <v>106</v>
+        <v>39</v>
       </c>
       <c r="L657" t="n">
         <v>0</v>
@@ -59665,7 +59660,7 @@
         </is>
       </c>
       <c r="C658" t="n">
-        <v>3880</v>
+        <v>3881</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -59701,7 +59696,7 @@
         </is>
       </c>
       <c r="K658" t="n">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="L658" t="n">
         <v>0</v>
@@ -59753,7 +59748,7 @@
         </is>
       </c>
       <c r="K659" t="n">
-        <v>75</v>
+        <v>37</v>
       </c>
       <c r="L659" t="n">
         <v>0</v>
@@ -59805,7 +59800,7 @@
         </is>
       </c>
       <c r="K660" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="L660" t="n">
         <v>0</v>
@@ -59857,7 +59852,7 @@
         </is>
       </c>
       <c r="K661" t="n">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="L661" t="n">
         <v>0</v>
@@ -59909,7 +59904,7 @@
         </is>
       </c>
       <c r="K662" t="n">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="L662" t="n">
         <v>0</v>
@@ -59961,7 +59956,7 @@
         </is>
       </c>
       <c r="K663" t="n">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="L663" t="n">
         <v>0</v>
@@ -60013,7 +60008,7 @@
         </is>
       </c>
       <c r="K664" t="n">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="L664" t="n">
         <v>0</v>
@@ -60065,7 +60060,7 @@
         </is>
       </c>
       <c r="K665" t="n">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="L665" t="n">
         <v>0</v>
@@ -60117,7 +60112,7 @@
         </is>
       </c>
       <c r="K666" t="n">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="L666" t="n">
         <v>0</v>
@@ -60169,7 +60164,7 @@
         </is>
       </c>
       <c r="K667" t="n">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="L667" t="n">
         <v>0</v>
@@ -60221,7 +60216,7 @@
         </is>
       </c>
       <c r="K668" t="n">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="L668" t="n">
         <v>0</v>
@@ -60273,7 +60268,7 @@
         </is>
       </c>
       <c r="K669" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="L669" t="n">
         <v>0</v>
@@ -60325,7 +60320,7 @@
         </is>
       </c>
       <c r="K670" t="n">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="L670" t="n">
         <v>0</v>
@@ -60377,7 +60372,7 @@
         </is>
       </c>
       <c r="K671" t="n">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="L671" t="n">
         <v>0</v>
@@ -60429,7 +60424,7 @@
         </is>
       </c>
       <c r="K672" t="n">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="L672" t="n">
         <v>0</v>
@@ -60481,7 +60476,7 @@
         </is>
       </c>
       <c r="K673" t="n">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="L673" t="n">
         <v>0</v>
@@ -60533,7 +60528,7 @@
         </is>
       </c>
       <c r="K674" t="n">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="L674" t="n">
         <v>0</v>
@@ -60585,7 +60580,7 @@
         </is>
       </c>
       <c r="K675" t="n">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="L675" t="n">
         <v>0</v>
@@ -60637,7 +60632,7 @@
         </is>
       </c>
       <c r="K676" t="n">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="L676" t="n">
         <v>0</v>
@@ -60689,7 +60684,7 @@
         </is>
       </c>
       <c r="K677" t="n">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="L677" t="n">
         <v>0</v>
@@ -60741,7 +60736,7 @@
         </is>
       </c>
       <c r="K678" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="L678" t="n">
         <v>0</v>
@@ -60793,7 +60788,7 @@
         </is>
       </c>
       <c r="K679" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="L679" t="n">
         <v>0</v>
@@ -60845,7 +60840,7 @@
         </is>
       </c>
       <c r="K680" t="n">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="L680" t="n">
         <v>0</v>
@@ -60897,7 +60892,7 @@
         </is>
       </c>
       <c r="K681" t="n">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="L681" t="n">
         <v>0</v>
@@ -60949,7 +60944,7 @@
         </is>
       </c>
       <c r="K682" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="L682" t="n">
         <v>0</v>
@@ -61001,7 +60996,7 @@
         </is>
       </c>
       <c r="K683" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="L683" t="n">
         <v>0</v>
@@ -61053,7 +61048,7 @@
         </is>
       </c>
       <c r="K684" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="L684" t="n">
         <v>0</v>
@@ -61105,7 +61100,7 @@
         </is>
       </c>
       <c r="K685" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="L685" t="n">
         <v>0</v>
@@ -61121,7 +61116,7 @@
         </is>
       </c>
       <c r="C686" t="n">
-        <v>10447</v>
+        <v>10449</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -61135,7 +61130,7 @@
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q32 ; http://www.wikidata.org/entity/Q334</t>
+          <t>http://www.wikidata.org/entity/Q1842 ; http://www.wikidata.org/entity/Q334</t>
         </is>
       </c>
       <c r="G686" t="inlineStr">
@@ -61157,7 +61152,7 @@
         </is>
       </c>
       <c r="K686" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="L686" t="n">
         <v>0</v>
@@ -61209,7 +61204,7 @@
         </is>
       </c>
       <c r="K687" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="L687" t="n">
         <v>0</v>
@@ -61261,7 +61256,7 @@
         </is>
       </c>
       <c r="K688" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="L688" t="n">
         <v>0</v>
@@ -61313,7 +61308,7 @@
         </is>
       </c>
       <c r="K689" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="L689" t="n">
         <v>0</v>
@@ -61365,7 +61360,7 @@
         </is>
       </c>
       <c r="K690" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="L690" t="n">
         <v>0</v>
@@ -61417,7 +61412,7 @@
         </is>
       </c>
       <c r="K691" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="L691" t="n">
         <v>0</v>
@@ -61469,7 +61464,7 @@
         </is>
       </c>
       <c r="K692" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L692" t="n">
         <v>0</v>
@@ -61521,7 +61516,7 @@
         </is>
       </c>
       <c r="K693" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="L693" t="n">
         <v>0</v>
@@ -61573,7 +61568,7 @@
         </is>
       </c>
       <c r="K694" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="L694" t="n">
         <v>0</v>
@@ -61625,7 +61620,7 @@
         </is>
       </c>
       <c r="K695" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="L695" t="n">
         <v>0</v>
@@ -61677,7 +61672,7 @@
         </is>
       </c>
       <c r="K696" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="L696" t="n">
         <v>0</v>
@@ -61729,7 +61724,7 @@
         </is>
       </c>
       <c r="K697" t="n">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="L697" t="n">
         <v>0</v>
@@ -61781,7 +61776,7 @@
         </is>
       </c>
       <c r="K698" t="n">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="L698" t="n">
         <v>0</v>
@@ -61833,7 +61828,7 @@
         </is>
       </c>
       <c r="K699" t="n">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="L699" t="n">
         <v>0</v>
@@ -61885,7 +61880,7 @@
         </is>
       </c>
       <c r="K700" t="n">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="L700" t="n">
         <v>0</v>
@@ -61937,7 +61932,7 @@
         </is>
       </c>
       <c r="K701" t="n">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="L701" t="n">
         <v>0</v>
@@ -61989,7 +61984,7 @@
         </is>
       </c>
       <c r="K702" t="n">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="L702" t="n">
         <v>0</v>
@@ -62041,7 +62036,7 @@
         </is>
       </c>
       <c r="K703" t="n">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="L703" t="n">
         <v>0</v>
@@ -62093,7 +62088,7 @@
         </is>
       </c>
       <c r="K704" t="n">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="L704" t="n">
         <v>0</v>
@@ -62145,7 +62140,7 @@
         </is>
       </c>
       <c r="K705" t="n">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="L705" t="n">
         <v>0</v>
@@ -62161,7 +62156,7 @@
         </is>
       </c>
       <c r="C706" t="n">
-        <v>4736</v>
+        <v>4731</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -62175,7 +62170,7 @@
       </c>
       <c r="F706" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q32 ; http://www.wikidata.org/entity/Q3861</t>
+          <t>http://www.wikidata.org/entity/Q1842 ; http://www.wikidata.org/entity/Q3861</t>
         </is>
       </c>
       <c r="G706" t="inlineStr">
@@ -62197,7 +62192,7 @@
         </is>
       </c>
       <c r="K706" t="n">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="L706" t="n">
         <v>0</v>
@@ -62249,7 +62244,7 @@
         </is>
       </c>
       <c r="K707" t="n">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="L707" t="n">
         <v>0</v>
@@ -62301,7 +62296,7 @@
         </is>
       </c>
       <c r="K708" t="n">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="L708" t="n">
         <v>0</v>
@@ -62353,7 +62348,7 @@
         </is>
       </c>
       <c r="K709" t="n">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="L709" t="n">
         <v>0</v>
@@ -62405,7 +62400,7 @@
         </is>
       </c>
       <c r="K710" t="n">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="L710" t="n">
         <v>0</v>
@@ -62457,7 +62452,7 @@
         </is>
       </c>
       <c r="K711" t="n">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="L711" t="n">
         <v>0</v>
@@ -62509,7 +62504,7 @@
         </is>
       </c>
       <c r="K712" t="n">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="L712" t="n">
         <v>0</v>
@@ -62561,7 +62556,7 @@
         </is>
       </c>
       <c r="K713" t="n">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="L713" t="n">
         <v>0</v>
@@ -62613,7 +62608,7 @@
         </is>
       </c>
       <c r="K714" t="n">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="L714" t="n">
         <v>0</v>
@@ -62665,7 +62660,7 @@
         </is>
       </c>
       <c r="K715" t="n">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="L715" t="n">
         <v>0</v>
@@ -62717,7 +62712,7 @@
         </is>
       </c>
       <c r="K716" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="L716" t="n">
         <v>0</v>
@@ -62769,7 +62764,7 @@
         </is>
       </c>
       <c r="K717" t="n">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="L717" t="n">
         <v>0</v>
@@ -62821,7 +62816,7 @@
         </is>
       </c>
       <c r="K718" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="L718" t="n">
         <v>0</v>
@@ -62837,7 +62832,7 @@
         </is>
       </c>
       <c r="C719" t="n">
-        <v>3057</v>
+        <v>3049</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -62851,7 +62846,7 @@
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q32 ; http://www.wikidata.org/entity/Q3766</t>
+          <t>http://www.wikidata.org/entity/Q1842 ; http://www.wikidata.org/entity/Q3766</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
@@ -62873,7 +62868,7 @@
         </is>
       </c>
       <c r="K719" t="n">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="L719" t="n">
         <v>0</v>
@@ -62889,7 +62884,7 @@
         </is>
       </c>
       <c r="C720" t="n">
-        <v>591</v>
+        <v>601</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -62903,7 +62898,7 @@
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q64 ; http://www.wikidata.org/entity/Q32</t>
+          <t>http://www.wikidata.org/entity/Q64 ; http://www.wikidata.org/entity/Q1842</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
@@ -62925,7 +62920,7 @@
         </is>
       </c>
       <c r="K720" t="n">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="L720" t="n">
         <v>0</v>
@@ -62977,7 +62972,7 @@
         </is>
       </c>
       <c r="K721" t="n">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="L721" t="n">
         <v>0</v>
@@ -63029,7 +63024,7 @@
         </is>
       </c>
       <c r="K722" t="n">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="L722" t="n">
         <v>0</v>
@@ -63081,7 +63076,7 @@
         </is>
       </c>
       <c r="K723" t="n">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="L723" t="n">
         <v>0</v>
@@ -63133,7 +63128,7 @@
         </is>
       </c>
       <c r="K724" t="n">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="L724" t="n">
         <v>0</v>
@@ -63185,7 +63180,7 @@
         </is>
       </c>
       <c r="K725" t="n">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="L725" t="n">
         <v>0</v>
@@ -63237,7 +63232,7 @@
         </is>
       </c>
       <c r="K726" t="n">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="L726" t="n">
         <v>0</v>
@@ -63289,7 +63284,7 @@
         </is>
       </c>
       <c r="K727" t="n">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="L727" t="n">
         <v>0</v>
@@ -63341,7 +63336,7 @@
         </is>
       </c>
       <c r="K728" t="n">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="L728" t="n">
         <v>0</v>
@@ -63393,7 +63388,7 @@
         </is>
       </c>
       <c r="K729" t="n">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="L729" t="n">
         <v>0</v>
@@ -63445,7 +63440,7 @@
         </is>
       </c>
       <c r="K730" t="n">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="L730" t="n">
         <v>0</v>
@@ -63497,7 +63492,7 @@
         </is>
       </c>
       <c r="K731" t="n">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="L731" t="n">
         <v>0</v>
@@ -63549,7 +63544,7 @@
         </is>
       </c>
       <c r="K732" t="n">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="L732" t="n">
         <v>0</v>
@@ -63601,7 +63596,7 @@
         </is>
       </c>
       <c r="K733" t="n">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="L733" t="n">
         <v>0</v>
@@ -63653,7 +63648,7 @@
         </is>
       </c>
       <c r="K734" t="n">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="L734" t="n">
         <v>0</v>
@@ -63705,7 +63700,7 @@
         </is>
       </c>
       <c r="K735" t="n">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="L735" t="n">
         <v>0</v>
@@ -63757,7 +63752,7 @@
         </is>
       </c>
       <c r="K736" t="n">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="L736" t="n">
         <v>0</v>
@@ -63809,7 +63804,7 @@
         </is>
       </c>
       <c r="K737" t="n">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="L737" t="n">
         <v>0</v>
@@ -63861,7 +63856,7 @@
         </is>
       </c>
       <c r="K738" t="n">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="L738" t="n">
         <v>0</v>
@@ -63913,7 +63908,7 @@
         </is>
       </c>
       <c r="K739" t="n">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="L739" t="n">
         <v>0</v>
@@ -63965,7 +63960,7 @@
         </is>
       </c>
       <c r="K740" t="n">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="L740" t="n">
         <v>0</v>
@@ -64017,7 +64012,7 @@
         </is>
       </c>
       <c r="K741" t="n">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="L741" t="n">
         <v>0</v>
@@ -64069,7 +64064,7 @@
         </is>
       </c>
       <c r="K742" t="n">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="L742" t="n">
         <v>0</v>
@@ -64121,7 +64116,7 @@
         </is>
       </c>
       <c r="K743" t="n">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="L743" t="n">
         <v>0</v>
@@ -64173,7 +64168,7 @@
         </is>
       </c>
       <c r="K744" t="n">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="L744" t="n">
         <v>0</v>
@@ -64225,7 +64220,7 @@
         </is>
       </c>
       <c r="K745" t="n">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="L745" t="n">
         <v>0</v>
@@ -64277,7 +64272,7 @@
         </is>
       </c>
       <c r="K746" t="n">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="L746" t="n">
         <v>0</v>
@@ -64329,7 +64324,7 @@
         </is>
       </c>
       <c r="K747" t="n">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="L747" t="n">
         <v>0</v>
@@ -64381,7 +64376,7 @@
         </is>
       </c>
       <c r="K748" t="n">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="L748" t="n">
         <v>0</v>
@@ -64433,7 +64428,7 @@
         </is>
       </c>
       <c r="K749" t="n">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="L749" t="n">
         <v>0</v>
@@ -64485,7 +64480,7 @@
         </is>
       </c>
       <c r="K750" t="n">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="L750" t="n">
         <v>0</v>
@@ -64537,7 +64532,7 @@
         </is>
       </c>
       <c r="K751" t="n">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="L751" t="n">
         <v>0</v>
@@ -64589,7 +64584,7 @@
         </is>
       </c>
       <c r="K752" t="n">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="L752" t="n">
         <v>0</v>
@@ -64641,7 +64636,7 @@
         </is>
       </c>
       <c r="K753" t="n">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="L753" t="n">
         <v>0</v>
@@ -64693,7 +64688,7 @@
         </is>
       </c>
       <c r="K754" t="n">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="L754" t="n">
         <v>0</v>
@@ -64745,7 +64740,7 @@
         </is>
       </c>
       <c r="K755" t="n">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="L755" t="n">
         <v>0</v>
@@ -64797,7 +64792,7 @@
         </is>
       </c>
       <c r="K756" t="n">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="L756" t="n">
         <v>0</v>
@@ -64849,7 +64844,7 @@
         </is>
       </c>
       <c r="K757" t="n">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="L757" t="n">
         <v>0</v>
@@ -64901,7 +64896,7 @@
         </is>
       </c>
       <c r="K758" t="n">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="L758" t="n">
         <v>0</v>
@@ -64953,7 +64948,7 @@
         </is>
       </c>
       <c r="K759" t="n">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="L759" t="n">
         <v>0</v>
@@ -65005,7 +65000,7 @@
         </is>
       </c>
       <c r="K760" t="n">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="L760" t="n">
         <v>0</v>
@@ -65057,7 +65052,7 @@
         </is>
       </c>
       <c r="K761" t="n">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="L761" t="n">
         <v>0</v>
@@ -65109,7 +65104,7 @@
         </is>
       </c>
       <c r="K762" t="n">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="L762" t="n">
         <v>0</v>
@@ -65161,7 +65156,7 @@
         </is>
       </c>
       <c r="K763" t="n">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="L763" t="n">
         <v>0</v>
@@ -65213,7 +65208,7 @@
         </is>
       </c>
       <c r="K764" t="n">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="L764" t="n">
         <v>0</v>
@@ -65265,7 +65260,7 @@
         </is>
       </c>
       <c r="K765" t="n">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="L765" t="n">
         <v>0</v>
@@ -65317,7 +65312,7 @@
         </is>
       </c>
       <c r="K766" t="n">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="L766" t="n">
         <v>0</v>
@@ -65369,7 +65364,7 @@
         </is>
       </c>
       <c r="K767" t="n">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="L767" t="n">
         <v>0</v>
@@ -65421,7 +65416,7 @@
         </is>
       </c>
       <c r="K768" t="n">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="L768" t="n">
         <v>0</v>
@@ -65473,7 +65468,7 @@
         </is>
       </c>
       <c r="K769" t="n">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="L769" t="n">
         <v>0</v>
@@ -65525,7 +65520,7 @@
         </is>
       </c>
       <c r="K770" t="n">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="L770" t="n">
         <v>0</v>
@@ -65577,7 +65572,7 @@
         </is>
       </c>
       <c r="K771" t="n">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="L771" t="n">
         <v>0</v>
@@ -65629,7 +65624,7 @@
         </is>
       </c>
       <c r="K772" t="n">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="L772" t="n">
         <v>0</v>
@@ -65681,7 +65676,7 @@
         </is>
       </c>
       <c r="K773" t="n">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="L773" t="n">
         <v>0</v>
@@ -65733,7 +65728,7 @@
         </is>
       </c>
       <c r="K774" t="n">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="L774" t="n">
         <v>0</v>
@@ -65785,7 +65780,7 @@
         </is>
       </c>
       <c r="K775" t="n">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="L775" t="n">
         <v>0</v>
@@ -65837,7 +65832,7 @@
         </is>
       </c>
       <c r="K776" t="n">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="L776" t="n">
         <v>0</v>
@@ -65889,7 +65884,7 @@
         </is>
       </c>
       <c r="K777" t="n">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="L777" t="n">
         <v>0</v>
@@ -65941,7 +65936,7 @@
         </is>
       </c>
       <c r="K778" t="n">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="L778" t="n">
         <v>0</v>
@@ -65993,7 +65988,7 @@
         </is>
       </c>
       <c r="K779" t="n">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="L779" t="n">
         <v>0</v>
@@ -66045,7 +66040,7 @@
         </is>
       </c>
       <c r="K780" t="n">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="L780" t="n">
         <v>0</v>
@@ -66097,7 +66092,7 @@
         </is>
       </c>
       <c r="K781" t="n">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="L781" t="n">
         <v>0</v>
@@ -66149,7 +66144,7 @@
         </is>
       </c>
       <c r="K782" t="n">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="L782" t="n">
         <v>0</v>
@@ -66201,7 +66196,7 @@
         </is>
       </c>
       <c r="K783" t="n">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="L783" t="n">
         <v>0</v>
@@ -66253,7 +66248,7 @@
         </is>
       </c>
       <c r="K784" t="n">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="L784" t="n">
         <v>0</v>
@@ -66305,7 +66300,7 @@
         </is>
       </c>
       <c r="K785" t="n">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="L785" t="n">
         <v>0</v>
@@ -66357,7 +66352,7 @@
         </is>
       </c>
       <c r="K786" t="n">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="L786" t="n">
         <v>0</v>
@@ -66409,7 +66404,7 @@
         </is>
       </c>
       <c r="K787" t="n">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="L787" t="n">
         <v>0</v>
@@ -66461,7 +66456,7 @@
         </is>
       </c>
       <c r="K788" t="n">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="L788" t="n">
         <v>0</v>
@@ -66513,7 +66508,7 @@
         </is>
       </c>
       <c r="K789" t="n">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="L789" t="n">
         <v>0</v>
@@ -66565,7 +66560,7 @@
         </is>
       </c>
       <c r="K790" t="n">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="L790" t="n">
         <v>0</v>
@@ -66617,7 +66612,7 @@
         </is>
       </c>
       <c r="K791" t="n">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="L791" t="n">
         <v>0</v>
@@ -66669,7 +66664,7 @@
         </is>
       </c>
       <c r="K792" t="n">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="L792" t="n">
         <v>0</v>
@@ -66721,7 +66716,7 @@
         </is>
       </c>
       <c r="K793" t="n">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="L793" t="n">
         <v>0</v>
@@ -66773,7 +66768,7 @@
         </is>
       </c>
       <c r="K794" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="L794" t="n">
         <v>0</v>
@@ -66825,7 +66820,7 @@
         </is>
       </c>
       <c r="K795" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="L795" t="n">
         <v>0</v>
@@ -66877,7 +66872,7 @@
         </is>
       </c>
       <c r="K796" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="L796" t="n">
         <v>0</v>
@@ -66929,7 +66924,7 @@
         </is>
       </c>
       <c r="K797" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="L797" t="n">
         <v>0</v>
@@ -66981,7 +66976,7 @@
         </is>
       </c>
       <c r="K798" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="L798" t="n">
         <v>0</v>
@@ -67033,7 +67028,7 @@
         </is>
       </c>
       <c r="K799" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="L799" t="n">
         <v>0</v>
@@ -67085,7 +67080,7 @@
         </is>
       </c>
       <c r="K800" t="n">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="L800" t="n">
         <v>0</v>
@@ -67137,7 +67132,7 @@
         </is>
       </c>
       <c r="K801" t="n">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="L801" t="n">
         <v>0</v>
@@ -67189,7 +67184,7 @@
         </is>
       </c>
       <c r="K802" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="L802" t="n">
         <v>0</v>
@@ -67241,7 +67236,7 @@
         </is>
       </c>
       <c r="K803" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="L803" t="n">
         <v>0</v>
@@ -67293,7 +67288,7 @@
         </is>
       </c>
       <c r="K804" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="L804" t="n">
         <v>0</v>
@@ -67345,7 +67340,7 @@
         </is>
       </c>
       <c r="K805" t="n">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="L805" t="n">
         <v>0</v>
@@ -67397,7 +67392,7 @@
         </is>
       </c>
       <c r="K806" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="L806" t="n">
         <v>0</v>
@@ -67449,7 +67444,7 @@
         </is>
       </c>
       <c r="K807" t="n">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="L807" t="n">
         <v>0</v>
@@ -67501,7 +67496,7 @@
         </is>
       </c>
       <c r="K808" t="n">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="L808" t="n">
         <v>0</v>
@@ -67553,7 +67548,7 @@
         </is>
       </c>
       <c r="K809" t="n">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="L809" t="n">
         <v>0</v>
@@ -67605,7 +67600,7 @@
         </is>
       </c>
       <c r="K810" t="n">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="L810" t="n">
         <v>0</v>
@@ -67657,7 +67652,7 @@
         </is>
       </c>
       <c r="K811" t="n">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="L811" t="n">
         <v>0</v>
@@ -67709,7 +67704,7 @@
         </is>
       </c>
       <c r="K812" t="n">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="L812" t="n">
         <v>0</v>
@@ -67761,7 +67756,7 @@
         </is>
       </c>
       <c r="K813" t="n">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="L813" t="n">
         <v>0</v>
@@ -67813,7 +67808,7 @@
         </is>
       </c>
       <c r="K814" t="n">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="L814" t="n">
         <v>0</v>
@@ -67865,7 +67860,7 @@
         </is>
       </c>
       <c r="K815" t="n">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="L815" t="n">
         <v>0</v>
@@ -67917,7 +67912,7 @@
         </is>
       </c>
       <c r="K816" t="n">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="L816" t="n">
         <v>0</v>
@@ -67969,7 +67964,7 @@
         </is>
       </c>
       <c r="K817" t="n">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="L817" t="n">
         <v>0</v>
@@ -68021,7 +68016,7 @@
         </is>
       </c>
       <c r="K818" t="n">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="L818" t="n">
         <v>0</v>
@@ -68073,7 +68068,7 @@
         </is>
       </c>
       <c r="K819" t="n">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="L819" t="n">
         <v>0</v>
@@ -68125,7 +68120,7 @@
         </is>
       </c>
       <c r="K820" t="n">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="L820" t="n">
         <v>0</v>
@@ -68177,7 +68172,7 @@
         </is>
       </c>
       <c r="K821" t="n">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="L821" t="n">
         <v>0</v>
@@ -68229,7 +68224,7 @@
         </is>
       </c>
       <c r="K822" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="L822" t="n">
         <v>0</v>
@@ -68281,7 +68276,7 @@
         </is>
       </c>
       <c r="K823" t="n">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="L823" t="n">
         <v>0</v>
@@ -68333,7 +68328,7 @@
         </is>
       </c>
       <c r="K824" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="L824" t="n">
         <v>0</v>
@@ -68385,7 +68380,7 @@
         </is>
       </c>
       <c r="K825" t="n">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="L825" t="n">
         <v>0</v>
@@ -68437,7 +68432,7 @@
         </is>
       </c>
       <c r="K826" t="n">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="L826" t="n">
         <v>0</v>
@@ -68489,7 +68484,7 @@
         </is>
       </c>
       <c r="K827" t="n">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="L827" t="n">
         <v>0</v>
@@ -68541,7 +68536,7 @@
         </is>
       </c>
       <c r="K828" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="L828" t="n">
         <v>0</v>
@@ -68593,7 +68588,7 @@
         </is>
       </c>
       <c r="K829" t="n">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="L829" t="n">
         <v>0</v>
@@ -68645,7 +68640,7 @@
         </is>
       </c>
       <c r="K830" t="n">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="L830" t="n">
         <v>0</v>
@@ -68697,7 +68692,7 @@
         </is>
       </c>
       <c r="K831" t="n">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="L831" t="n">
         <v>0</v>
@@ -68749,7 +68744,7 @@
         </is>
       </c>
       <c r="K832" t="n">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="L832" t="n">
         <v>0</v>
@@ -68801,7 +68796,7 @@
         </is>
       </c>
       <c r="K833" t="n">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="L833" t="n">
         <v>0</v>
@@ -68853,7 +68848,7 @@
         </is>
       </c>
       <c r="K834" t="n">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="L834" t="n">
         <v>0</v>
@@ -68905,7 +68900,7 @@
         </is>
       </c>
       <c r="K835" t="n">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="L835" t="n">
         <v>0</v>
@@ -68957,7 +68952,7 @@
         </is>
       </c>
       <c r="K836" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="L836" t="n">
         <v>0</v>
@@ -69009,7 +69004,7 @@
         </is>
       </c>
       <c r="K837" t="n">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="L837" t="n">
         <v>0</v>
@@ -69061,7 +69056,7 @@
         </is>
       </c>
       <c r="K838" t="n">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="L838" t="n">
         <v>0</v>
@@ -69113,7 +69108,7 @@
         </is>
       </c>
       <c r="K839" t="n">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="L839" t="n">
         <v>0</v>
@@ -69165,7 +69160,7 @@
         </is>
       </c>
       <c r="K840" t="n">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="L840" t="n">
         <v>0</v>
@@ -69217,7 +69212,7 @@
         </is>
       </c>
       <c r="K841" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="L841" t="n">
         <v>0</v>
@@ -69269,7 +69264,7 @@
         </is>
       </c>
       <c r="K842" t="n">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="L842" t="n">
         <v>0</v>
@@ -69321,7 +69316,7 @@
         </is>
       </c>
       <c r="K843" t="n">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="L843" t="n">
         <v>0</v>
@@ -69373,7 +69368,7 @@
         </is>
       </c>
       <c r="K844" t="n">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="L844" t="n">
         <v>0</v>
@@ -69425,7 +69420,7 @@
         </is>
       </c>
       <c r="K845" t="n">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="L845" t="n">
         <v>0</v>
@@ -69477,7 +69472,7 @@
         </is>
       </c>
       <c r="K846" t="n">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="L846" t="n">
         <v>0</v>
@@ -69529,7 +69524,7 @@
         </is>
       </c>
       <c r="K847" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="L847" t="n">
         <v>0</v>
@@ -69581,7 +69576,7 @@
         </is>
       </c>
       <c r="K848" t="n">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="L848" t="n">
         <v>0</v>
@@ -69633,7 +69628,7 @@
         </is>
       </c>
       <c r="K849" t="n">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="L849" t="n">
         <v>0</v>
@@ -69685,7 +69680,7 @@
         </is>
       </c>
       <c r="K850" t="n">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="L850" t="n">
         <v>0</v>
@@ -69737,7 +69732,7 @@
         </is>
       </c>
       <c r="K851" t="n">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="L851" t="n">
         <v>0</v>
@@ -69789,7 +69784,7 @@
         </is>
       </c>
       <c r="K852" t="n">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="L852" t="n">
         <v>0</v>
@@ -69841,7 +69836,7 @@
         </is>
       </c>
       <c r="K853" t="n">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="L853" t="n">
         <v>0</v>
@@ -69893,7 +69888,7 @@
         </is>
       </c>
       <c r="K854" t="n">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="L854" t="n">
         <v>0</v>
@@ -69945,7 +69940,7 @@
         </is>
       </c>
       <c r="K855" t="n">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="L855" t="n">
         <v>0</v>
@@ -69997,7 +69992,7 @@
         </is>
       </c>
       <c r="K856" t="n">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="L856" t="n">
         <v>0</v>
@@ -70049,7 +70044,7 @@
         </is>
       </c>
       <c r="K857" t="n">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="L857" t="n">
         <v>0</v>
@@ -70101,7 +70096,7 @@
         </is>
       </c>
       <c r="K858" t="n">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="L858" t="n">
         <v>0</v>
@@ -70153,7 +70148,7 @@
         </is>
       </c>
       <c r="K859" t="n">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="L859" t="n">
         <v>0</v>
@@ -70205,7 +70200,7 @@
         </is>
       </c>
       <c r="K860" t="n">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="L860" t="n">
         <v>0</v>
@@ -70257,7 +70252,7 @@
         </is>
       </c>
       <c r="K861" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="L861" t="n">
         <v>0</v>
@@ -70309,7 +70304,7 @@
         </is>
       </c>
       <c r="K862" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="L862" t="n">
         <v>0</v>
@@ -70361,7 +70356,7 @@
         </is>
       </c>
       <c r="K863" t="n">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="L863" t="n">
         <v>0</v>
@@ -70413,7 +70408,7 @@
         </is>
       </c>
       <c r="K864" t="n">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="L864" t="n">
         <v>0</v>
@@ -70465,7 +70460,7 @@
         </is>
       </c>
       <c r="K865" t="n">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="L865" t="n">
         <v>0</v>
@@ -70517,7 +70512,7 @@
         </is>
       </c>
       <c r="K866" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="L866" t="n">
         <v>0</v>
@@ -70569,7 +70564,7 @@
         </is>
       </c>
       <c r="K867" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="L867" t="n">
         <v>0</v>
@@ -70621,7 +70616,7 @@
         </is>
       </c>
       <c r="K868" t="n">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="L868" t="n">
         <v>0</v>
@@ -70673,7 +70668,7 @@
         </is>
       </c>
       <c r="K869" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="L869" t="n">
         <v>0</v>
@@ -70725,7 +70720,7 @@
         </is>
       </c>
       <c r="K870" t="n">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="L870" t="n">
         <v>0</v>
@@ -70777,7 +70772,7 @@
         </is>
       </c>
       <c r="K871" t="n">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="L871" t="n">
         <v>0</v>
@@ -70829,7 +70824,7 @@
         </is>
       </c>
       <c r="K872" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="L872" t="n">
         <v>0</v>
@@ -70881,7 +70876,7 @@
         </is>
       </c>
       <c r="K873" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="L873" t="n">
         <v>0</v>
@@ -70933,7 +70928,7 @@
         </is>
       </c>
       <c r="K874" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="L874" t="n">
         <v>0</v>
@@ -70985,7 +70980,7 @@
         </is>
       </c>
       <c r="K875" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="L875" t="n">
         <v>0</v>
@@ -71037,7 +71032,7 @@
         </is>
       </c>
       <c r="K876" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="L876" t="n">
         <v>0</v>
@@ -71089,7 +71084,7 @@
         </is>
       </c>
       <c r="K877" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="L877" t="n">
         <v>0</v>
@@ -71141,7 +71136,7 @@
         </is>
       </c>
       <c r="K878" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="L878" t="n">
         <v>0</v>
@@ -71193,7 +71188,7 @@
         </is>
       </c>
       <c r="K879" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="L879" t="n">
         <v>0</v>
@@ -71245,7 +71240,7 @@
         </is>
       </c>
       <c r="K880" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="L880" t="n">
         <v>0</v>
@@ -71261,7 +71256,7 @@
         </is>
       </c>
       <c r="C881" t="n">
-        <v>2807</v>
+        <v>2806</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -71297,7 +71292,7 @@
         </is>
       </c>
       <c r="K881" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="L881" t="n">
         <v>0</v>
@@ -71349,7 +71344,7 @@
         </is>
       </c>
       <c r="K882" t="n">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="L882" t="n">
         <v>0</v>
@@ -71401,7 +71396,7 @@
         </is>
       </c>
       <c r="K883" t="n">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="L883" t="n">
         <v>0</v>
@@ -71453,7 +71448,7 @@
         </is>
       </c>
       <c r="K884" t="n">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="L884" t="n">
         <v>0</v>
@@ -71505,7 +71500,7 @@
         </is>
       </c>
       <c r="K885" t="n">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="L885" t="n">
         <v>0</v>
@@ -71557,7 +71552,7 @@
         </is>
       </c>
       <c r="K886" t="n">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="L886" t="n">
         <v>0</v>
@@ -71609,7 +71604,7 @@
         </is>
       </c>
       <c r="K887" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="L887" t="n">
         <v>0</v>
@@ -71661,7 +71656,7 @@
         </is>
       </c>
       <c r="K888" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="L888" t="n">
         <v>0</v>
@@ -71713,7 +71708,7 @@
         </is>
       </c>
       <c r="K889" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="L889" t="n">
         <v>0</v>
@@ -71765,7 +71760,7 @@
         </is>
       </c>
       <c r="K890" t="n">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="L890" t="n">
         <v>0</v>
@@ -71817,7 +71812,7 @@
         </is>
       </c>
       <c r="K891" t="n">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="L891" t="n">
         <v>0</v>
@@ -71869,7 +71864,7 @@
         </is>
       </c>
       <c r="K892" t="n">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="L892" t="n">
         <v>0</v>
@@ -71921,7 +71916,7 @@
         </is>
       </c>
       <c r="K893" t="n">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="L893" t="n">
         <v>0</v>
@@ -71973,7 +71968,7 @@
         </is>
       </c>
       <c r="K894" t="n">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="L894" t="n">
         <v>0</v>
@@ -71989,7 +71984,7 @@
         </is>
       </c>
       <c r="C895" t="n">
-        <v>4952</v>
+        <v>4935</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -72003,7 +71998,7 @@
       </c>
       <c r="F895" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q32 ; http://www.wikidata.org/entity/Q3761</t>
+          <t>http://www.wikidata.org/entity/Q1842 ; http://www.wikidata.org/entity/Q3761</t>
         </is>
       </c>
       <c r="G895" t="inlineStr">
@@ -72025,7 +72020,7 @@
         </is>
       </c>
       <c r="K895" t="n">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="L895" t="n">
         <v>0</v>
@@ -72077,7 +72072,7 @@
         </is>
       </c>
       <c r="K896" t="n">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="L896" t="n">
         <v>0</v>
@@ -72129,7 +72124,7 @@
         </is>
       </c>
       <c r="K897" t="n">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="L897" t="n">
         <v>0</v>
@@ -72181,7 +72176,7 @@
         </is>
       </c>
       <c r="K898" t="n">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="L898" t="n">
         <v>0</v>
@@ -72233,7 +72228,7 @@
         </is>
       </c>
       <c r="K899" t="n">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="L899" t="n">
         <v>0</v>
@@ -72285,7 +72280,7 @@
         </is>
       </c>
       <c r="K900" t="n">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="L900" t="n">
         <v>0</v>
@@ -72337,7 +72332,7 @@
         </is>
       </c>
       <c r="K901" t="n">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="L901" t="n">
         <v>0</v>
@@ -72389,7 +72384,7 @@
         </is>
       </c>
       <c r="K902" t="n">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="L902" t="n">
         <v>0</v>
@@ -72441,7 +72436,7 @@
         </is>
       </c>
       <c r="K903" t="n">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="L903" t="n">
         <v>0</v>
@@ -72493,7 +72488,7 @@
         </is>
       </c>
       <c r="K904" t="n">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="L904" t="n">
         <v>0</v>
@@ -72545,7 +72540,7 @@
         </is>
       </c>
       <c r="K905" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="L905" t="n">
         <v>0</v>
@@ -72597,7 +72592,7 @@
         </is>
       </c>
       <c r="K906" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="L906" t="n">
         <v>0</v>
@@ -72613,7 +72608,7 @@
         </is>
       </c>
       <c r="C907" t="n">
-        <v>3037</v>
+        <v>3027</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -72627,7 +72622,7 @@
       </c>
       <c r="F907" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q32 ; http://www.wikidata.org/entity/Q85</t>
+          <t>http://www.wikidata.org/entity/Q1842 ; http://www.wikidata.org/entity/Q85</t>
         </is>
       </c>
       <c r="G907" t="inlineStr">
@@ -72649,7 +72644,7 @@
         </is>
       </c>
       <c r="K907" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="L907" t="n">
         <v>0</v>
@@ -72701,7 +72696,7 @@
         </is>
       </c>
       <c r="K908" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="L908" t="n">
         <v>0</v>
@@ -72753,7 +72748,7 @@
         </is>
       </c>
       <c r="K909" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="L909" t="n">
         <v>0</v>
@@ -72805,7 +72800,7 @@
         </is>
       </c>
       <c r="K910" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="L910" t="n">
         <v>0</v>
@@ -72857,7 +72852,7 @@
         </is>
       </c>
       <c r="K911" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="L911" t="n">
         <v>0</v>
@@ -72909,7 +72904,7 @@
         </is>
       </c>
       <c r="K912" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="L912" t="n">
         <v>0</v>
@@ -72961,7 +72956,7 @@
         </is>
       </c>
       <c r="K913" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="L913" t="n">
         <v>0</v>
@@ -73013,7 +73008,7 @@
         </is>
       </c>
       <c r="K914" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="L914" t="n">
         <v>0</v>
@@ -73065,7 +73060,7 @@
         </is>
       </c>
       <c r="K915" t="n">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="L915" t="n">
         <v>0</v>
@@ -73117,7 +73112,7 @@
         </is>
       </c>
       <c r="K916" t="n">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="L916" t="n">
         <v>0</v>
@@ -73169,7 +73164,7 @@
         </is>
       </c>
       <c r="K917" t="n">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="L917" t="n">
         <v>0</v>
@@ -73221,7 +73216,7 @@
         </is>
       </c>
       <c r="K918" t="n">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="L918" t="n">
         <v>0</v>
@@ -73273,7 +73268,7 @@
         </is>
       </c>
       <c r="K919" t="n">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="L919" t="n">
         <v>0</v>
@@ -73325,7 +73320,7 @@
         </is>
       </c>
       <c r="K920" t="n">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="L920" t="n">
         <v>0</v>
@@ -73377,7 +73372,7 @@
         </is>
       </c>
       <c r="K921" t="n">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="L921" t="n">
         <v>0</v>
@@ -73429,7 +73424,7 @@
         </is>
       </c>
       <c r="K922" t="n">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="L922" t="n">
         <v>0</v>
@@ -73481,7 +73476,7 @@
         </is>
       </c>
       <c r="K923" t="n">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="L923" t="n">
         <v>0</v>
@@ -73533,7 +73528,7 @@
         </is>
       </c>
       <c r="K924" t="n">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="L924" t="n">
         <v>0</v>
@@ -73585,7 +73580,7 @@
         </is>
       </c>
       <c r="K925" t="n">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="L925" t="n">
         <v>0</v>
@@ -73637,7 +73632,7 @@
         </is>
       </c>
       <c r="K926" t="n">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="L926" t="n">
         <v>0</v>
@@ -73689,7 +73684,7 @@
         </is>
       </c>
       <c r="K927" t="n">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="L927" t="n">
         <v>0</v>
@@ -73741,7 +73736,7 @@
         </is>
       </c>
       <c r="K928" t="n">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="L928" t="n">
         <v>0</v>
@@ -73793,7 +73788,7 @@
         </is>
       </c>
       <c r="K929" t="n">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="L929" t="n">
         <v>0</v>
@@ -73845,7 +73840,7 @@
         </is>
       </c>
       <c r="K930" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="L930" t="n">
         <v>0</v>
@@ -73897,7 +73892,7 @@
         </is>
       </c>
       <c r="K931" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="L931" t="n">
         <v>0</v>
@@ -73949,7 +73944,7 @@
         </is>
       </c>
       <c r="K932" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="L932" t="n">
         <v>0</v>
@@ -74001,7 +73996,7 @@
         </is>
       </c>
       <c r="K933" t="n">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="L933" t="n">
         <v>0</v>
@@ -74053,7 +74048,7 @@
         </is>
       </c>
       <c r="K934" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="L934" t="n">
         <v>0</v>
@@ -74105,7 +74100,7 @@
         </is>
       </c>
       <c r="K935" t="n">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="L935" t="n">
         <v>0</v>
@@ -74157,7 +74152,7 @@
         </is>
       </c>
       <c r="K936" t="n">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="L936" t="n">
         <v>0</v>
@@ -74209,7 +74204,7 @@
         </is>
       </c>
       <c r="K937" t="n">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="L937" t="n">
         <v>0</v>
@@ -74261,7 +74256,7 @@
         </is>
       </c>
       <c r="K938" t="n">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="L938" t="n">
         <v>0</v>
@@ -74313,7 +74308,7 @@
         </is>
       </c>
       <c r="K939" t="n">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="L939" t="n">
         <v>0</v>
@@ -74365,7 +74360,7 @@
         </is>
       </c>
       <c r="K940" t="n">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="L940" t="n">
         <v>0</v>
@@ -74417,7 +74412,7 @@
         </is>
       </c>
       <c r="K941" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="L941" t="n">
         <v>0</v>
@@ -74469,7 +74464,7 @@
         </is>
       </c>
       <c r="K942" t="n">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="L942" t="n">
         <v>0</v>
@@ -74521,7 +74516,7 @@
         </is>
       </c>
       <c r="K943" t="n">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="L943" t="n">
         <v>0</v>
@@ -74573,7 +74568,7 @@
         </is>
       </c>
       <c r="K944" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="L944" t="n">
         <v>0</v>
@@ -74625,7 +74620,7 @@
         </is>
       </c>
       <c r="K945" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="L945" t="n">
         <v>0</v>
@@ -74677,7 +74672,7 @@
         </is>
       </c>
       <c r="K946" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="L946" t="n">
         <v>0</v>
@@ -74729,7 +74724,7 @@
         </is>
       </c>
       <c r="K947" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="L947" t="n">
         <v>0</v>
@@ -74781,7 +74776,7 @@
         </is>
       </c>
       <c r="K948" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="L948" t="n">
         <v>0</v>
@@ -74833,7 +74828,7 @@
         </is>
       </c>
       <c r="K949" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="L949" t="n">
         <v>0</v>
@@ -74885,7 +74880,7 @@
         </is>
       </c>
       <c r="K950" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="L950" t="n">
         <v>0</v>
@@ -74937,7 +74932,7 @@
         </is>
       </c>
       <c r="K951" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="L951" t="n">
         <v>0</v>
@@ -74989,7 +74984,7 @@
         </is>
       </c>
       <c r="K952" t="n">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="L952" t="n">
         <v>0</v>
@@ -75041,7 +75036,7 @@
         </is>
       </c>
       <c r="K953" t="n">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="L953" t="n">
         <v>0</v>
@@ -75093,7 +75088,7 @@
         </is>
       </c>
       <c r="K954" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="L954" t="n">
         <v>0</v>
@@ -75145,7 +75140,7 @@
         </is>
       </c>
       <c r="K955" t="n">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="L955" t="n">
         <v>0</v>
@@ -75197,7 +75192,7 @@
         </is>
       </c>
       <c r="K956" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="L956" t="n">
         <v>0</v>
@@ -75249,7 +75244,7 @@
         </is>
       </c>
       <c r="K957" t="n">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="L957" t="n">
         <v>0</v>
@@ -75301,7 +75296,7 @@
         </is>
       </c>
       <c r="K958" t="n">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="L958" t="n">
         <v>0</v>
@@ -75353,7 +75348,7 @@
         </is>
       </c>
       <c r="K959" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="L959" t="n">
         <v>0</v>
@@ -75405,7 +75400,7 @@
         </is>
       </c>
       <c r="K960" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="L960" t="n">
         <v>0</v>
@@ -75457,7 +75452,7 @@
         </is>
       </c>
       <c r="K961" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="L961" t="n">
         <v>0</v>
@@ -75509,7 +75504,7 @@
         </is>
       </c>
       <c r="K962" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="L962" t="n">
         <v>0</v>
@@ -75561,7 +75556,7 @@
         </is>
       </c>
       <c r="K963" t="n">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="L963" t="n">
         <v>0</v>
@@ -75613,7 +75608,7 @@
         </is>
       </c>
       <c r="K964" t="n">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="L964" t="n">
         <v>0</v>
@@ -75665,7 +75660,7 @@
         </is>
       </c>
       <c r="K965" t="n">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="L965" t="n">
         <v>0</v>
@@ -75717,7 +75712,7 @@
         </is>
       </c>
       <c r="K966" t="n">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="L966" t="n">
         <v>0</v>
@@ -75769,7 +75764,7 @@
         </is>
       </c>
       <c r="K967" t="n">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="L967" t="n">
         <v>0</v>
@@ -75821,7 +75816,7 @@
         </is>
       </c>
       <c r="K968" t="n">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="L968" t="n">
         <v>0</v>
@@ -75873,7 +75868,7 @@
         </is>
       </c>
       <c r="K969" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="L969" t="n">
         <v>0</v>
@@ -75925,7 +75920,7 @@
         </is>
       </c>
       <c r="K970" t="n">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="L970" t="n">
         <v>0</v>
@@ -75977,7 +75972,7 @@
         </is>
       </c>
       <c r="K971" t="n">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="L971" t="n">
         <v>0</v>
@@ -76029,7 +76024,7 @@
         </is>
       </c>
       <c r="K972" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="L972" t="n">
         <v>0</v>
@@ -76081,7 +76076,7 @@
         </is>
       </c>
       <c r="K973" t="n">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="L973" t="n">
         <v>0</v>
@@ -76133,7 +76128,7 @@
         </is>
       </c>
       <c r="K974" t="n">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="L974" t="n">
         <v>0</v>
@@ -76185,7 +76180,7 @@
         </is>
       </c>
       <c r="K975" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="L975" t="n">
         <v>0</v>
@@ -76237,7 +76232,7 @@
         </is>
       </c>
       <c r="K976" t="n">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="L976" t="n">
         <v>0</v>
@@ -76289,7 +76284,7 @@
         </is>
       </c>
       <c r="K977" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="L977" t="n">
         <v>0</v>
@@ -76341,7 +76336,7 @@
         </is>
       </c>
       <c r="K978" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="L978" t="n">
         <v>0</v>
@@ -76357,7 +76352,7 @@
         </is>
       </c>
       <c r="C979" t="n">
-        <v>2688</v>
+        <v>2687</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -76393,7 +76388,7 @@
         </is>
       </c>
       <c r="K979" t="n">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="L979" t="n">
         <v>0</v>
@@ -76445,7 +76440,7 @@
         </is>
       </c>
       <c r="K980" t="n">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="L980" t="n">
         <v>0</v>
@@ -76497,7 +76492,7 @@
         </is>
       </c>
       <c r="K981" t="n">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="L981" t="n">
         <v>0</v>
@@ -76549,7 +76544,7 @@
         </is>
       </c>
       <c r="K982" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="L982" t="n">
         <v>0</v>
@@ -76601,7 +76596,7 @@
         </is>
       </c>
       <c r="K983" t="n">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="L983" t="n">
         <v>0</v>
@@ -76653,7 +76648,7 @@
         </is>
       </c>
       <c r="K984" t="n">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="L984" t="n">
         <v>0</v>
@@ -76705,7 +76700,7 @@
         </is>
       </c>
       <c r="K985" t="n">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="L985" t="n">
         <v>0</v>
@@ -76757,7 +76752,7 @@
         </is>
       </c>
       <c r="K986" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="L986" t="n">
         <v>0</v>
@@ -76809,7 +76804,7 @@
         </is>
       </c>
       <c r="K987" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="L987" t="n">
         <v>0</v>
@@ -76861,7 +76856,7 @@
         </is>
       </c>
       <c r="K988" t="n">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="L988" t="n">
         <v>0</v>
@@ -76913,7 +76908,7 @@
         </is>
       </c>
       <c r="K989" t="n">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="L989" t="n">
         <v>0</v>
@@ -76965,7 +76960,7 @@
         </is>
       </c>
       <c r="K990" t="n">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="L990" t="n">
         <v>0</v>
@@ -77017,7 +77012,7 @@
         </is>
       </c>
       <c r="K991" t="n">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="L991" t="n">
         <v>0</v>
@@ -77069,7 +77064,7 @@
         </is>
       </c>
       <c r="K992" t="n">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="L992" t="n">
         <v>0</v>
@@ -77121,7 +77116,7 @@
         </is>
       </c>
       <c r="K993" t="n">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="L993" t="n">
         <v>0</v>
@@ -77173,7 +77168,7 @@
         </is>
       </c>
       <c r="K994" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L994" t="n">
         <v>0</v>
@@ -77225,7 +77220,7 @@
         </is>
       </c>
       <c r="K995" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L995" t="n">
         <v>0</v>
@@ -77277,7 +77272,7 @@
         </is>
       </c>
       <c r="K996" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="L996" t="n">
         <v>0</v>
@@ -77329,7 +77324,7 @@
         </is>
       </c>
       <c r="K997" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="L997" t="n">
         <v>0</v>
@@ -77381,7 +77376,7 @@
         </is>
       </c>
       <c r="K998" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L998" t="n">
         <v>0</v>
@@ -77485,7 +77480,7 @@
         </is>
       </c>
       <c r="K1000" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="L1000" t="n">
         <v>0</v>
@@ -77537,7 +77532,7 @@
         </is>
       </c>
       <c r="K1001" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="L1001" t="n">
         <v>0</v>

--- a/Data/Output/stress_1000_enriched.xlsx
+++ b/Data/Output/stress_1000_enriched.xlsx
@@ -25584,7 +25584,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -25636,7 +25636,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -25688,7 +25688,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -25740,7 +25740,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -25792,7 +25792,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -25844,7 +25844,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -25896,7 +25896,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -25948,7 +25948,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -26000,7 +26000,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -26052,7 +26052,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -26104,7 +26104,7 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -26156,7 +26156,7 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -26208,7 +26208,7 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -26260,7 +26260,7 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -26364,7 +26364,7 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -26416,7 +26416,7 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -26468,7 +26468,7 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -26520,7 +26520,7 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -26572,7 +26572,7 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -26624,7 +26624,7 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -26676,7 +26676,7 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -26728,7 +26728,7 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -26780,7 +26780,7 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -26832,7 +26832,7 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -26884,7 +26884,7 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -26936,7 +26936,7 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -26988,7 +26988,7 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -27040,7 +27040,7 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -27092,7 +27092,7 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -27144,7 +27144,7 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -27196,7 +27196,7 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -27300,7 +27300,7 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -27352,7 +27352,7 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -27404,7 +27404,7 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -27508,7 +27508,7 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -27560,7 +27560,7 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -27612,7 +27612,7 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -27664,7 +27664,7 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -27768,7 +27768,7 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -27820,7 +27820,7 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -27976,7 +27976,7 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -28028,7 +28028,7 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -28080,7 +28080,7 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -28132,7 +28132,7 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -28184,7 +28184,7 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -28236,7 +28236,7 @@
         </is>
       </c>
       <c r="K53" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -28288,7 +28288,7 @@
         </is>
       </c>
       <c r="K54" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -28340,7 +28340,7 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -28392,7 +28392,7 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -28444,7 +28444,7 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -28496,7 +28496,7 @@
         </is>
       </c>
       <c r="K58" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -28548,7 +28548,7 @@
         </is>
       </c>
       <c r="K59" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -28600,7 +28600,7 @@
         </is>
       </c>
       <c r="K60" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -28652,7 +28652,7 @@
         </is>
       </c>
       <c r="K61" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -28704,7 +28704,7 @@
         </is>
       </c>
       <c r="K62" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -28756,7 +28756,7 @@
         </is>
       </c>
       <c r="K63" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -28808,7 +28808,7 @@
         </is>
       </c>
       <c r="K64" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -28860,7 +28860,7 @@
         </is>
       </c>
       <c r="K65" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -28912,7 +28912,7 @@
         </is>
       </c>
       <c r="K66" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -28964,7 +28964,7 @@
         </is>
       </c>
       <c r="K67" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -29016,7 +29016,7 @@
         </is>
       </c>
       <c r="K68" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -29068,7 +29068,7 @@
         </is>
       </c>
       <c r="K69" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -29120,7 +29120,7 @@
         </is>
       </c>
       <c r="K70" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -29172,7 +29172,7 @@
         </is>
       </c>
       <c r="K71" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
@@ -29224,7 +29224,7 @@
         </is>
       </c>
       <c r="K72" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
@@ -29276,7 +29276,7 @@
         </is>
       </c>
       <c r="K73" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -29328,7 +29328,7 @@
         </is>
       </c>
       <c r="K74" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
@@ -29380,7 +29380,7 @@
         </is>
       </c>
       <c r="K75" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -29432,7 +29432,7 @@
         </is>
       </c>
       <c r="K76" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
@@ -29484,7 +29484,7 @@
         </is>
       </c>
       <c r="K77" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -29536,7 +29536,7 @@
         </is>
       </c>
       <c r="K78" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -29588,7 +29588,7 @@
         </is>
       </c>
       <c r="K79" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
@@ -29640,7 +29640,7 @@
         </is>
       </c>
       <c r="K80" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -29692,7 +29692,7 @@
         </is>
       </c>
       <c r="K81" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -29744,7 +29744,7 @@
         </is>
       </c>
       <c r="K82" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -29796,7 +29796,7 @@
         </is>
       </c>
       <c r="K83" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -29848,7 +29848,7 @@
         </is>
       </c>
       <c r="K84" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
@@ -29900,7 +29900,7 @@
         </is>
       </c>
       <c r="K85" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -29952,7 +29952,7 @@
         </is>
       </c>
       <c r="K86" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
@@ -30004,7 +30004,7 @@
         </is>
       </c>
       <c r="K87" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -30056,7 +30056,7 @@
         </is>
       </c>
       <c r="K88" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -30108,7 +30108,7 @@
         </is>
       </c>
       <c r="K89" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
@@ -30160,7 +30160,7 @@
         </is>
       </c>
       <c r="K90" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -30212,7 +30212,7 @@
         </is>
       </c>
       <c r="K91" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="L91" t="n">
         <v>0</v>
@@ -30264,7 +30264,7 @@
         </is>
       </c>
       <c r="K92" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
@@ -30316,7 +30316,7 @@
         </is>
       </c>
       <c r="K93" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
@@ -30368,7 +30368,7 @@
         </is>
       </c>
       <c r="K94" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="L94" t="n">
         <v>0</v>
@@ -30420,7 +30420,7 @@
         </is>
       </c>
       <c r="K95" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="L95" t="n">
         <v>0</v>
@@ -30472,7 +30472,7 @@
         </is>
       </c>
       <c r="K96" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
@@ -30524,7 +30524,7 @@
         </is>
       </c>
       <c r="K97" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
@@ -30576,7 +30576,7 @@
         </is>
       </c>
       <c r="K98" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
@@ -30628,7 +30628,7 @@
         </is>
       </c>
       <c r="K99" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
@@ -30680,7 +30680,7 @@
         </is>
       </c>
       <c r="K100" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>
@@ -30732,7 +30732,7 @@
         </is>
       </c>
       <c r="K101" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="L101" t="n">
         <v>0</v>
@@ -30784,7 +30784,7 @@
         </is>
       </c>
       <c r="K102" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L102" t="n">
         <v>0</v>
@@ -30836,7 +30836,7 @@
         </is>
       </c>
       <c r="K103" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L103" t="n">
         <v>0</v>
@@ -30888,7 +30888,7 @@
         </is>
       </c>
       <c r="K104" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
@@ -30940,7 +30940,7 @@
         </is>
       </c>
       <c r="K105" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L105" t="n">
         <v>0</v>
@@ -30992,7 +30992,7 @@
         </is>
       </c>
       <c r="K106" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
@@ -31044,7 +31044,7 @@
         </is>
       </c>
       <c r="K107" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L107" t="n">
         <v>0</v>
@@ -31096,7 +31096,7 @@
         </is>
       </c>
       <c r="K108" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
@@ -31148,7 +31148,7 @@
         </is>
       </c>
       <c r="K109" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
@@ -31200,7 +31200,7 @@
         </is>
       </c>
       <c r="K110" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L110" t="n">
         <v>0</v>
@@ -31252,7 +31252,7 @@
         </is>
       </c>
       <c r="K111" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L111" t="n">
         <v>0</v>
@@ -31304,7 +31304,7 @@
         </is>
       </c>
       <c r="K112" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
@@ -31356,7 +31356,7 @@
         </is>
       </c>
       <c r="K113" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
@@ -31408,7 +31408,7 @@
         </is>
       </c>
       <c r="K114" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
@@ -31460,7 +31460,7 @@
         </is>
       </c>
       <c r="K115" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L115" t="n">
         <v>0</v>
@@ -31512,7 +31512,7 @@
         </is>
       </c>
       <c r="K116" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
@@ -31564,7 +31564,7 @@
         </is>
       </c>
       <c r="K117" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
@@ -31616,7 +31616,7 @@
         </is>
       </c>
       <c r="K118" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
@@ -31668,7 +31668,7 @@
         </is>
       </c>
       <c r="K119" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
@@ -31720,7 +31720,7 @@
         </is>
       </c>
       <c r="K120" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L120" t="n">
         <v>0</v>
@@ -31772,7 +31772,7 @@
         </is>
       </c>
       <c r="K121" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L121" t="n">
         <v>0</v>
@@ -31824,7 +31824,7 @@
         </is>
       </c>
       <c r="K122" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="L122" t="n">
         <v>0</v>
@@ -31876,7 +31876,7 @@
         </is>
       </c>
       <c r="K123" t="n">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="L123" t="n">
         <v>0</v>
@@ -31928,7 +31928,7 @@
         </is>
       </c>
       <c r="K124" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
@@ -31980,7 +31980,7 @@
         </is>
       </c>
       <c r="K125" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="L125" t="n">
         <v>0</v>
@@ -32032,7 +32032,7 @@
         </is>
       </c>
       <c r="K126" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="L126" t="n">
         <v>0</v>
@@ -32084,7 +32084,7 @@
         </is>
       </c>
       <c r="K127" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="L127" t="n">
         <v>0</v>
@@ -32136,7 +32136,7 @@
         </is>
       </c>
       <c r="K128" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="L128" t="n">
         <v>0</v>
@@ -32188,7 +32188,7 @@
         </is>
       </c>
       <c r="K129" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="L129" t="n">
         <v>0</v>
@@ -32240,7 +32240,7 @@
         </is>
       </c>
       <c r="K130" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="L130" t="n">
         <v>0</v>
@@ -32292,7 +32292,7 @@
         </is>
       </c>
       <c r="K131" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="L131" t="n">
         <v>0</v>
@@ -32344,7 +32344,7 @@
         </is>
       </c>
       <c r="K132" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="L132" t="n">
         <v>0</v>
@@ -32396,7 +32396,7 @@
         </is>
       </c>
       <c r="K133" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="L133" t="n">
         <v>0</v>
@@ -32448,7 +32448,7 @@
         </is>
       </c>
       <c r="K134" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="L134" t="n">
         <v>0</v>
@@ -32500,7 +32500,7 @@
         </is>
       </c>
       <c r="K135" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="L135" t="n">
         <v>0</v>
@@ -32552,7 +32552,7 @@
         </is>
       </c>
       <c r="K136" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="L136" t="n">
         <v>0</v>
@@ -32604,7 +32604,7 @@
         </is>
       </c>
       <c r="K137" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="L137" t="n">
         <v>0</v>
@@ -32656,7 +32656,7 @@
         </is>
       </c>
       <c r="K138" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="L138" t="n">
         <v>0</v>
@@ -32708,7 +32708,7 @@
         </is>
       </c>
       <c r="K139" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
@@ -32760,7 +32760,7 @@
         </is>
       </c>
       <c r="K140" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
@@ -32812,7 +32812,7 @@
         </is>
       </c>
       <c r="K141" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
@@ -32864,7 +32864,7 @@
         </is>
       </c>
       <c r="K142" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="L142" t="n">
         <v>0</v>
@@ -32916,7 +32916,7 @@
         </is>
       </c>
       <c r="K143" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="L143" t="n">
         <v>0</v>
@@ -32968,7 +32968,7 @@
         </is>
       </c>
       <c r="K144" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="L144" t="n">
         <v>0</v>
@@ -33020,7 +33020,7 @@
         </is>
       </c>
       <c r="K145" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="L145" t="n">
         <v>0</v>
@@ -33072,7 +33072,7 @@
         </is>
       </c>
       <c r="K146" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="L146" t="n">
         <v>0</v>
@@ -33124,7 +33124,7 @@
         </is>
       </c>
       <c r="K147" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="L147" t="n">
         <v>0</v>
@@ -33176,7 +33176,7 @@
         </is>
       </c>
       <c r="K148" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="L148" t="n">
         <v>0</v>
@@ -33228,7 +33228,7 @@
         </is>
       </c>
       <c r="K149" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="L149" t="n">
         <v>0</v>
@@ -33280,7 +33280,7 @@
         </is>
       </c>
       <c r="K150" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="L150" t="n">
         <v>0</v>
@@ -33332,7 +33332,7 @@
         </is>
       </c>
       <c r="K151" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="L151" t="n">
         <v>0</v>
@@ -33384,7 +33384,7 @@
         </is>
       </c>
       <c r="K152" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="L152" t="n">
         <v>0</v>
@@ -33436,7 +33436,7 @@
         </is>
       </c>
       <c r="K153" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="L153" t="n">
         <v>0</v>
@@ -33488,7 +33488,7 @@
         </is>
       </c>
       <c r="K154" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="L154" t="n">
         <v>0</v>
@@ -33540,7 +33540,7 @@
         </is>
       </c>
       <c r="K155" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="L155" t="n">
         <v>0</v>
@@ -33592,7 +33592,7 @@
         </is>
       </c>
       <c r="K156" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="L156" t="n">
         <v>0</v>
@@ -33644,7 +33644,7 @@
         </is>
       </c>
       <c r="K157" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="L157" t="n">
         <v>0</v>
@@ -33696,7 +33696,7 @@
         </is>
       </c>
       <c r="K158" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="L158" t="n">
         <v>0</v>
@@ -33748,7 +33748,7 @@
         </is>
       </c>
       <c r="K159" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="L159" t="n">
         <v>0</v>
@@ -33800,7 +33800,7 @@
         </is>
       </c>
       <c r="K160" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="L160" t="n">
         <v>0</v>
@@ -33852,7 +33852,7 @@
         </is>
       </c>
       <c r="K161" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="L161" t="n">
         <v>0</v>
@@ -33904,7 +33904,7 @@
         </is>
       </c>
       <c r="K162" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="L162" t="n">
         <v>0</v>
@@ -33956,7 +33956,7 @@
         </is>
       </c>
       <c r="K163" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="L163" t="n">
         <v>0</v>
@@ -34008,7 +34008,7 @@
         </is>
       </c>
       <c r="K164" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="L164" t="n">
         <v>0</v>
@@ -34060,7 +34060,7 @@
         </is>
       </c>
       <c r="K165" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="L165" t="n">
         <v>0</v>
@@ -34112,7 +34112,7 @@
         </is>
       </c>
       <c r="K166" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="L166" t="n">
         <v>0</v>
@@ -34164,7 +34164,7 @@
         </is>
       </c>
       <c r="K167" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="L167" t="n">
         <v>0</v>
@@ -34216,7 +34216,7 @@
         </is>
       </c>
       <c r="K168" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="L168" t="n">
         <v>0</v>
@@ -34268,7 +34268,7 @@
         </is>
       </c>
       <c r="K169" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="L169" t="n">
         <v>0</v>
@@ -34320,7 +34320,7 @@
         </is>
       </c>
       <c r="K170" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="L170" t="n">
         <v>0</v>
@@ -34372,7 +34372,7 @@
         </is>
       </c>
       <c r="K171" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="L171" t="n">
         <v>0</v>
@@ -34424,7 +34424,7 @@
         </is>
       </c>
       <c r="K172" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="L172" t="n">
         <v>0</v>
@@ -34476,7 +34476,7 @@
         </is>
       </c>
       <c r="K173" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="L173" t="n">
         <v>0</v>
@@ -34528,7 +34528,7 @@
         </is>
       </c>
       <c r="K174" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="L174" t="n">
         <v>0</v>
@@ -34580,7 +34580,7 @@
         </is>
       </c>
       <c r="K175" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="L175" t="n">
         <v>0</v>
@@ -34632,7 +34632,7 @@
         </is>
       </c>
       <c r="K176" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="L176" t="n">
         <v>0</v>
@@ -34684,7 +34684,7 @@
         </is>
       </c>
       <c r="K177" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="L177" t="n">
         <v>0</v>
@@ -34736,7 +34736,7 @@
         </is>
       </c>
       <c r="K178" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="L178" t="n">
         <v>0</v>
@@ -34788,7 +34788,7 @@
         </is>
       </c>
       <c r="K179" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="L179" t="n">
         <v>0</v>
@@ -34840,7 +34840,7 @@
         </is>
       </c>
       <c r="K180" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="L180" t="n">
         <v>0</v>
@@ -34892,7 +34892,7 @@
         </is>
       </c>
       <c r="K181" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="L181" t="n">
         <v>0</v>
@@ -34944,7 +34944,7 @@
         </is>
       </c>
       <c r="K182" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="L182" t="n">
         <v>0</v>
@@ -34996,7 +34996,7 @@
         </is>
       </c>
       <c r="K183" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="L183" t="n">
         <v>0</v>
@@ -35048,7 +35048,7 @@
         </is>
       </c>
       <c r="K184" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="L184" t="n">
         <v>0</v>
@@ -35100,7 +35100,7 @@
         </is>
       </c>
       <c r="K185" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="L185" t="n">
         <v>0</v>
@@ -35152,7 +35152,7 @@
         </is>
       </c>
       <c r="K186" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="L186" t="n">
         <v>0</v>
@@ -35204,7 +35204,7 @@
         </is>
       </c>
       <c r="K187" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="L187" t="n">
         <v>0</v>
@@ -35256,7 +35256,7 @@
         </is>
       </c>
       <c r="K188" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="L188" t="n">
         <v>0</v>
@@ -35308,7 +35308,7 @@
         </is>
       </c>
       <c r="K189" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="L189" t="n">
         <v>0</v>
@@ -35360,7 +35360,7 @@
         </is>
       </c>
       <c r="K190" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="L190" t="n">
         <v>0</v>
@@ -35412,7 +35412,7 @@
         </is>
       </c>
       <c r="K191" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="L191" t="n">
         <v>0</v>
@@ -35464,7 +35464,7 @@
         </is>
       </c>
       <c r="K192" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="L192" t="n">
         <v>0</v>
@@ -35516,7 +35516,7 @@
         </is>
       </c>
       <c r="K193" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="L193" t="n">
         <v>0</v>
@@ -35568,7 +35568,7 @@
         </is>
       </c>
       <c r="K194" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="L194" t="n">
         <v>0</v>
@@ -35620,7 +35620,7 @@
         </is>
       </c>
       <c r="K195" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="L195" t="n">
         <v>0</v>
@@ -35672,7 +35672,7 @@
         </is>
       </c>
       <c r="K196" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="L196" t="n">
         <v>0</v>
@@ -35724,7 +35724,7 @@
         </is>
       </c>
       <c r="K197" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="L197" t="n">
         <v>0</v>
@@ -35776,7 +35776,7 @@
         </is>
       </c>
       <c r="K198" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="L198" t="n">
         <v>0</v>
@@ -35828,7 +35828,7 @@
         </is>
       </c>
       <c r="K199" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="L199" t="n">
         <v>0</v>
@@ -35880,7 +35880,7 @@
         </is>
       </c>
       <c r="K200" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="L200" t="n">
         <v>0</v>
@@ -35932,7 +35932,7 @@
         </is>
       </c>
       <c r="K201" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="L201" t="n">
         <v>0</v>
@@ -35984,7 +35984,7 @@
         </is>
       </c>
       <c r="K202" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="L202" t="n">
         <v>0</v>
@@ -36036,7 +36036,7 @@
         </is>
       </c>
       <c r="K203" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="L203" t="n">
         <v>0</v>
@@ -36088,7 +36088,7 @@
         </is>
       </c>
       <c r="K204" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="L204" t="n">
         <v>0</v>
@@ -36140,7 +36140,7 @@
         </is>
       </c>
       <c r="K205" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="L205" t="n">
         <v>0</v>
@@ -36192,7 +36192,7 @@
         </is>
       </c>
       <c r="K206" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="L206" t="n">
         <v>0</v>
@@ -36244,7 +36244,7 @@
         </is>
       </c>
       <c r="K207" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="L207" t="n">
         <v>0</v>
@@ -36296,7 +36296,7 @@
         </is>
       </c>
       <c r="K208" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="L208" t="n">
         <v>0</v>
@@ -36348,7 +36348,7 @@
         </is>
       </c>
       <c r="K209" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="L209" t="n">
         <v>0</v>
@@ -36400,7 +36400,7 @@
         </is>
       </c>
       <c r="K210" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="L210" t="n">
         <v>0</v>
@@ -36452,7 +36452,7 @@
         </is>
       </c>
       <c r="K211" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="L211" t="n">
         <v>0</v>
@@ -36504,7 +36504,7 @@
         </is>
       </c>
       <c r="K212" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="L212" t="n">
         <v>0</v>
@@ -36556,7 +36556,7 @@
         </is>
       </c>
       <c r="K213" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="L213" t="n">
         <v>0</v>
@@ -36608,7 +36608,7 @@
         </is>
       </c>
       <c r="K214" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="L214" t="n">
         <v>0</v>
@@ -36660,7 +36660,7 @@
         </is>
       </c>
       <c r="K215" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="L215" t="n">
         <v>0</v>
@@ -36712,7 +36712,7 @@
         </is>
       </c>
       <c r="K216" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="L216" t="n">
         <v>0</v>
@@ -36764,7 +36764,7 @@
         </is>
       </c>
       <c r="K217" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="L217" t="n">
         <v>0</v>
@@ -36816,7 +36816,7 @@
         </is>
       </c>
       <c r="K218" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="L218" t="n">
         <v>0</v>
@@ -36868,7 +36868,7 @@
         </is>
       </c>
       <c r="K219" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="L219" t="n">
         <v>0</v>
@@ -36920,7 +36920,7 @@
         </is>
       </c>
       <c r="K220" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="L220" t="n">
         <v>0</v>
@@ -36972,7 +36972,7 @@
         </is>
       </c>
       <c r="K221" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="L221" t="n">
         <v>0</v>
@@ -37024,7 +37024,7 @@
         </is>
       </c>
       <c r="K222" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="L222" t="n">
         <v>0</v>
@@ -37076,7 +37076,7 @@
         </is>
       </c>
       <c r="K223" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="L223" t="n">
         <v>0</v>
@@ -37128,7 +37128,7 @@
         </is>
       </c>
       <c r="K224" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="L224" t="n">
         <v>0</v>
@@ -37180,7 +37180,7 @@
         </is>
       </c>
       <c r="K225" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="L225" t="n">
         <v>0</v>
@@ -37232,7 +37232,7 @@
         </is>
       </c>
       <c r="K226" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="L226" t="n">
         <v>0</v>
@@ -37284,7 +37284,7 @@
         </is>
       </c>
       <c r="K227" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="L227" t="n">
         <v>0</v>
@@ -37336,7 +37336,7 @@
         </is>
       </c>
       <c r="K228" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="L228" t="n">
         <v>0</v>
@@ -37388,7 +37388,7 @@
         </is>
       </c>
       <c r="K229" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="L229" t="n">
         <v>0</v>
@@ -37440,7 +37440,7 @@
         </is>
       </c>
       <c r="K230" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="L230" t="n">
         <v>0</v>
@@ -37492,7 +37492,7 @@
         </is>
       </c>
       <c r="K231" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="L231" t="n">
         <v>0</v>
@@ -37544,7 +37544,7 @@
         </is>
       </c>
       <c r="K232" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="L232" t="n">
         <v>0</v>
@@ -37596,7 +37596,7 @@
         </is>
       </c>
       <c r="K233" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="L233" t="n">
         <v>0</v>
@@ -37648,7 +37648,7 @@
         </is>
       </c>
       <c r="K234" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="L234" t="n">
         <v>0</v>
@@ -37700,7 +37700,7 @@
         </is>
       </c>
       <c r="K235" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="L235" t="n">
         <v>0</v>
@@ -37752,7 +37752,7 @@
         </is>
       </c>
       <c r="K236" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="L236" t="n">
         <v>0</v>
@@ -37804,7 +37804,7 @@
         </is>
       </c>
       <c r="K237" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="L237" t="n">
         <v>0</v>
@@ -37856,7 +37856,7 @@
         </is>
       </c>
       <c r="K238" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="L238" t="n">
         <v>0</v>
@@ -37908,7 +37908,7 @@
         </is>
       </c>
       <c r="K239" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="L239" t="n">
         <v>0</v>
@@ -37960,7 +37960,7 @@
         </is>
       </c>
       <c r="K240" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L240" t="n">
         <v>0</v>
@@ -38116,7 +38116,7 @@
         </is>
       </c>
       <c r="K243" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L243" t="n">
         <v>0</v>
@@ -38168,7 +38168,7 @@
         </is>
       </c>
       <c r="K244" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L244" t="n">
         <v>0</v>
@@ -38220,7 +38220,7 @@
         </is>
       </c>
       <c r="K245" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L245" t="n">
         <v>0</v>
@@ -38272,7 +38272,7 @@
         </is>
       </c>
       <c r="K246" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L246" t="n">
         <v>0</v>
@@ -38376,7 +38376,7 @@
         </is>
       </c>
       <c r="K248" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L248" t="n">
         <v>0</v>
@@ -38428,7 +38428,7 @@
         </is>
       </c>
       <c r="K249" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L249" t="n">
         <v>0</v>
@@ -38584,7 +38584,7 @@
         </is>
       </c>
       <c r="K252" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L252" t="n">
         <v>0</v>
@@ -38688,7 +38688,7 @@
         </is>
       </c>
       <c r="K254" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L254" t="n">
         <v>0</v>
@@ -38792,7 +38792,7 @@
         </is>
       </c>
       <c r="K256" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L256" t="n">
         <v>0</v>
@@ -38844,7 +38844,7 @@
         </is>
       </c>
       <c r="K257" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L257" t="n">
         <v>0</v>
@@ -38948,7 +38948,7 @@
         </is>
       </c>
       <c r="K259" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L259" t="n">
         <v>0</v>
@@ -39000,7 +39000,7 @@
         </is>
       </c>
       <c r="K260" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L260" t="n">
         <v>0</v>
@@ -39156,7 +39156,7 @@
         </is>
       </c>
       <c r="K263" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L263" t="n">
         <v>0</v>
@@ -39260,7 +39260,7 @@
         </is>
       </c>
       <c r="K265" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L265" t="n">
         <v>0</v>
@@ -39468,7 +39468,7 @@
         </is>
       </c>
       <c r="K269" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L269" t="n">
         <v>0</v>
@@ -39572,7 +39572,7 @@
         </is>
       </c>
       <c r="K271" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="L271" t="n">
         <v>0</v>
@@ -39624,7 +39624,7 @@
         </is>
       </c>
       <c r="K272" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="L272" t="n">
         <v>0</v>
@@ -39676,7 +39676,7 @@
         </is>
       </c>
       <c r="K273" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="L273" t="n">
         <v>0</v>
@@ -39728,7 +39728,7 @@
         </is>
       </c>
       <c r="K274" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="L274" t="n">
         <v>0</v>
@@ -39780,7 +39780,7 @@
         </is>
       </c>
       <c r="K275" t="n">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="L275" t="n">
         <v>0</v>
@@ -39832,7 +39832,7 @@
         </is>
       </c>
       <c r="K276" t="n">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="L276" t="n">
         <v>0</v>
@@ -39884,7 +39884,7 @@
         </is>
       </c>
       <c r="K277" t="n">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="L277" t="n">
         <v>0</v>
@@ -39936,7 +39936,7 @@
         </is>
       </c>
       <c r="K278" t="n">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="L278" t="n">
         <v>0</v>
@@ -39988,7 +39988,7 @@
         </is>
       </c>
       <c r="K279" t="n">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="L279" t="n">
         <v>0</v>
@@ -40040,7 +40040,7 @@
         </is>
       </c>
       <c r="K280" t="n">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="L280" t="n">
         <v>0</v>
@@ -40092,7 +40092,7 @@
         </is>
       </c>
       <c r="K281" t="n">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="L281" t="n">
         <v>0</v>
@@ -40144,7 +40144,7 @@
         </is>
       </c>
       <c r="K282" t="n">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="L282" t="n">
         <v>0</v>
@@ -40196,7 +40196,7 @@
         </is>
       </c>
       <c r="K283" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="L283" t="n">
         <v>0</v>
@@ -40248,7 +40248,7 @@
         </is>
       </c>
       <c r="K284" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="L284" t="n">
         <v>0</v>
@@ -40300,7 +40300,7 @@
         </is>
       </c>
       <c r="K285" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="L285" t="n">
         <v>0</v>
@@ -40352,7 +40352,7 @@
         </is>
       </c>
       <c r="K286" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="L286" t="n">
         <v>0</v>
@@ -40404,7 +40404,7 @@
         </is>
       </c>
       <c r="K287" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="L287" t="n">
         <v>0</v>
@@ -40456,7 +40456,7 @@
         </is>
       </c>
       <c r="K288" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="L288" t="n">
         <v>0</v>
@@ -40508,7 +40508,7 @@
         </is>
       </c>
       <c r="K289" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="L289" t="n">
         <v>0</v>
@@ -40560,7 +40560,7 @@
         </is>
       </c>
       <c r="K290" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L290" t="n">
         <v>0</v>
@@ -40612,7 +40612,7 @@
         </is>
       </c>
       <c r="K291" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="L291" t="n">
         <v>0</v>
@@ -40664,7 +40664,7 @@
         </is>
       </c>
       <c r="K292" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="L292" t="n">
         <v>0</v>
@@ -40716,7 +40716,7 @@
         </is>
       </c>
       <c r="K293" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="L293" t="n">
         <v>0</v>
@@ -40768,7 +40768,7 @@
         </is>
       </c>
       <c r="K294" t="n">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="L294" t="n">
         <v>0</v>
@@ -40820,7 +40820,7 @@
         </is>
       </c>
       <c r="K295" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="L295" t="n">
         <v>0</v>
@@ -40872,7 +40872,7 @@
         </is>
       </c>
       <c r="K296" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="L296" t="n">
         <v>0</v>
@@ -40924,7 +40924,7 @@
         </is>
       </c>
       <c r="K297" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="L297" t="n">
         <v>0</v>
@@ -40976,7 +40976,7 @@
         </is>
       </c>
       <c r="K298" t="n">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="L298" t="n">
         <v>0</v>
@@ -41028,7 +41028,7 @@
         </is>
       </c>
       <c r="K299" t="n">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="L299" t="n">
         <v>0</v>
@@ -41080,7 +41080,7 @@
         </is>
       </c>
       <c r="K300" t="n">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="L300" t="n">
         <v>0</v>
@@ -41132,7 +41132,7 @@
         </is>
       </c>
       <c r="K301" t="n">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="L301" t="n">
         <v>0</v>
@@ -41184,7 +41184,7 @@
         </is>
       </c>
       <c r="K302" t="n">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="L302" t="n">
         <v>0</v>
@@ -41236,7 +41236,7 @@
         </is>
       </c>
       <c r="K303" t="n">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="L303" t="n">
         <v>0</v>
@@ -41288,7 +41288,7 @@
         </is>
       </c>
       <c r="K304" t="n">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="L304" t="n">
         <v>0</v>
@@ -41340,7 +41340,7 @@
         </is>
       </c>
       <c r="K305" t="n">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="L305" t="n">
         <v>0</v>
@@ -41392,7 +41392,7 @@
         </is>
       </c>
       <c r="K306" t="n">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="L306" t="n">
         <v>0</v>
@@ -41444,7 +41444,7 @@
         </is>
       </c>
       <c r="K307" t="n">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="L307" t="n">
         <v>0</v>
@@ -41496,7 +41496,7 @@
         </is>
       </c>
       <c r="K308" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="L308" t="n">
         <v>0</v>
@@ -41548,7 +41548,7 @@
         </is>
       </c>
       <c r="K309" t="n">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="L309" t="n">
         <v>0</v>
@@ -41600,7 +41600,7 @@
         </is>
       </c>
       <c r="K310" t="n">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="L310" t="n">
         <v>0</v>
@@ -41652,7 +41652,7 @@
         </is>
       </c>
       <c r="K311" t="n">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="L311" t="n">
         <v>0</v>
@@ -41704,7 +41704,7 @@
         </is>
       </c>
       <c r="K312" t="n">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="L312" t="n">
         <v>0</v>
@@ -41756,7 +41756,7 @@
         </is>
       </c>
       <c r="K313" t="n">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="L313" t="n">
         <v>0</v>
@@ -41808,7 +41808,7 @@
         </is>
       </c>
       <c r="K314" t="n">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="L314" t="n">
         <v>0</v>
@@ -41860,7 +41860,7 @@
         </is>
       </c>
       <c r="K315" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="L315" t="n">
         <v>0</v>
@@ -41912,7 +41912,7 @@
         </is>
       </c>
       <c r="K316" t="n">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="L316" t="n">
         <v>0</v>
@@ -41964,7 +41964,7 @@
         </is>
       </c>
       <c r="K317" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="L317" t="n">
         <v>0</v>
@@ -42016,7 +42016,7 @@
         </is>
       </c>
       <c r="K318" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="L318" t="n">
         <v>0</v>
@@ -42068,7 +42068,7 @@
         </is>
       </c>
       <c r="K319" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L319" t="n">
         <v>0</v>
@@ -42120,7 +42120,7 @@
         </is>
       </c>
       <c r="K320" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="L320" t="n">
         <v>0</v>
@@ -42172,7 +42172,7 @@
         </is>
       </c>
       <c r="K321" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="L321" t="n">
         <v>0</v>
@@ -42224,7 +42224,7 @@
         </is>
       </c>
       <c r="K322" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="L322" t="n">
         <v>0</v>
@@ -42276,7 +42276,7 @@
         </is>
       </c>
       <c r="K323" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="L323" t="n">
         <v>0</v>
@@ -42328,7 +42328,7 @@
         </is>
       </c>
       <c r="K324" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="L324" t="n">
         <v>0</v>
@@ -42380,7 +42380,7 @@
         </is>
       </c>
       <c r="K325" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="L325" t="n">
         <v>0</v>
@@ -42432,7 +42432,7 @@
         </is>
       </c>
       <c r="K326" t="n">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="L326" t="n">
         <v>0</v>
@@ -42484,7 +42484,7 @@
         </is>
       </c>
       <c r="K327" t="n">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="L327" t="n">
         <v>0</v>
@@ -42536,7 +42536,7 @@
         </is>
       </c>
       <c r="K328" t="n">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="L328" t="n">
         <v>0</v>
@@ -42588,7 +42588,7 @@
         </is>
       </c>
       <c r="K329" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="L329" t="n">
         <v>0</v>
@@ -42640,7 +42640,7 @@
         </is>
       </c>
       <c r="K330" t="n">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="L330" t="n">
         <v>0</v>
@@ -42692,7 +42692,7 @@
         </is>
       </c>
       <c r="K331" t="n">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="L331" t="n">
         <v>0</v>
@@ -42744,7 +42744,7 @@
         </is>
       </c>
       <c r="K332" t="n">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="L332" t="n">
         <v>0</v>
@@ -42796,7 +42796,7 @@
         </is>
       </c>
       <c r="K333" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="L333" t="n">
         <v>0</v>
@@ -42848,7 +42848,7 @@
         </is>
       </c>
       <c r="K334" t="n">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="L334" t="n">
         <v>0</v>
@@ -42900,7 +42900,7 @@
         </is>
       </c>
       <c r="K335" t="n">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="L335" t="n">
         <v>0</v>
@@ -42952,7 +42952,7 @@
         </is>
       </c>
       <c r="K336" t="n">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="L336" t="n">
         <v>0</v>
@@ -43004,7 +43004,7 @@
         </is>
       </c>
       <c r="K337" t="n">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="L337" t="n">
         <v>0</v>
@@ -43056,7 +43056,7 @@
         </is>
       </c>
       <c r="K338" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L338" t="n">
         <v>0</v>
@@ -43108,7 +43108,7 @@
         </is>
       </c>
       <c r="K339" t="n">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="L339" t="n">
         <v>0</v>
@@ -43160,7 +43160,7 @@
         </is>
       </c>
       <c r="K340" t="n">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="L340" t="n">
         <v>0</v>
@@ -43212,7 +43212,7 @@
         </is>
       </c>
       <c r="K341" t="n">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="L341" t="n">
         <v>0</v>
@@ -43264,7 +43264,7 @@
         </is>
       </c>
       <c r="K342" t="n">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="L342" t="n">
         <v>0</v>
@@ -43316,7 +43316,7 @@
         </is>
       </c>
       <c r="K343" t="n">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="L343" t="n">
         <v>0</v>
@@ -43368,7 +43368,7 @@
         </is>
       </c>
       <c r="K344" t="n">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="L344" t="n">
         <v>0</v>
@@ -43420,7 +43420,7 @@
         </is>
       </c>
       <c r="K345" t="n">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="L345" t="n">
         <v>0</v>
@@ -43472,7 +43472,7 @@
         </is>
       </c>
       <c r="K346" t="n">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="L346" t="n">
         <v>0</v>
@@ -43524,7 +43524,7 @@
         </is>
       </c>
       <c r="K347" t="n">
-        <v>37</v>
+        <v>91</v>
       </c>
       <c r="L347" t="n">
         <v>0</v>
@@ -43576,7 +43576,7 @@
         </is>
       </c>
       <c r="K348" t="n">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="L348" t="n">
         <v>0</v>
@@ -43628,7 +43628,7 @@
         </is>
       </c>
       <c r="K349" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="L349" t="n">
         <v>0</v>
@@ -43680,7 +43680,7 @@
         </is>
       </c>
       <c r="K350" t="n">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="L350" t="n">
         <v>0</v>
@@ -43732,7 +43732,7 @@
         </is>
       </c>
       <c r="K351" t="n">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="L351" t="n">
         <v>0</v>
@@ -43784,7 +43784,7 @@
         </is>
       </c>
       <c r="K352" t="n">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="L352" t="n">
         <v>0</v>
@@ -43836,7 +43836,7 @@
         </is>
       </c>
       <c r="K353" t="n">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="L353" t="n">
         <v>0</v>
@@ -43888,7 +43888,7 @@
         </is>
       </c>
       <c r="K354" t="n">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="L354" t="n">
         <v>0</v>
@@ -43940,7 +43940,7 @@
         </is>
       </c>
       <c r="K355" t="n">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="L355" t="n">
         <v>0</v>
@@ -43992,7 +43992,7 @@
         </is>
       </c>
       <c r="K356" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="L356" t="n">
         <v>0</v>
@@ -44044,7 +44044,7 @@
         </is>
       </c>
       <c r="K357" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="L357" t="n">
         <v>0</v>
@@ -44096,7 +44096,7 @@
         </is>
       </c>
       <c r="K358" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="L358" t="n">
         <v>0</v>
@@ -44148,7 +44148,7 @@
         </is>
       </c>
       <c r="K359" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="L359" t="n">
         <v>0</v>
@@ -44200,7 +44200,7 @@
         </is>
       </c>
       <c r="K360" t="n">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="L360" t="n">
         <v>0</v>
@@ -44252,7 +44252,7 @@
         </is>
       </c>
       <c r="K361" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="L361" t="n">
         <v>0</v>
@@ -44304,7 +44304,7 @@
         </is>
       </c>
       <c r="K362" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="L362" t="n">
         <v>0</v>
@@ -44356,7 +44356,7 @@
         </is>
       </c>
       <c r="K363" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="L363" t="n">
         <v>0</v>
@@ -44408,7 +44408,7 @@
         </is>
       </c>
       <c r="K364" t="n">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="L364" t="n">
         <v>0</v>
@@ -44460,7 +44460,7 @@
         </is>
       </c>
       <c r="K365" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="L365" t="n">
         <v>0</v>
@@ -44512,7 +44512,7 @@
         </is>
       </c>
       <c r="K366" t="n">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="L366" t="n">
         <v>0</v>
@@ -44564,7 +44564,7 @@
         </is>
       </c>
       <c r="K367" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="L367" t="n">
         <v>0</v>
@@ -44616,7 +44616,7 @@
         </is>
       </c>
       <c r="K368" t="n">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="L368" t="n">
         <v>0</v>
@@ -44668,7 +44668,7 @@
         </is>
       </c>
       <c r="K369" t="n">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="L369" t="n">
         <v>0</v>
@@ -44720,7 +44720,7 @@
         </is>
       </c>
       <c r="K370" t="n">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="L370" t="n">
         <v>0</v>
@@ -44772,7 +44772,7 @@
         </is>
       </c>
       <c r="K371" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="L371" t="n">
         <v>0</v>
@@ -44824,7 +44824,7 @@
         </is>
       </c>
       <c r="K372" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="L372" t="n">
         <v>0</v>
@@ -44876,7 +44876,7 @@
         </is>
       </c>
       <c r="K373" t="n">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="L373" t="n">
         <v>0</v>
@@ -44928,7 +44928,7 @@
         </is>
       </c>
       <c r="K374" t="n">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="L374" t="n">
         <v>0</v>
@@ -44980,7 +44980,7 @@
         </is>
       </c>
       <c r="K375" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="L375" t="n">
         <v>0</v>
@@ -45032,7 +45032,7 @@
         </is>
       </c>
       <c r="K376" t="n">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="L376" t="n">
         <v>0</v>
@@ -45084,7 +45084,7 @@
         </is>
       </c>
       <c r="K377" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="L377" t="n">
         <v>0</v>
@@ -45136,7 +45136,7 @@
         </is>
       </c>
       <c r="K378" t="n">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="L378" t="n">
         <v>0</v>
@@ -45188,7 +45188,7 @@
         </is>
       </c>
       <c r="K379" t="n">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="L379" t="n">
         <v>0</v>
@@ -45240,7 +45240,7 @@
         </is>
       </c>
       <c r="K380" t="n">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="L380" t="n">
         <v>0</v>
@@ -45292,7 +45292,7 @@
         </is>
       </c>
       <c r="K381" t="n">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="L381" t="n">
         <v>0</v>
@@ -45344,7 +45344,7 @@
         </is>
       </c>
       <c r="K382" t="n">
-        <v>40</v>
+        <v>97</v>
       </c>
       <c r="L382" t="n">
         <v>0</v>
@@ -45396,7 +45396,7 @@
         </is>
       </c>
       <c r="K383" t="n">
-        <v>40</v>
+        <v>98</v>
       </c>
       <c r="L383" t="n">
         <v>0</v>
@@ -45448,7 +45448,7 @@
         </is>
       </c>
       <c r="K384" t="n">
-        <v>41</v>
+        <v>101</v>
       </c>
       <c r="L384" t="n">
         <v>0</v>
@@ -45500,7 +45500,7 @@
         </is>
       </c>
       <c r="K385" t="n">
-        <v>41</v>
+        <v>103</v>
       </c>
       <c r="L385" t="n">
         <v>0</v>
@@ -45552,7 +45552,7 @@
         </is>
       </c>
       <c r="K386" t="n">
-        <v>40</v>
+        <v>140</v>
       </c>
       <c r="L386" t="n">
         <v>0</v>
@@ -45604,7 +45604,7 @@
         </is>
       </c>
       <c r="K387" t="n">
-        <v>38</v>
+        <v>144</v>
       </c>
       <c r="L387" t="n">
         <v>0</v>
@@ -45656,7 +45656,7 @@
         </is>
       </c>
       <c r="K388" t="n">
-        <v>38</v>
+        <v>184</v>
       </c>
       <c r="L388" t="n">
         <v>0</v>
@@ -45708,7 +45708,7 @@
         </is>
       </c>
       <c r="K389" t="n">
-        <v>37</v>
+        <v>225</v>
       </c>
       <c r="L389" t="n">
         <v>0</v>
@@ -45760,7 +45760,7 @@
         </is>
       </c>
       <c r="K390" t="n">
-        <v>37</v>
+        <v>225</v>
       </c>
       <c r="L390" t="n">
         <v>0</v>
@@ -45812,7 +45812,7 @@
         </is>
       </c>
       <c r="K391" t="n">
-        <v>37</v>
+        <v>235</v>
       </c>
       <c r="L391" t="n">
         <v>0</v>
@@ -45864,7 +45864,7 @@
         </is>
       </c>
       <c r="K392" t="n">
-        <v>37</v>
+        <v>221</v>
       </c>
       <c r="L392" t="n">
         <v>0</v>
@@ -45916,7 +45916,7 @@
         </is>
       </c>
       <c r="K393" t="n">
-        <v>38</v>
+        <v>233</v>
       </c>
       <c r="L393" t="n">
         <v>0</v>
@@ -45968,7 +45968,7 @@
         </is>
       </c>
       <c r="K394" t="n">
-        <v>37</v>
+        <v>227</v>
       </c>
       <c r="L394" t="n">
         <v>0</v>
@@ -46020,7 +46020,7 @@
         </is>
       </c>
       <c r="K395" t="n">
-        <v>37</v>
+        <v>243</v>
       </c>
       <c r="L395" t="n">
         <v>0</v>
@@ -46072,7 +46072,7 @@
         </is>
       </c>
       <c r="K396" t="n">
-        <v>37</v>
+        <v>205</v>
       </c>
       <c r="L396" t="n">
         <v>0</v>
@@ -46124,7 +46124,7 @@
         </is>
       </c>
       <c r="K397" t="n">
-        <v>39</v>
+        <v>199</v>
       </c>
       <c r="L397" t="n">
         <v>0</v>
@@ -46176,7 +46176,7 @@
         </is>
       </c>
       <c r="K398" t="n">
-        <v>38</v>
+        <v>158</v>
       </c>
       <c r="L398" t="n">
         <v>0</v>
@@ -46228,7 +46228,7 @@
         </is>
       </c>
       <c r="K399" t="n">
-        <v>39</v>
+        <v>108</v>
       </c>
       <c r="L399" t="n">
         <v>0</v>
@@ -46280,7 +46280,7 @@
         </is>
       </c>
       <c r="K400" t="n">
-        <v>38</v>
+        <v>102</v>
       </c>
       <c r="L400" t="n">
         <v>0</v>
@@ -46332,7 +46332,7 @@
         </is>
       </c>
       <c r="K401" t="n">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="L401" t="n">
         <v>0</v>
@@ -46384,7 +46384,7 @@
         </is>
       </c>
       <c r="K402" t="n">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="L402" t="n">
         <v>0</v>
@@ -46436,7 +46436,7 @@
         </is>
       </c>
       <c r="K403" t="n">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="L403" t="n">
         <v>0</v>
@@ -46488,7 +46488,7 @@
         </is>
       </c>
       <c r="K404" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="L404" t="n">
         <v>0</v>
@@ -46540,7 +46540,7 @@
         </is>
       </c>
       <c r="K405" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="L405" t="n">
         <v>0</v>
@@ -46592,7 +46592,7 @@
         </is>
       </c>
       <c r="K406" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="L406" t="n">
         <v>0</v>
@@ -46644,7 +46644,7 @@
         </is>
       </c>
       <c r="K407" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="L407" t="n">
         <v>0</v>
@@ -46696,7 +46696,7 @@
         </is>
       </c>
       <c r="K408" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="L408" t="n">
         <v>0</v>
@@ -46748,7 +46748,7 @@
         </is>
       </c>
       <c r="K409" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="L409" t="n">
         <v>0</v>
@@ -46800,7 +46800,7 @@
         </is>
       </c>
       <c r="K410" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="L410" t="n">
         <v>0</v>
@@ -46852,7 +46852,7 @@
         </is>
       </c>
       <c r="K411" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="L411" t="n">
         <v>0</v>
@@ -46904,7 +46904,7 @@
         </is>
       </c>
       <c r="K412" t="n">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="L412" t="n">
         <v>0</v>
@@ -46956,7 +46956,7 @@
         </is>
       </c>
       <c r="K413" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="L413" t="n">
         <v>0</v>
@@ -47008,7 +47008,7 @@
         </is>
       </c>
       <c r="K414" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="L414" t="n">
         <v>0</v>
@@ -47060,7 +47060,7 @@
         </is>
       </c>
       <c r="K415" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="L415" t="n">
         <v>0</v>
@@ -47112,7 +47112,7 @@
         </is>
       </c>
       <c r="K416" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="L416" t="n">
         <v>0</v>
@@ -47164,7 +47164,7 @@
         </is>
       </c>
       <c r="K417" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="L417" t="n">
         <v>0</v>
@@ -47216,7 +47216,7 @@
         </is>
       </c>
       <c r="K418" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="L418" t="n">
         <v>0</v>
@@ -47268,7 +47268,7 @@
         </is>
       </c>
       <c r="K419" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="L419" t="n">
         <v>0</v>
@@ -47320,7 +47320,7 @@
         </is>
       </c>
       <c r="K420" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="L420" t="n">
         <v>0</v>
@@ -47372,7 +47372,7 @@
         </is>
       </c>
       <c r="K421" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="L421" t="n">
         <v>0</v>
@@ -47424,7 +47424,7 @@
         </is>
       </c>
       <c r="K422" t="n">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L422" t="n">
         <v>0</v>
@@ -47476,7 +47476,7 @@
         </is>
       </c>
       <c r="K423" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="L423" t="n">
         <v>0</v>
@@ -47528,7 +47528,7 @@
         </is>
       </c>
       <c r="K424" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="L424" t="n">
         <v>0</v>
@@ -47580,7 +47580,7 @@
         </is>
       </c>
       <c r="K425" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="L425" t="n">
         <v>0</v>
@@ -47632,7 +47632,7 @@
         </is>
       </c>
       <c r="K426" t="n">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="L426" t="n">
         <v>0</v>
@@ -47684,7 +47684,7 @@
         </is>
       </c>
       <c r="K427" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="L427" t="n">
         <v>0</v>
@@ -47736,7 +47736,7 @@
         </is>
       </c>
       <c r="K428" t="n">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="L428" t="n">
         <v>0</v>
@@ -47788,7 +47788,7 @@
         </is>
       </c>
       <c r="K429" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="L429" t="n">
         <v>0</v>
@@ -47840,7 +47840,7 @@
         </is>
       </c>
       <c r="K430" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="L430" t="n">
         <v>0</v>
@@ -47892,7 +47892,7 @@
         </is>
       </c>
       <c r="K431" t="n">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="L431" t="n">
         <v>0</v>
@@ -47944,7 +47944,7 @@
         </is>
       </c>
       <c r="K432" t="n">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="L432" t="n">
         <v>0</v>
@@ -47996,7 +47996,7 @@
         </is>
       </c>
       <c r="K433" t="n">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="L433" t="n">
         <v>0</v>
@@ -48048,7 +48048,7 @@
         </is>
       </c>
       <c r="K434" t="n">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="L434" t="n">
         <v>0</v>
@@ -48100,7 +48100,7 @@
         </is>
       </c>
       <c r="K435" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="L435" t="n">
         <v>0</v>
@@ -48152,7 +48152,7 @@
         </is>
       </c>
       <c r="K436" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="L436" t="n">
         <v>0</v>
@@ -48204,7 +48204,7 @@
         </is>
       </c>
       <c r="K437" t="n">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="L437" t="n">
         <v>0</v>
@@ -48256,7 +48256,7 @@
         </is>
       </c>
       <c r="K438" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="L438" t="n">
         <v>0</v>
@@ -48308,7 +48308,7 @@
         </is>
       </c>
       <c r="K439" t="n">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="L439" t="n">
         <v>0</v>
@@ -48360,7 +48360,7 @@
         </is>
       </c>
       <c r="K440" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="L440" t="n">
         <v>0</v>
@@ -48412,7 +48412,7 @@
         </is>
       </c>
       <c r="K441" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="L441" t="n">
         <v>0</v>
@@ -48464,7 +48464,7 @@
         </is>
       </c>
       <c r="K442" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="L442" t="n">
         <v>0</v>
@@ -48516,7 +48516,7 @@
         </is>
       </c>
       <c r="K443" t="n">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="L443" t="n">
         <v>0</v>
@@ -48568,7 +48568,7 @@
         </is>
       </c>
       <c r="K444" t="n">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="L444" t="n">
         <v>0</v>
@@ -48620,7 +48620,7 @@
         </is>
       </c>
       <c r="K445" t="n">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="L445" t="n">
         <v>0</v>
@@ -48672,7 +48672,7 @@
         </is>
       </c>
       <c r="K446" t="n">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="L446" t="n">
         <v>0</v>
@@ -48724,7 +48724,7 @@
         </is>
       </c>
       <c r="K447" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="L447" t="n">
         <v>0</v>
@@ -48776,7 +48776,7 @@
         </is>
       </c>
       <c r="K448" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="L448" t="n">
         <v>0</v>
@@ -48828,7 +48828,7 @@
         </is>
       </c>
       <c r="K449" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="L449" t="n">
         <v>0</v>
@@ -48880,7 +48880,7 @@
         </is>
       </c>
       <c r="K450" t="n">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="L450" t="n">
         <v>0</v>
@@ -48932,7 +48932,7 @@
         </is>
       </c>
       <c r="K451" t="n">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="L451" t="n">
         <v>0</v>
@@ -48984,7 +48984,7 @@
         </is>
       </c>
       <c r="K452" t="n">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="L452" t="n">
         <v>0</v>
@@ -49036,7 +49036,7 @@
         </is>
       </c>
       <c r="K453" t="n">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="L453" t="n">
         <v>0</v>
@@ -49088,7 +49088,7 @@
         </is>
       </c>
       <c r="K454" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="L454" t="n">
         <v>0</v>
@@ -49140,7 +49140,7 @@
         </is>
       </c>
       <c r="K455" t="n">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="L455" t="n">
         <v>0</v>
@@ -49192,7 +49192,7 @@
         </is>
       </c>
       <c r="K456" t="n">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="L456" t="n">
         <v>0</v>
@@ -49244,7 +49244,7 @@
         </is>
       </c>
       <c r="K457" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="L457" t="n">
         <v>0</v>
@@ -49296,7 +49296,7 @@
         </is>
       </c>
       <c r="K458" t="n">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="L458" t="n">
         <v>0</v>
@@ -49348,7 +49348,7 @@
         </is>
       </c>
       <c r="K459" t="n">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="L459" t="n">
         <v>0</v>
@@ -49400,7 +49400,7 @@
         </is>
       </c>
       <c r="K460" t="n">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="L460" t="n">
         <v>0</v>
@@ -49452,7 +49452,7 @@
         </is>
       </c>
       <c r="K461" t="n">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="L461" t="n">
         <v>0</v>
@@ -49504,7 +49504,7 @@
         </is>
       </c>
       <c r="K462" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="L462" t="n">
         <v>0</v>
@@ -49556,7 +49556,7 @@
         </is>
       </c>
       <c r="K463" t="n">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="L463" t="n">
         <v>0</v>
@@ -49608,7 +49608,7 @@
         </is>
       </c>
       <c r="K464" t="n">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="L464" t="n">
         <v>0</v>
@@ -49660,7 +49660,7 @@
         </is>
       </c>
       <c r="K465" t="n">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="L465" t="n">
         <v>0</v>
@@ -49712,7 +49712,7 @@
         </is>
       </c>
       <c r="K466" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="L466" t="n">
         <v>0</v>
@@ -49764,7 +49764,7 @@
         </is>
       </c>
       <c r="K467" t="n">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="L467" t="n">
         <v>0</v>
@@ -49816,7 +49816,7 @@
         </is>
       </c>
       <c r="K468" t="n">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="L468" t="n">
         <v>0</v>
@@ -49868,7 +49868,7 @@
         </is>
       </c>
       <c r="K469" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="L469" t="n">
         <v>0</v>
@@ -49920,7 +49920,7 @@
         </is>
       </c>
       <c r="K470" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="L470" t="n">
         <v>0</v>
@@ -49972,7 +49972,7 @@
         </is>
       </c>
       <c r="K471" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="L471" t="n">
         <v>0</v>
@@ -50024,7 +50024,7 @@
         </is>
       </c>
       <c r="K472" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="L472" t="n">
         <v>0</v>
@@ -50076,7 +50076,7 @@
         </is>
       </c>
       <c r="K473" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="L473" t="n">
         <v>0</v>
@@ -50128,7 +50128,7 @@
         </is>
       </c>
       <c r="K474" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="L474" t="n">
         <v>0</v>
@@ -50180,7 +50180,7 @@
         </is>
       </c>
       <c r="K475" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="L475" t="n">
         <v>0</v>
@@ -50232,7 +50232,7 @@
         </is>
       </c>
       <c r="K476" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="L476" t="n">
         <v>0</v>
@@ -50284,7 +50284,7 @@
         </is>
       </c>
       <c r="K477" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="L477" t="n">
         <v>0</v>
@@ -50336,7 +50336,7 @@
         </is>
       </c>
       <c r="K478" t="n">
-        <v>34</v>
+        <v>107</v>
       </c>
       <c r="L478" t="n">
         <v>0</v>
@@ -50388,7 +50388,7 @@
         </is>
       </c>
       <c r="K479" t="n">
-        <v>34</v>
+        <v>104</v>
       </c>
       <c r="L479" t="n">
         <v>0</v>
@@ -50440,7 +50440,7 @@
         </is>
       </c>
       <c r="K480" t="n">
-        <v>34</v>
+        <v>104</v>
       </c>
       <c r="L480" t="n">
         <v>0</v>
@@ -50492,7 +50492,7 @@
         </is>
       </c>
       <c r="K481" t="n">
-        <v>35</v>
+        <v>108</v>
       </c>
       <c r="L481" t="n">
         <v>0</v>
@@ -50544,7 +50544,7 @@
         </is>
       </c>
       <c r="K482" t="n">
-        <v>36</v>
+        <v>113</v>
       </c>
       <c r="L482" t="n">
         <v>0</v>
@@ -50596,7 +50596,7 @@
         </is>
       </c>
       <c r="K483" t="n">
-        <v>35</v>
+        <v>114</v>
       </c>
       <c r="L483" t="n">
         <v>0</v>
@@ -50648,7 +50648,7 @@
         </is>
       </c>
       <c r="K484" t="n">
-        <v>34</v>
+        <v>131</v>
       </c>
       <c r="L484" t="n">
         <v>0</v>
@@ -50700,7 +50700,7 @@
         </is>
       </c>
       <c r="K485" t="n">
-        <v>34</v>
+        <v>127</v>
       </c>
       <c r="L485" t="n">
         <v>0</v>
@@ -50752,7 +50752,7 @@
         </is>
       </c>
       <c r="K486" t="n">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="L486" t="n">
         <v>0</v>
@@ -50804,7 +50804,7 @@
         </is>
       </c>
       <c r="K487" t="n">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="L487" t="n">
         <v>0</v>
@@ -50856,7 +50856,7 @@
         </is>
       </c>
       <c r="K488" t="n">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="L488" t="n">
         <v>0</v>
@@ -50908,7 +50908,7 @@
         </is>
       </c>
       <c r="K489" t="n">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="L489" t="n">
         <v>0</v>
@@ -50960,7 +50960,7 @@
         </is>
       </c>
       <c r="K490" t="n">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="L490" t="n">
         <v>0</v>
@@ -51012,7 +51012,7 @@
         </is>
       </c>
       <c r="K491" t="n">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="L491" t="n">
         <v>0</v>
@@ -51064,7 +51064,7 @@
         </is>
       </c>
       <c r="K492" t="n">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="L492" t="n">
         <v>0</v>
@@ -51116,7 +51116,7 @@
         </is>
       </c>
       <c r="K493" t="n">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="L493" t="n">
         <v>0</v>
@@ -51168,7 +51168,7 @@
         </is>
       </c>
       <c r="K494" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="L494" t="n">
         <v>0</v>
@@ -51220,7 +51220,7 @@
         </is>
       </c>
       <c r="K495" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="L495" t="n">
         <v>0</v>
@@ -51272,7 +51272,7 @@
         </is>
       </c>
       <c r="K496" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="L496" t="n">
         <v>0</v>
@@ -51324,7 +51324,7 @@
         </is>
       </c>
       <c r="K497" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="L497" t="n">
         <v>0</v>
@@ -51376,7 +51376,7 @@
         </is>
       </c>
       <c r="K498" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="L498" t="n">
         <v>0</v>
@@ -51428,7 +51428,7 @@
         </is>
       </c>
       <c r="K499" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="L499" t="n">
         <v>0</v>
@@ -51480,7 +51480,7 @@
         </is>
       </c>
       <c r="K500" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="L500" t="n">
         <v>0</v>
@@ -51532,7 +51532,7 @@
         </is>
       </c>
       <c r="K501" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="L501" t="n">
         <v>0</v>
@@ -51584,7 +51584,7 @@
         </is>
       </c>
       <c r="K502" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="L502" t="n">
         <v>0</v>
@@ -51636,7 +51636,7 @@
         </is>
       </c>
       <c r="K503" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="L503" t="n">
         <v>0</v>
@@ -51688,7 +51688,7 @@
         </is>
       </c>
       <c r="K504" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="L504" t="n">
         <v>0</v>
@@ -51740,7 +51740,7 @@
         </is>
       </c>
       <c r="K505" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="L505" t="n">
         <v>0</v>
@@ -51792,7 +51792,7 @@
         </is>
       </c>
       <c r="K506" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="L506" t="n">
         <v>0</v>
@@ -51844,7 +51844,7 @@
         </is>
       </c>
       <c r="K507" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="L507" t="n">
         <v>0</v>
@@ -51896,7 +51896,7 @@
         </is>
       </c>
       <c r="K508" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="L508" t="n">
         <v>0</v>
@@ -51948,7 +51948,7 @@
         </is>
       </c>
       <c r="K509" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="L509" t="n">
         <v>0</v>
@@ -52000,7 +52000,7 @@
         </is>
       </c>
       <c r="K510" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="L510" t="n">
         <v>0</v>
@@ -52052,7 +52052,7 @@
         </is>
       </c>
       <c r="K511" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="L511" t="n">
         <v>0</v>
@@ -52104,7 +52104,7 @@
         </is>
       </c>
       <c r="K512" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="L512" t="n">
         <v>0</v>
@@ -52156,7 +52156,7 @@
         </is>
       </c>
       <c r="K513" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="L513" t="n">
         <v>0</v>
@@ -52208,7 +52208,7 @@
         </is>
       </c>
       <c r="K514" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="L514" t="n">
         <v>0</v>
@@ -52260,7 +52260,7 @@
         </is>
       </c>
       <c r="K515" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="L515" t="n">
         <v>0</v>
@@ -52312,7 +52312,7 @@
         </is>
       </c>
       <c r="K516" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="L516" t="n">
         <v>0</v>
@@ -52364,7 +52364,7 @@
         </is>
       </c>
       <c r="K517" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="L517" t="n">
         <v>0</v>
@@ -52416,7 +52416,7 @@
         </is>
       </c>
       <c r="K518" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="L518" t="n">
         <v>0</v>
@@ -52468,7 +52468,7 @@
         </is>
       </c>
       <c r="K519" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="L519" t="n">
         <v>0</v>
@@ -52520,7 +52520,7 @@
         </is>
       </c>
       <c r="K520" t="n">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="L520" t="n">
         <v>0</v>
@@ -52572,7 +52572,7 @@
         </is>
       </c>
       <c r="K521" t="n">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="L521" t="n">
         <v>0</v>
@@ -52624,7 +52624,7 @@
         </is>
       </c>
       <c r="K522" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="L522" t="n">
         <v>0</v>
@@ -52676,7 +52676,7 @@
         </is>
       </c>
       <c r="K523" t="n">
-        <v>35</v>
+        <v>88</v>
       </c>
       <c r="L523" t="n">
         <v>0</v>
@@ -52728,7 +52728,7 @@
         </is>
       </c>
       <c r="K524" t="n">
-        <v>35</v>
+        <v>88</v>
       </c>
       <c r="L524" t="n">
         <v>0</v>
@@ -52780,7 +52780,7 @@
         </is>
       </c>
       <c r="K525" t="n">
-        <v>35</v>
+        <v>93</v>
       </c>
       <c r="L525" t="n">
         <v>0</v>
@@ -52832,7 +52832,7 @@
         </is>
       </c>
       <c r="K526" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="L526" t="n">
         <v>0</v>
@@ -52884,7 +52884,7 @@
         </is>
       </c>
       <c r="K527" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="L527" t="n">
         <v>0</v>
@@ -52936,7 +52936,7 @@
         </is>
       </c>
       <c r="K528" t="n">
-        <v>36</v>
+        <v>92</v>
       </c>
       <c r="L528" t="n">
         <v>0</v>
@@ -52988,7 +52988,7 @@
         </is>
       </c>
       <c r="K529" t="n">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="L529" t="n">
         <v>0</v>
@@ -53040,7 +53040,7 @@
         </is>
       </c>
       <c r="K530" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="L530" t="n">
         <v>0</v>
@@ -53092,7 +53092,7 @@
         </is>
       </c>
       <c r="K531" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="L531" t="n">
         <v>0</v>
@@ -53144,7 +53144,7 @@
         </is>
       </c>
       <c r="K532" t="n">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="L532" t="n">
         <v>0</v>
@@ -53196,7 +53196,7 @@
         </is>
       </c>
       <c r="K533" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="L533" t="n">
         <v>0</v>
@@ -53248,7 +53248,7 @@
         </is>
       </c>
       <c r="K534" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="L534" t="n">
         <v>0</v>
@@ -53300,7 +53300,7 @@
         </is>
       </c>
       <c r="K535" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="L535" t="n">
         <v>0</v>
@@ -53352,7 +53352,7 @@
         </is>
       </c>
       <c r="K536" t="n">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="L536" t="n">
         <v>0</v>
@@ -53404,7 +53404,7 @@
         </is>
       </c>
       <c r="K537" t="n">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="L537" t="n">
         <v>0</v>
@@ -53456,7 +53456,7 @@
         </is>
       </c>
       <c r="K538" t="n">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="L538" t="n">
         <v>0</v>
@@ -53508,7 +53508,7 @@
         </is>
       </c>
       <c r="K539" t="n">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="L539" t="n">
         <v>0</v>
@@ -53560,7 +53560,7 @@
         </is>
       </c>
       <c r="K540" t="n">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="L540" t="n">
         <v>0</v>
@@ -53612,7 +53612,7 @@
         </is>
       </c>
       <c r="K541" t="n">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="L541" t="n">
         <v>0</v>
@@ -53664,7 +53664,7 @@
         </is>
       </c>
       <c r="K542" t="n">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="L542" t="n">
         <v>0</v>
@@ -53716,7 +53716,7 @@
         </is>
       </c>
       <c r="K543" t="n">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="L543" t="n">
         <v>0</v>
@@ -53768,7 +53768,7 @@
         </is>
       </c>
       <c r="K544" t="n">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="L544" t="n">
         <v>0</v>
@@ -53820,7 +53820,7 @@
         </is>
       </c>
       <c r="K545" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="L545" t="n">
         <v>0</v>
@@ -53872,7 +53872,7 @@
         </is>
       </c>
       <c r="K546" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="L546" t="n">
         <v>0</v>
@@ -53924,7 +53924,7 @@
         </is>
       </c>
       <c r="K547" t="n">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="L547" t="n">
         <v>0</v>
@@ -53976,7 +53976,7 @@
         </is>
       </c>
       <c r="K548" t="n">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="L548" t="n">
         <v>0</v>
@@ -54028,7 +54028,7 @@
         </is>
       </c>
       <c r="K549" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="L549" t="n">
         <v>0</v>
@@ -54080,7 +54080,7 @@
         </is>
       </c>
       <c r="K550" t="n">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="L550" t="n">
         <v>0</v>
@@ -54132,7 +54132,7 @@
         </is>
       </c>
       <c r="K551" t="n">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="L551" t="n">
         <v>0</v>
@@ -54184,7 +54184,7 @@
         </is>
       </c>
       <c r="K552" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="L552" t="n">
         <v>0</v>
@@ -54236,7 +54236,7 @@
         </is>
       </c>
       <c r="K553" t="n">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="L553" t="n">
         <v>0</v>
@@ -54288,7 +54288,7 @@
         </is>
       </c>
       <c r="K554" t="n">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="L554" t="n">
         <v>0</v>
@@ -54340,7 +54340,7 @@
         </is>
       </c>
       <c r="K555" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="L555" t="n">
         <v>0</v>
@@ -54392,7 +54392,7 @@
         </is>
       </c>
       <c r="K556" t="n">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="L556" t="n">
         <v>0</v>
@@ -54444,7 +54444,7 @@
         </is>
       </c>
       <c r="K557" t="n">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="L557" t="n">
         <v>0</v>
@@ -54496,7 +54496,7 @@
         </is>
       </c>
       <c r="K558" t="n">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="L558" t="n">
         <v>0</v>
@@ -54548,7 +54548,7 @@
         </is>
       </c>
       <c r="K559" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="L559" t="n">
         <v>0</v>
@@ -54600,7 +54600,7 @@
         </is>
       </c>
       <c r="K560" t="n">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="L560" t="n">
         <v>0</v>
@@ -54652,7 +54652,7 @@
         </is>
       </c>
       <c r="K561" t="n">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="L561" t="n">
         <v>0</v>
@@ -54704,7 +54704,7 @@
         </is>
       </c>
       <c r="K562" t="n">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="L562" t="n">
         <v>0</v>
@@ -54756,7 +54756,7 @@
         </is>
       </c>
       <c r="K563" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="L563" t="n">
         <v>0</v>
@@ -54808,7 +54808,7 @@
         </is>
       </c>
       <c r="K564" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="L564" t="n">
         <v>0</v>
@@ -54860,7 +54860,7 @@
         </is>
       </c>
       <c r="K565" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="L565" t="n">
         <v>0</v>
@@ -54912,7 +54912,7 @@
         </is>
       </c>
       <c r="K566" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L566" t="n">
         <v>0</v>
@@ -54964,7 +54964,7 @@
         </is>
       </c>
       <c r="K567" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="L567" t="n">
         <v>0</v>
@@ -55016,7 +55016,7 @@
         </is>
       </c>
       <c r="K568" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="L568" t="n">
         <v>0</v>
@@ -55068,7 +55068,7 @@
         </is>
       </c>
       <c r="K569" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L569" t="n">
         <v>0</v>
@@ -55120,7 +55120,7 @@
         </is>
       </c>
       <c r="K570" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L570" t="n">
         <v>0</v>
@@ -55172,7 +55172,7 @@
         </is>
       </c>
       <c r="K571" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="L571" t="n">
         <v>0</v>
@@ -55224,7 +55224,7 @@
         </is>
       </c>
       <c r="K572" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="L572" t="n">
         <v>0</v>
@@ -55276,7 +55276,7 @@
         </is>
       </c>
       <c r="K573" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L573" t="n">
         <v>0</v>
@@ -55328,7 +55328,7 @@
         </is>
       </c>
       <c r="K574" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="L574" t="n">
         <v>0</v>
@@ -55380,7 +55380,7 @@
         </is>
       </c>
       <c r="K575" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="L575" t="n">
         <v>0</v>
@@ -55432,7 +55432,7 @@
         </is>
       </c>
       <c r="K576" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="L576" t="n">
         <v>0</v>
@@ -55484,7 +55484,7 @@
         </is>
       </c>
       <c r="K577" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L577" t="n">
         <v>0</v>
@@ -55536,7 +55536,7 @@
         </is>
       </c>
       <c r="K578" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L578" t="n">
         <v>0</v>
@@ -55588,7 +55588,7 @@
         </is>
       </c>
       <c r="K579" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="L579" t="n">
         <v>0</v>
@@ -55640,7 +55640,7 @@
         </is>
       </c>
       <c r="K580" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="L580" t="n">
         <v>0</v>
@@ -55692,7 +55692,7 @@
         </is>
       </c>
       <c r="K581" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L581" t="n">
         <v>0</v>
@@ -55744,7 +55744,7 @@
         </is>
       </c>
       <c r="K582" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L582" t="n">
         <v>0</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="K583" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="L583" t="n">
         <v>0</v>
@@ -55848,7 +55848,7 @@
         </is>
       </c>
       <c r="K584" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="L584" t="n">
         <v>0</v>
@@ -55900,7 +55900,7 @@
         </is>
       </c>
       <c r="K585" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L585" t="n">
         <v>0</v>
@@ -55952,7 +55952,7 @@
         </is>
       </c>
       <c r="K586" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L586" t="n">
         <v>0</v>
@@ -56004,7 +56004,7 @@
         </is>
       </c>
       <c r="K587" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L587" t="n">
         <v>0</v>
@@ -56056,7 +56056,7 @@
         </is>
       </c>
       <c r="K588" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L588" t="n">
         <v>0</v>
@@ -56108,7 +56108,7 @@
         </is>
       </c>
       <c r="K589" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="L589" t="n">
         <v>0</v>
@@ -56160,7 +56160,7 @@
         </is>
       </c>
       <c r="K590" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L590" t="n">
         <v>0</v>
@@ -56212,7 +56212,7 @@
         </is>
       </c>
       <c r="K591" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="L591" t="n">
         <v>0</v>
@@ -56264,7 +56264,7 @@
         </is>
       </c>
       <c r="K592" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="L592" t="n">
         <v>0</v>
@@ -56316,7 +56316,7 @@
         </is>
       </c>
       <c r="K593" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="L593" t="n">
         <v>0</v>
@@ -56368,7 +56368,7 @@
         </is>
       </c>
       <c r="K594" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L594" t="n">
         <v>0</v>
@@ -56420,7 +56420,7 @@
         </is>
       </c>
       <c r="K595" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="L595" t="n">
         <v>0</v>
@@ -56472,7 +56472,7 @@
         </is>
       </c>
       <c r="K596" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="L596" t="n">
         <v>0</v>
@@ -56524,7 +56524,7 @@
         </is>
       </c>
       <c r="K597" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="L597" t="n">
         <v>0</v>
@@ -56576,7 +56576,7 @@
         </is>
       </c>
       <c r="K598" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="L598" t="n">
         <v>0</v>
@@ -56628,7 +56628,7 @@
         </is>
       </c>
       <c r="K599" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="L599" t="n">
         <v>0</v>
@@ -56680,7 +56680,7 @@
         </is>
       </c>
       <c r="K600" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L600" t="n">
         <v>0</v>
@@ -56732,7 +56732,7 @@
         </is>
       </c>
       <c r="K601" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="L601" t="n">
         <v>0</v>
@@ -56784,7 +56784,7 @@
         </is>
       </c>
       <c r="K602" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="L602" t="n">
         <v>0</v>
@@ -56836,7 +56836,7 @@
         </is>
       </c>
       <c r="K603" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="L603" t="n">
         <v>0</v>
@@ -56888,7 +56888,7 @@
         </is>
       </c>
       <c r="K604" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="L604" t="n">
         <v>0</v>
@@ -56940,7 +56940,7 @@
         </is>
       </c>
       <c r="K605" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="L605" t="n">
         <v>0</v>
@@ -56992,7 +56992,7 @@
         </is>
       </c>
       <c r="K606" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="L606" t="n">
         <v>0</v>
@@ -57044,7 +57044,7 @@
         </is>
       </c>
       <c r="K607" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="L607" t="n">
         <v>0</v>
@@ -57096,7 +57096,7 @@
         </is>
       </c>
       <c r="K608" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="L608" t="n">
         <v>0</v>
@@ -57148,7 +57148,7 @@
         </is>
       </c>
       <c r="K609" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L609" t="n">
         <v>0</v>
@@ -57200,7 +57200,7 @@
         </is>
       </c>
       <c r="K610" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="L610" t="n">
         <v>0</v>
@@ -57252,7 +57252,7 @@
         </is>
       </c>
       <c r="K611" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L611" t="n">
         <v>0</v>
@@ -57304,7 +57304,7 @@
         </is>
       </c>
       <c r="K612" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L612" t="n">
         <v>0</v>
@@ -57356,7 +57356,7 @@
         </is>
       </c>
       <c r="K613" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L613" t="n">
         <v>0</v>
@@ -57408,7 +57408,7 @@
         </is>
       </c>
       <c r="K614" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L614" t="n">
         <v>0</v>
@@ -57460,7 +57460,7 @@
         </is>
       </c>
       <c r="K615" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="L615" t="n">
         <v>0</v>
@@ -57512,7 +57512,7 @@
         </is>
       </c>
       <c r="K616" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L616" t="n">
         <v>0</v>
@@ -57564,7 +57564,7 @@
         </is>
       </c>
       <c r="K617" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L617" t="n">
         <v>0</v>
@@ -57616,7 +57616,7 @@
         </is>
       </c>
       <c r="K618" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L618" t="n">
         <v>0</v>
@@ -57668,7 +57668,7 @@
         </is>
       </c>
       <c r="K619" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L619" t="n">
         <v>0</v>
@@ -57720,7 +57720,7 @@
         </is>
       </c>
       <c r="K620" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L620" t="n">
         <v>0</v>
@@ -57772,7 +57772,7 @@
         </is>
       </c>
       <c r="K621" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L621" t="n">
         <v>0</v>
@@ -57824,7 +57824,7 @@
         </is>
       </c>
       <c r="K622" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L622" t="n">
         <v>0</v>
@@ -57876,7 +57876,7 @@
         </is>
       </c>
       <c r="K623" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L623" t="n">
         <v>0</v>
@@ -57928,7 +57928,7 @@
         </is>
       </c>
       <c r="K624" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L624" t="n">
         <v>0</v>
@@ -57980,7 +57980,7 @@
         </is>
       </c>
       <c r="K625" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="L625" t="n">
         <v>0</v>
@@ -58032,7 +58032,7 @@
         </is>
       </c>
       <c r="K626" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L626" t="n">
         <v>0</v>
@@ -58084,7 +58084,7 @@
         </is>
       </c>
       <c r="K627" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L627" t="n">
         <v>0</v>
@@ -58136,7 +58136,7 @@
         </is>
       </c>
       <c r="K628" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="L628" t="n">
         <v>0</v>
@@ -58188,7 +58188,7 @@
         </is>
       </c>
       <c r="K629" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="L629" t="n">
         <v>0</v>
@@ -58240,7 +58240,7 @@
         </is>
       </c>
       <c r="K630" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="L630" t="n">
         <v>0</v>
@@ -58292,7 +58292,7 @@
         </is>
       </c>
       <c r="K631" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="L631" t="n">
         <v>0</v>
@@ -58344,7 +58344,7 @@
         </is>
       </c>
       <c r="K632" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="L632" t="n">
         <v>0</v>
@@ -58396,7 +58396,7 @@
         </is>
       </c>
       <c r="K633" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="L633" t="n">
         <v>0</v>
@@ -58448,7 +58448,7 @@
         </is>
       </c>
       <c r="K634" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L634" t="n">
         <v>0</v>
@@ -58500,7 +58500,7 @@
         </is>
       </c>
       <c r="K635" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="L635" t="n">
         <v>0</v>
@@ -58552,7 +58552,7 @@
         </is>
       </c>
       <c r="K636" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="L636" t="n">
         <v>0</v>
@@ -58604,7 +58604,7 @@
         </is>
       </c>
       <c r="K637" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L637" t="n">
         <v>0</v>
@@ -58656,7 +58656,7 @@
         </is>
       </c>
       <c r="K638" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="L638" t="n">
         <v>0</v>
@@ -58760,7 +58760,7 @@
         </is>
       </c>
       <c r="K640" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L640" t="n">
         <v>0</v>
@@ -58812,7 +58812,7 @@
         </is>
       </c>
       <c r="K641" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L641" t="n">
         <v>0</v>
@@ -58864,7 +58864,7 @@
         </is>
       </c>
       <c r="K642" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L642" t="n">
         <v>0</v>
@@ -58916,7 +58916,7 @@
         </is>
       </c>
       <c r="K643" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="L643" t="n">
         <v>0</v>
@@ -58968,7 +58968,7 @@
         </is>
       </c>
       <c r="K644" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L644" t="n">
         <v>0</v>
@@ -59020,7 +59020,7 @@
         </is>
       </c>
       <c r="K645" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L645" t="n">
         <v>0</v>
@@ -59072,7 +59072,7 @@
         </is>
       </c>
       <c r="K646" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L646" t="n">
         <v>0</v>
@@ -59124,7 +59124,7 @@
         </is>
       </c>
       <c r="K647" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L647" t="n">
         <v>0</v>
@@ -59176,7 +59176,7 @@
         </is>
       </c>
       <c r="K648" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="L648" t="n">
         <v>0</v>
@@ -59228,7 +59228,7 @@
         </is>
       </c>
       <c r="K649" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L649" t="n">
         <v>0</v>
@@ -59332,7 +59332,7 @@
         </is>
       </c>
       <c r="K651" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L651" t="n">
         <v>0</v>
@@ -59384,7 +59384,7 @@
         </is>
       </c>
       <c r="K652" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L652" t="n">
         <v>0</v>
@@ -59436,7 +59436,7 @@
         </is>
       </c>
       <c r="K653" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L653" t="n">
         <v>0</v>
@@ -59488,7 +59488,7 @@
         </is>
       </c>
       <c r="K654" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L654" t="n">
         <v>0</v>
@@ -59644,7 +59644,7 @@
         </is>
       </c>
       <c r="K657" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L657" t="n">
         <v>0</v>
@@ -59696,7 +59696,7 @@
         </is>
       </c>
       <c r="K658" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L658" t="n">
         <v>0</v>
@@ -59748,7 +59748,7 @@
         </is>
       </c>
       <c r="K659" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L659" t="n">
         <v>0</v>
@@ -59800,7 +59800,7 @@
         </is>
       </c>
       <c r="K660" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L660" t="n">
         <v>0</v>
@@ -59852,7 +59852,7 @@
         </is>
       </c>
       <c r="K661" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L661" t="n">
         <v>0</v>
@@ -59904,7 +59904,7 @@
         </is>
       </c>
       <c r="K662" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="L662" t="n">
         <v>0</v>
@@ -59956,7 +59956,7 @@
         </is>
       </c>
       <c r="K663" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="L663" t="n">
         <v>0</v>
@@ -60008,7 +60008,7 @@
         </is>
       </c>
       <c r="K664" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L664" t="n">
         <v>0</v>
@@ -60060,7 +60060,7 @@
         </is>
       </c>
       <c r="K665" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L665" t="n">
         <v>0</v>
@@ -60164,7 +60164,7 @@
         </is>
       </c>
       <c r="K667" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="L667" t="n">
         <v>0</v>
@@ -60216,7 +60216,7 @@
         </is>
       </c>
       <c r="K668" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L668" t="n">
         <v>0</v>
@@ -60268,7 +60268,7 @@
         </is>
       </c>
       <c r="K669" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L669" t="n">
         <v>0</v>
@@ -60320,7 +60320,7 @@
         </is>
       </c>
       <c r="K670" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L670" t="n">
         <v>0</v>
@@ -60372,7 +60372,7 @@
         </is>
       </c>
       <c r="K671" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L671" t="n">
         <v>0</v>
@@ -60424,7 +60424,7 @@
         </is>
       </c>
       <c r="K672" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L672" t="n">
         <v>0</v>
@@ -60476,7 +60476,7 @@
         </is>
       </c>
       <c r="K673" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L673" t="n">
         <v>0</v>
@@ -60528,7 +60528,7 @@
         </is>
       </c>
       <c r="K674" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L674" t="n">
         <v>0</v>
@@ -60580,7 +60580,7 @@
         </is>
       </c>
       <c r="K675" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="L675" t="n">
         <v>0</v>
@@ -60632,7 +60632,7 @@
         </is>
       </c>
       <c r="K676" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="L676" t="n">
         <v>0</v>
@@ -60684,7 +60684,7 @@
         </is>
       </c>
       <c r="K677" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L677" t="n">
         <v>0</v>
@@ -60736,7 +60736,7 @@
         </is>
       </c>
       <c r="K678" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L678" t="n">
         <v>0</v>
@@ -60788,7 +60788,7 @@
         </is>
       </c>
       <c r="K679" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L679" t="n">
         <v>0</v>
@@ -60840,7 +60840,7 @@
         </is>
       </c>
       <c r="K680" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L680" t="n">
         <v>0</v>
@@ -60892,7 +60892,7 @@
         </is>
       </c>
       <c r="K681" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L681" t="n">
         <v>0</v>
@@ -60944,7 +60944,7 @@
         </is>
       </c>
       <c r="K682" t="n">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="L682" t="n">
         <v>0</v>
@@ -60996,7 +60996,7 @@
         </is>
       </c>
       <c r="K683" t="n">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="L683" t="n">
         <v>0</v>
@@ -61048,7 +61048,7 @@
         </is>
       </c>
       <c r="K684" t="n">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="L684" t="n">
         <v>0</v>
@@ -61100,7 +61100,7 @@
         </is>
       </c>
       <c r="K685" t="n">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="L685" t="n">
         <v>0</v>
@@ -61152,7 +61152,7 @@
         </is>
       </c>
       <c r="K686" t="n">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="L686" t="n">
         <v>0</v>
@@ -61204,7 +61204,7 @@
         </is>
       </c>
       <c r="K687" t="n">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="L687" t="n">
         <v>0</v>
@@ -61256,7 +61256,7 @@
         </is>
       </c>
       <c r="K688" t="n">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="L688" t="n">
         <v>0</v>
@@ -61308,7 +61308,7 @@
         </is>
       </c>
       <c r="K689" t="n">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="L689" t="n">
         <v>0</v>
@@ -61360,7 +61360,7 @@
         </is>
       </c>
       <c r="K690" t="n">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="L690" t="n">
         <v>0</v>
@@ -61412,7 +61412,7 @@
         </is>
       </c>
       <c r="K691" t="n">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="L691" t="n">
         <v>0</v>
@@ -61464,7 +61464,7 @@
         </is>
       </c>
       <c r="K692" t="n">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="L692" t="n">
         <v>0</v>
@@ -61516,7 +61516,7 @@
         </is>
       </c>
       <c r="K693" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L693" t="n">
         <v>0</v>
@@ -61568,7 +61568,7 @@
         </is>
       </c>
       <c r="K694" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="L694" t="n">
         <v>0</v>
@@ -61620,7 +61620,7 @@
         </is>
       </c>
       <c r="K695" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="L695" t="n">
         <v>0</v>
@@ -61672,7 +61672,7 @@
         </is>
       </c>
       <c r="K696" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="L696" t="n">
         <v>0</v>
@@ -61724,7 +61724,7 @@
         </is>
       </c>
       <c r="K697" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="L697" t="n">
         <v>0</v>
@@ -61776,7 +61776,7 @@
         </is>
       </c>
       <c r="K698" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="L698" t="n">
         <v>0</v>
@@ -61828,7 +61828,7 @@
         </is>
       </c>
       <c r="K699" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="L699" t="n">
         <v>0</v>
@@ -61880,7 +61880,7 @@
         </is>
       </c>
       <c r="K700" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="L700" t="n">
         <v>0</v>
@@ -61932,7 +61932,7 @@
         </is>
       </c>
       <c r="K701" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L701" t="n">
         <v>0</v>
@@ -61984,7 +61984,7 @@
         </is>
       </c>
       <c r="K702" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="L702" t="n">
         <v>0</v>
@@ -62036,7 +62036,7 @@
         </is>
       </c>
       <c r="K703" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="L703" t="n">
         <v>0</v>
@@ -62088,7 +62088,7 @@
         </is>
       </c>
       <c r="K704" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="L704" t="n">
         <v>0</v>
@@ -62140,7 +62140,7 @@
         </is>
       </c>
       <c r="K705" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L705" t="n">
         <v>0</v>
@@ -62192,7 +62192,7 @@
         </is>
       </c>
       <c r="K706" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L706" t="n">
         <v>0</v>
@@ -62244,7 +62244,7 @@
         </is>
       </c>
       <c r="K707" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="L707" t="n">
         <v>0</v>
@@ -62296,7 +62296,7 @@
         </is>
       </c>
       <c r="K708" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L708" t="n">
         <v>0</v>
@@ -62348,7 +62348,7 @@
         </is>
       </c>
       <c r="K709" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L709" t="n">
         <v>0</v>
@@ -62400,7 +62400,7 @@
         </is>
       </c>
       <c r="K710" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="L710" t="n">
         <v>0</v>
@@ -62452,7 +62452,7 @@
         </is>
       </c>
       <c r="K711" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="L711" t="n">
         <v>0</v>
@@ -62556,7 +62556,7 @@
         </is>
       </c>
       <c r="K713" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L713" t="n">
         <v>0</v>
@@ -62608,7 +62608,7 @@
         </is>
       </c>
       <c r="K714" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L714" t="n">
         <v>0</v>
@@ -62660,7 +62660,7 @@
         </is>
       </c>
       <c r="K715" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L715" t="n">
         <v>0</v>
@@ -62712,7 +62712,7 @@
         </is>
       </c>
       <c r="K716" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L716" t="n">
         <v>0</v>
@@ -62764,7 +62764,7 @@
         </is>
       </c>
       <c r="K717" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="L717" t="n">
         <v>0</v>
@@ -62816,7 +62816,7 @@
         </is>
       </c>
       <c r="K718" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L718" t="n">
         <v>0</v>
@@ -62868,7 +62868,7 @@
         </is>
       </c>
       <c r="K719" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L719" t="n">
         <v>0</v>
@@ -62920,7 +62920,7 @@
         </is>
       </c>
       <c r="K720" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L720" t="n">
         <v>0</v>
@@ -62972,7 +62972,7 @@
         </is>
       </c>
       <c r="K721" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L721" t="n">
         <v>0</v>
@@ -63024,7 +63024,7 @@
         </is>
       </c>
       <c r="K722" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L722" t="n">
         <v>0</v>
@@ -63076,7 +63076,7 @@
         </is>
       </c>
       <c r="K723" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L723" t="n">
         <v>0</v>
@@ -63128,7 +63128,7 @@
         </is>
       </c>
       <c r="K724" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L724" t="n">
         <v>0</v>
@@ -63180,7 +63180,7 @@
         </is>
       </c>
       <c r="K725" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L725" t="n">
         <v>0</v>
@@ -63232,7 +63232,7 @@
         </is>
       </c>
       <c r="K726" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L726" t="n">
         <v>0</v>
@@ -63284,7 +63284,7 @@
         </is>
       </c>
       <c r="K727" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L727" t="n">
         <v>0</v>
@@ -63336,7 +63336,7 @@
         </is>
       </c>
       <c r="K728" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L728" t="n">
         <v>0</v>
@@ -63388,7 +63388,7 @@
         </is>
       </c>
       <c r="K729" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L729" t="n">
         <v>0</v>
@@ -63440,7 +63440,7 @@
         </is>
       </c>
       <c r="K730" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L730" t="n">
         <v>0</v>
@@ -63492,7 +63492,7 @@
         </is>
       </c>
       <c r="K731" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L731" t="n">
         <v>0</v>
@@ -63596,7 +63596,7 @@
         </is>
       </c>
       <c r="K733" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L733" t="n">
         <v>0</v>
@@ -63648,7 +63648,7 @@
         </is>
       </c>
       <c r="K734" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="L734" t="n">
         <v>0</v>
@@ -63700,7 +63700,7 @@
         </is>
       </c>
       <c r="K735" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L735" t="n">
         <v>0</v>
@@ -63752,7 +63752,7 @@
         </is>
       </c>
       <c r="K736" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L736" t="n">
         <v>0</v>
@@ -63804,7 +63804,7 @@
         </is>
       </c>
       <c r="K737" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L737" t="n">
         <v>0</v>
@@ -63856,7 +63856,7 @@
         </is>
       </c>
       <c r="K738" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="L738" t="n">
         <v>0</v>
@@ -63908,7 +63908,7 @@
         </is>
       </c>
       <c r="K739" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="L739" t="n">
         <v>0</v>
@@ -63960,7 +63960,7 @@
         </is>
       </c>
       <c r="K740" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L740" t="n">
         <v>0</v>
@@ -64012,7 +64012,7 @@
         </is>
       </c>
       <c r="K741" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="L741" t="n">
         <v>0</v>
@@ -64064,7 +64064,7 @@
         </is>
       </c>
       <c r="K742" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="L742" t="n">
         <v>0</v>
@@ -64116,7 +64116,7 @@
         </is>
       </c>
       <c r="K743" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="L743" t="n">
         <v>0</v>
@@ -64168,7 +64168,7 @@
         </is>
       </c>
       <c r="K744" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="L744" t="n">
         <v>0</v>
@@ -64220,7 +64220,7 @@
         </is>
       </c>
       <c r="K745" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="L745" t="n">
         <v>0</v>
@@ -64272,7 +64272,7 @@
         </is>
       </c>
       <c r="K746" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="L746" t="n">
         <v>0</v>
@@ -64324,7 +64324,7 @@
         </is>
       </c>
       <c r="K747" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="L747" t="n">
         <v>0</v>
@@ -64376,7 +64376,7 @@
         </is>
       </c>
       <c r="K748" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L748" t="n">
         <v>0</v>
@@ -64428,7 +64428,7 @@
         </is>
       </c>
       <c r="K749" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L749" t="n">
         <v>0</v>
@@ -64480,7 +64480,7 @@
         </is>
       </c>
       <c r="K750" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="L750" t="n">
         <v>0</v>
@@ -64532,7 +64532,7 @@
         </is>
       </c>
       <c r="K751" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="L751" t="n">
         <v>0</v>
@@ -64584,7 +64584,7 @@
         </is>
       </c>
       <c r="K752" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="L752" t="n">
         <v>0</v>
@@ -64636,7 +64636,7 @@
         </is>
       </c>
       <c r="K753" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="L753" t="n">
         <v>0</v>
@@ -64688,7 +64688,7 @@
         </is>
       </c>
       <c r="K754" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L754" t="n">
         <v>0</v>
@@ -64740,7 +64740,7 @@
         </is>
       </c>
       <c r="K755" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L755" t="n">
         <v>0</v>
@@ -64792,7 +64792,7 @@
         </is>
       </c>
       <c r="K756" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="L756" t="n">
         <v>0</v>
@@ -64844,7 +64844,7 @@
         </is>
       </c>
       <c r="K757" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="L757" t="n">
         <v>0</v>
@@ -64896,7 +64896,7 @@
         </is>
       </c>
       <c r="K758" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L758" t="n">
         <v>0</v>
@@ -64948,7 +64948,7 @@
         </is>
       </c>
       <c r="K759" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L759" t="n">
         <v>0</v>
@@ -65000,7 +65000,7 @@
         </is>
       </c>
       <c r="K760" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="L760" t="n">
         <v>0</v>
@@ -65052,7 +65052,7 @@
         </is>
       </c>
       <c r="K761" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="L761" t="n">
         <v>0</v>
@@ -65104,7 +65104,7 @@
         </is>
       </c>
       <c r="K762" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L762" t="n">
         <v>0</v>
@@ -65156,7 +65156,7 @@
         </is>
       </c>
       <c r="K763" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="L763" t="n">
         <v>0</v>
@@ -65208,7 +65208,7 @@
         </is>
       </c>
       <c r="K764" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="L764" t="n">
         <v>0</v>
@@ -65260,7 +65260,7 @@
         </is>
       </c>
       <c r="K765" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="L765" t="n">
         <v>0</v>
@@ -65312,7 +65312,7 @@
         </is>
       </c>
       <c r="K766" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L766" t="n">
         <v>0</v>
@@ -65364,7 +65364,7 @@
         </is>
       </c>
       <c r="K767" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L767" t="n">
         <v>0</v>
@@ -65416,7 +65416,7 @@
         </is>
       </c>
       <c r="K768" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="L768" t="n">
         <v>0</v>
@@ -65468,7 +65468,7 @@
         </is>
       </c>
       <c r="K769" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="L769" t="n">
         <v>0</v>
@@ -65520,7 +65520,7 @@
         </is>
       </c>
       <c r="K770" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L770" t="n">
         <v>0</v>
@@ -65572,7 +65572,7 @@
         </is>
       </c>
       <c r="K771" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="L771" t="n">
         <v>0</v>
@@ -65624,7 +65624,7 @@
         </is>
       </c>
       <c r="K772" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L772" t="n">
         <v>0</v>
@@ -65676,7 +65676,7 @@
         </is>
       </c>
       <c r="K773" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L773" t="n">
         <v>0</v>
@@ -65728,7 +65728,7 @@
         </is>
       </c>
       <c r="K774" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L774" t="n">
         <v>0</v>
@@ -65780,7 +65780,7 @@
         </is>
       </c>
       <c r="K775" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="L775" t="n">
         <v>0</v>
@@ -65832,7 +65832,7 @@
         </is>
       </c>
       <c r="K776" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="L776" t="n">
         <v>0</v>
@@ -65884,7 +65884,7 @@
         </is>
       </c>
       <c r="K777" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="L777" t="n">
         <v>0</v>
@@ -65936,7 +65936,7 @@
         </is>
       </c>
       <c r="K778" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="L778" t="n">
         <v>0</v>
@@ -65988,7 +65988,7 @@
         </is>
       </c>
       <c r="K779" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L779" t="n">
         <v>0</v>
@@ -66040,7 +66040,7 @@
         </is>
       </c>
       <c r="K780" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="L780" t="n">
         <v>0</v>
@@ -66092,7 +66092,7 @@
         </is>
       </c>
       <c r="K781" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="L781" t="n">
         <v>0</v>
@@ -66144,7 +66144,7 @@
         </is>
       </c>
       <c r="K782" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="L782" t="n">
         <v>0</v>
@@ -66196,7 +66196,7 @@
         </is>
       </c>
       <c r="K783" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="L783" t="n">
         <v>0</v>
@@ -66248,7 +66248,7 @@
         </is>
       </c>
       <c r="K784" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="L784" t="n">
         <v>0</v>
@@ -66300,7 +66300,7 @@
         </is>
       </c>
       <c r="K785" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="L785" t="n">
         <v>0</v>
@@ -66352,7 +66352,7 @@
         </is>
       </c>
       <c r="K786" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="L786" t="n">
         <v>0</v>
@@ -66404,7 +66404,7 @@
         </is>
       </c>
       <c r="K787" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="L787" t="n">
         <v>0</v>
@@ -66456,7 +66456,7 @@
         </is>
       </c>
       <c r="K788" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="L788" t="n">
         <v>0</v>
@@ -66508,7 +66508,7 @@
         </is>
       </c>
       <c r="K789" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="L789" t="n">
         <v>0</v>
@@ -66560,7 +66560,7 @@
         </is>
       </c>
       <c r="K790" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L790" t="n">
         <v>0</v>
@@ -66612,7 +66612,7 @@
         </is>
       </c>
       <c r="K791" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L791" t="n">
         <v>0</v>
@@ -66664,7 +66664,7 @@
         </is>
       </c>
       <c r="K792" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="L792" t="n">
         <v>0</v>
@@ -66716,7 +66716,7 @@
         </is>
       </c>
       <c r="K793" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L793" t="n">
         <v>0</v>
@@ -66768,7 +66768,7 @@
         </is>
       </c>
       <c r="K794" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L794" t="n">
         <v>0</v>
@@ -66820,7 +66820,7 @@
         </is>
       </c>
       <c r="K795" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L795" t="n">
         <v>0</v>
@@ -66872,7 +66872,7 @@
         </is>
       </c>
       <c r="K796" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="L796" t="n">
         <v>0</v>
@@ -66924,7 +66924,7 @@
         </is>
       </c>
       <c r="K797" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L797" t="n">
         <v>0</v>
@@ -66976,7 +66976,7 @@
         </is>
       </c>
       <c r="K798" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L798" t="n">
         <v>0</v>
@@ -67028,7 +67028,7 @@
         </is>
       </c>
       <c r="K799" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L799" t="n">
         <v>0</v>
@@ -67080,7 +67080,7 @@
         </is>
       </c>
       <c r="K800" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L800" t="n">
         <v>0</v>
@@ -67132,7 +67132,7 @@
         </is>
       </c>
       <c r="K801" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L801" t="n">
         <v>0</v>
@@ -67184,7 +67184,7 @@
         </is>
       </c>
       <c r="K802" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L802" t="n">
         <v>0</v>
@@ -67236,7 +67236,7 @@
         </is>
       </c>
       <c r="K803" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L803" t="n">
         <v>0</v>
@@ -67288,7 +67288,7 @@
         </is>
       </c>
       <c r="K804" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L804" t="n">
         <v>0</v>
@@ -67340,7 +67340,7 @@
         </is>
       </c>
       <c r="K805" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L805" t="n">
         <v>0</v>
@@ -67496,7 +67496,7 @@
         </is>
       </c>
       <c r="K808" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L808" t="n">
         <v>0</v>
@@ -67548,7 +67548,7 @@
         </is>
       </c>
       <c r="K809" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L809" t="n">
         <v>0</v>
@@ -67704,7 +67704,7 @@
         </is>
       </c>
       <c r="K812" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L812" t="n">
         <v>0</v>
@@ -67808,7 +67808,7 @@
         </is>
       </c>
       <c r="K814" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L814" t="n">
         <v>0</v>
@@ -67860,7 +67860,7 @@
         </is>
       </c>
       <c r="K815" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L815" t="n">
         <v>0</v>
@@ -67964,7 +67964,7 @@
         </is>
       </c>
       <c r="K817" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L817" t="n">
         <v>0</v>
@@ -68120,7 +68120,7 @@
         </is>
       </c>
       <c r="K820" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L820" t="n">
         <v>0</v>
@@ -68172,7 +68172,7 @@
         </is>
       </c>
       <c r="K821" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L821" t="n">
         <v>0</v>
@@ -68276,7 +68276,7 @@
         </is>
       </c>
       <c r="K823" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="L823" t="n">
         <v>0</v>
@@ -68380,7 +68380,7 @@
         </is>
       </c>
       <c r="K825" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L825" t="n">
         <v>0</v>
@@ -68432,7 +68432,7 @@
         </is>
       </c>
       <c r="K826" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L826" t="n">
         <v>0</v>
@@ -68484,7 +68484,7 @@
         </is>
       </c>
       <c r="K827" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L827" t="n">
         <v>0</v>
@@ -68536,7 +68536,7 @@
         </is>
       </c>
       <c r="K828" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L828" t="n">
         <v>0</v>
@@ -68588,7 +68588,7 @@
         </is>
       </c>
       <c r="K829" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="L829" t="n">
         <v>0</v>
@@ -68640,7 +68640,7 @@
         </is>
       </c>
       <c r="K830" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L830" t="n">
         <v>0</v>
@@ -68692,7 +68692,7 @@
         </is>
       </c>
       <c r="K831" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="L831" t="n">
         <v>0</v>
@@ -68744,7 +68744,7 @@
         </is>
       </c>
       <c r="K832" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="L832" t="n">
         <v>0</v>
@@ -68796,7 +68796,7 @@
         </is>
       </c>
       <c r="K833" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="L833" t="n">
         <v>0</v>
@@ -68848,7 +68848,7 @@
         </is>
       </c>
       <c r="K834" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="L834" t="n">
         <v>0</v>
@@ -68900,7 +68900,7 @@
         </is>
       </c>
       <c r="K835" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="L835" t="n">
         <v>0</v>
@@ -68952,7 +68952,7 @@
         </is>
       </c>
       <c r="K836" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="L836" t="n">
         <v>0</v>
@@ -69004,7 +69004,7 @@
         </is>
       </c>
       <c r="K837" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="L837" t="n">
         <v>0</v>
@@ -69056,7 +69056,7 @@
         </is>
       </c>
       <c r="K838" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="L838" t="n">
         <v>0</v>
@@ -69108,7 +69108,7 @@
         </is>
       </c>
       <c r="K839" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="L839" t="n">
         <v>0</v>
@@ -69160,7 +69160,7 @@
         </is>
       </c>
       <c r="K840" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="L840" t="n">
         <v>0</v>
@@ -69264,7 +69264,7 @@
         </is>
       </c>
       <c r="K842" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L842" t="n">
         <v>0</v>
@@ -69316,7 +69316,7 @@
         </is>
       </c>
       <c r="K843" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L843" t="n">
         <v>0</v>
@@ -69368,7 +69368,7 @@
         </is>
       </c>
       <c r="K844" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L844" t="n">
         <v>0</v>
@@ -69420,7 +69420,7 @@
         </is>
       </c>
       <c r="K845" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L845" t="n">
         <v>0</v>
@@ -69472,7 +69472,7 @@
         </is>
       </c>
       <c r="K846" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="L846" t="n">
         <v>0</v>
@@ -69524,7 +69524,7 @@
         </is>
       </c>
       <c r="K847" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="L847" t="n">
         <v>0</v>
@@ -69576,7 +69576,7 @@
         </is>
       </c>
       <c r="K848" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="L848" t="n">
         <v>0</v>
@@ -69628,7 +69628,7 @@
         </is>
       </c>
       <c r="K849" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L849" t="n">
         <v>0</v>
@@ -69680,7 +69680,7 @@
         </is>
       </c>
       <c r="K850" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="L850" t="n">
         <v>0</v>
@@ -69732,7 +69732,7 @@
         </is>
       </c>
       <c r="K851" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L851" t="n">
         <v>0</v>
@@ -69784,7 +69784,7 @@
         </is>
       </c>
       <c r="K852" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L852" t="n">
         <v>0</v>
@@ -69836,7 +69836,7 @@
         </is>
       </c>
       <c r="K853" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="L853" t="n">
         <v>0</v>
@@ -69888,7 +69888,7 @@
         </is>
       </c>
       <c r="K854" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="L854" t="n">
         <v>0</v>
@@ -69940,7 +69940,7 @@
         </is>
       </c>
       <c r="K855" t="n">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="L855" t="n">
         <v>0</v>
@@ -69992,7 +69992,7 @@
         </is>
       </c>
       <c r="K856" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="L856" t="n">
         <v>0</v>
@@ -70044,7 +70044,7 @@
         </is>
       </c>
       <c r="K857" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="L857" t="n">
         <v>0</v>
@@ -70096,7 +70096,7 @@
         </is>
       </c>
       <c r="K858" t="n">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="L858" t="n">
         <v>0</v>
@@ -70148,7 +70148,7 @@
         </is>
       </c>
       <c r="K859" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="L859" t="n">
         <v>0</v>
@@ -70200,7 +70200,7 @@
         </is>
       </c>
       <c r="K860" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="L860" t="n">
         <v>0</v>
@@ -70252,7 +70252,7 @@
         </is>
       </c>
       <c r="K861" t="n">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="L861" t="n">
         <v>0</v>
@@ -70304,7 +70304,7 @@
         </is>
       </c>
       <c r="K862" t="n">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="L862" t="n">
         <v>0</v>
@@ -70356,7 +70356,7 @@
         </is>
       </c>
       <c r="K863" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="L863" t="n">
         <v>0</v>
@@ -70408,7 +70408,7 @@
         </is>
       </c>
       <c r="K864" t="n">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="L864" t="n">
         <v>0</v>
@@ -70460,7 +70460,7 @@
         </is>
       </c>
       <c r="K865" t="n">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="L865" t="n">
         <v>0</v>
@@ -70512,7 +70512,7 @@
         </is>
       </c>
       <c r="K866" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="L866" t="n">
         <v>0</v>
@@ -70564,7 +70564,7 @@
         </is>
       </c>
       <c r="K867" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="L867" t="n">
         <v>0</v>
@@ -70616,7 +70616,7 @@
         </is>
       </c>
       <c r="K868" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="L868" t="n">
         <v>0</v>
@@ -70668,7 +70668,7 @@
         </is>
       </c>
       <c r="K869" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="L869" t="n">
         <v>0</v>
@@ -70720,7 +70720,7 @@
         </is>
       </c>
       <c r="K870" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="L870" t="n">
         <v>0</v>
@@ -70772,7 +70772,7 @@
         </is>
       </c>
       <c r="K871" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="L871" t="n">
         <v>0</v>
@@ -70824,7 +70824,7 @@
         </is>
       </c>
       <c r="K872" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="L872" t="n">
         <v>0</v>
@@ -70876,7 +70876,7 @@
         </is>
       </c>
       <c r="K873" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L873" t="n">
         <v>0</v>
@@ -70980,7 +70980,7 @@
         </is>
       </c>
       <c r="K875" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L875" t="n">
         <v>0</v>
@@ -71032,7 +71032,7 @@
         </is>
       </c>
       <c r="K876" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="L876" t="n">
         <v>0</v>
@@ -71084,7 +71084,7 @@
         </is>
       </c>
       <c r="K877" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L877" t="n">
         <v>0</v>
@@ -71136,7 +71136,7 @@
         </is>
       </c>
       <c r="K878" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="L878" t="n">
         <v>0</v>
@@ -71188,7 +71188,7 @@
         </is>
       </c>
       <c r="K879" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="L879" t="n">
         <v>0</v>
@@ -71240,7 +71240,7 @@
         </is>
       </c>
       <c r="K880" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L880" t="n">
         <v>0</v>
@@ -71292,7 +71292,7 @@
         </is>
       </c>
       <c r="K881" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="L881" t="n">
         <v>0</v>
@@ -71344,7 +71344,7 @@
         </is>
       </c>
       <c r="K882" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="L882" t="n">
         <v>0</v>
@@ -71396,7 +71396,7 @@
         </is>
       </c>
       <c r="K883" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="L883" t="n">
         <v>0</v>
@@ -71448,7 +71448,7 @@
         </is>
       </c>
       <c r="K884" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L884" t="n">
         <v>0</v>
@@ -71500,7 +71500,7 @@
         </is>
       </c>
       <c r="K885" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L885" t="n">
         <v>0</v>
@@ -71552,7 +71552,7 @@
         </is>
       </c>
       <c r="K886" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L886" t="n">
         <v>0</v>
@@ -71604,7 +71604,7 @@
         </is>
       </c>
       <c r="K887" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="L887" t="n">
         <v>0</v>
@@ -71656,7 +71656,7 @@
         </is>
       </c>
       <c r="K888" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="L888" t="n">
         <v>0</v>
@@ -71708,7 +71708,7 @@
         </is>
       </c>
       <c r="K889" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="L889" t="n">
         <v>0</v>
@@ -71760,7 +71760,7 @@
         </is>
       </c>
       <c r="K890" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="L890" t="n">
         <v>0</v>
@@ -71812,7 +71812,7 @@
         </is>
       </c>
       <c r="K891" t="n">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="L891" t="n">
         <v>0</v>
@@ -71864,7 +71864,7 @@
         </is>
       </c>
       <c r="K892" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="L892" t="n">
         <v>0</v>
@@ -71916,7 +71916,7 @@
         </is>
       </c>
       <c r="K893" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="L893" t="n">
         <v>0</v>
@@ -71968,7 +71968,7 @@
         </is>
       </c>
       <c r="K894" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="L894" t="n">
         <v>0</v>
@@ -72020,7 +72020,7 @@
         </is>
       </c>
       <c r="K895" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="L895" t="n">
         <v>0</v>
@@ -72072,7 +72072,7 @@
         </is>
       </c>
       <c r="K896" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="L896" t="n">
         <v>0</v>
@@ -72124,7 +72124,7 @@
         </is>
       </c>
       <c r="K897" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L897" t="n">
         <v>0</v>
@@ -72176,7 +72176,7 @@
         </is>
       </c>
       <c r="K898" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="L898" t="n">
         <v>0</v>
@@ -72332,7 +72332,7 @@
         </is>
       </c>
       <c r="K901" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L901" t="n">
         <v>0</v>
@@ -72384,7 +72384,7 @@
         </is>
       </c>
       <c r="K902" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L902" t="n">
         <v>0</v>
@@ -72436,7 +72436,7 @@
         </is>
       </c>
       <c r="K903" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="L903" t="n">
         <v>0</v>
@@ -72488,7 +72488,7 @@
         </is>
       </c>
       <c r="K904" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L904" t="n">
         <v>0</v>
@@ -72540,7 +72540,7 @@
         </is>
       </c>
       <c r="K905" t="n">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="L905" t="n">
         <v>0</v>
@@ -72592,7 +72592,7 @@
         </is>
       </c>
       <c r="K906" t="n">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="L906" t="n">
         <v>0</v>
@@ -72644,7 +72644,7 @@
         </is>
       </c>
       <c r="K907" t="n">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="L907" t="n">
         <v>0</v>
@@ -72696,7 +72696,7 @@
         </is>
       </c>
       <c r="K908" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="L908" t="n">
         <v>0</v>
@@ -72748,7 +72748,7 @@
         </is>
       </c>
       <c r="K909" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="L909" t="n">
         <v>0</v>
@@ -72800,7 +72800,7 @@
         </is>
       </c>
       <c r="K910" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="L910" t="n">
         <v>0</v>
@@ -72852,7 +72852,7 @@
         </is>
       </c>
       <c r="K911" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="L911" t="n">
         <v>0</v>
@@ -72904,7 +72904,7 @@
         </is>
       </c>
       <c r="K912" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="L912" t="n">
         <v>0</v>
@@ -72956,7 +72956,7 @@
         </is>
       </c>
       <c r="K913" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="L913" t="n">
         <v>0</v>
@@ -73008,7 +73008,7 @@
         </is>
       </c>
       <c r="K914" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="L914" t="n">
         <v>0</v>
@@ -73060,7 +73060,7 @@
         </is>
       </c>
       <c r="K915" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="L915" t="n">
         <v>0</v>
@@ -73112,7 +73112,7 @@
         </is>
       </c>
       <c r="K916" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="L916" t="n">
         <v>0</v>
@@ -73164,7 +73164,7 @@
         </is>
       </c>
       <c r="K917" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="L917" t="n">
         <v>0</v>
@@ -73216,7 +73216,7 @@
         </is>
       </c>
       <c r="K918" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="L918" t="n">
         <v>0</v>
@@ -73268,7 +73268,7 @@
         </is>
       </c>
       <c r="K919" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L919" t="n">
         <v>0</v>
@@ -73320,7 +73320,7 @@
         </is>
       </c>
       <c r="K920" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="L920" t="n">
         <v>0</v>
@@ -73372,7 +73372,7 @@
         </is>
       </c>
       <c r="K921" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="L921" t="n">
         <v>0</v>
@@ -73424,7 +73424,7 @@
         </is>
       </c>
       <c r="K922" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L922" t="n">
         <v>0</v>
@@ -73528,7 +73528,7 @@
         </is>
       </c>
       <c r="K924" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L924" t="n">
         <v>0</v>
@@ -73684,7 +73684,7 @@
         </is>
       </c>
       <c r="K927" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L927" t="n">
         <v>0</v>
@@ -73736,7 +73736,7 @@
         </is>
       </c>
       <c r="K928" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L928" t="n">
         <v>0</v>
@@ -73788,7 +73788,7 @@
         </is>
       </c>
       <c r="K929" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="L929" t="n">
         <v>0</v>
@@ -73840,7 +73840,7 @@
         </is>
       </c>
       <c r="K930" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L930" t="n">
         <v>0</v>
@@ -73892,7 +73892,7 @@
         </is>
       </c>
       <c r="K931" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L931" t="n">
         <v>0</v>
@@ -73944,7 +73944,7 @@
         </is>
       </c>
       <c r="K932" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L932" t="n">
         <v>0</v>
@@ -73996,7 +73996,7 @@
         </is>
       </c>
       <c r="K933" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L933" t="n">
         <v>0</v>
@@ -74048,7 +74048,7 @@
         </is>
       </c>
       <c r="K934" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L934" t="n">
         <v>0</v>
@@ -74256,7 +74256,7 @@
         </is>
       </c>
       <c r="K938" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L938" t="n">
         <v>0</v>
@@ -74308,7 +74308,7 @@
         </is>
       </c>
       <c r="K939" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L939" t="n">
         <v>0</v>
@@ -74360,7 +74360,7 @@
         </is>
       </c>
       <c r="K940" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="L940" t="n">
         <v>0</v>
@@ -74412,7 +74412,7 @@
         </is>
       </c>
       <c r="K941" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="L941" t="n">
         <v>0</v>
@@ -74464,7 +74464,7 @@
         </is>
       </c>
       <c r="K942" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="L942" t="n">
         <v>0</v>
@@ -74516,7 +74516,7 @@
         </is>
       </c>
       <c r="K943" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="L943" t="n">
         <v>0</v>
@@ -74568,7 +74568,7 @@
         </is>
       </c>
       <c r="K944" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="L944" t="n">
         <v>0</v>
@@ -74672,7 +74672,7 @@
         </is>
       </c>
       <c r="K946" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="L946" t="n">
         <v>0</v>
@@ -74724,7 +74724,7 @@
         </is>
       </c>
       <c r="K947" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="L947" t="n">
         <v>0</v>
@@ -74776,7 +74776,7 @@
         </is>
       </c>
       <c r="K948" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L948" t="n">
         <v>0</v>
@@ -74828,7 +74828,7 @@
         </is>
       </c>
       <c r="K949" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L949" t="n">
         <v>0</v>
@@ -74880,7 +74880,7 @@
         </is>
       </c>
       <c r="K950" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L950" t="n">
         <v>0</v>
@@ -74932,7 +74932,7 @@
         </is>
       </c>
       <c r="K951" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="L951" t="n">
         <v>0</v>
@@ -74984,7 +74984,7 @@
         </is>
       </c>
       <c r="K952" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L952" t="n">
         <v>0</v>
@@ -75036,7 +75036,7 @@
         </is>
       </c>
       <c r="K953" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L953" t="n">
         <v>0</v>
@@ -75088,7 +75088,7 @@
         </is>
       </c>
       <c r="K954" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="L954" t="n">
         <v>0</v>
@@ -75140,7 +75140,7 @@
         </is>
       </c>
       <c r="K955" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="L955" t="n">
         <v>0</v>
@@ -75192,7 +75192,7 @@
         </is>
       </c>
       <c r="K956" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="L956" t="n">
         <v>0</v>
@@ -75244,7 +75244,7 @@
         </is>
       </c>
       <c r="K957" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="L957" t="n">
         <v>0</v>
@@ -75296,7 +75296,7 @@
         </is>
       </c>
       <c r="K958" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="L958" t="n">
         <v>0</v>
@@ -75348,7 +75348,7 @@
         </is>
       </c>
       <c r="K959" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="L959" t="n">
         <v>0</v>
@@ -75400,7 +75400,7 @@
         </is>
       </c>
       <c r="K960" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="L960" t="n">
         <v>0</v>
@@ -75452,7 +75452,7 @@
         </is>
       </c>
       <c r="K961" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="L961" t="n">
         <v>0</v>
@@ -75504,7 +75504,7 @@
         </is>
       </c>
       <c r="K962" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="L962" t="n">
         <v>0</v>
@@ -75556,7 +75556,7 @@
         </is>
       </c>
       <c r="K963" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="L963" t="n">
         <v>0</v>
@@ -75608,7 +75608,7 @@
         </is>
       </c>
       <c r="K964" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="L964" t="n">
         <v>0</v>
@@ -75660,7 +75660,7 @@
         </is>
       </c>
       <c r="K965" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="L965" t="n">
         <v>0</v>
@@ -75712,7 +75712,7 @@
         </is>
       </c>
       <c r="K966" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="L966" t="n">
         <v>0</v>
@@ -75764,7 +75764,7 @@
         </is>
       </c>
       <c r="K967" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="L967" t="n">
         <v>0</v>
@@ -75816,7 +75816,7 @@
         </is>
       </c>
       <c r="K968" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="L968" t="n">
         <v>0</v>
@@ -75868,7 +75868,7 @@
         </is>
       </c>
       <c r="K969" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="L969" t="n">
         <v>0</v>
@@ -75920,7 +75920,7 @@
         </is>
       </c>
       <c r="K970" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="L970" t="n">
         <v>0</v>
@@ -76076,7 +76076,7 @@
         </is>
       </c>
       <c r="K973" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L973" t="n">
         <v>0</v>
@@ -76128,7 +76128,7 @@
         </is>
       </c>
       <c r="K974" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L974" t="n">
         <v>0</v>
@@ -76232,7 +76232,7 @@
         </is>
       </c>
       <c r="K976" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L976" t="n">
         <v>0</v>
@@ -76336,7 +76336,7 @@
         </is>
       </c>
       <c r="K978" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L978" t="n">
         <v>0</v>
@@ -76388,7 +76388,7 @@
         </is>
       </c>
       <c r="K979" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="L979" t="n">
         <v>0</v>
@@ -76440,7 +76440,7 @@
         </is>
       </c>
       <c r="K980" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="L980" t="n">
         <v>0</v>
@@ -76492,7 +76492,7 @@
         </is>
       </c>
       <c r="K981" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="L981" t="n">
         <v>0</v>
@@ -76544,7 +76544,7 @@
         </is>
       </c>
       <c r="K982" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="L982" t="n">
         <v>0</v>
@@ -76596,7 +76596,7 @@
         </is>
       </c>
       <c r="K983" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="L983" t="n">
         <v>0</v>
@@ -76648,7 +76648,7 @@
         </is>
       </c>
       <c r="K984" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="L984" t="n">
         <v>0</v>
@@ -76700,7 +76700,7 @@
         </is>
       </c>
       <c r="K985" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="L985" t="n">
         <v>0</v>
@@ -76752,7 +76752,7 @@
         </is>
       </c>
       <c r="K986" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L986" t="n">
         <v>0</v>
@@ -76804,7 +76804,7 @@
         </is>
       </c>
       <c r="K987" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L987" t="n">
         <v>0</v>
@@ -76856,7 +76856,7 @@
         </is>
       </c>
       <c r="K988" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="L988" t="n">
         <v>0</v>
@@ -76908,7 +76908,7 @@
         </is>
       </c>
       <c r="K989" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="L989" t="n">
         <v>0</v>
@@ -76960,7 +76960,7 @@
         </is>
       </c>
       <c r="K990" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="L990" t="n">
         <v>0</v>
@@ -77168,7 +77168,7 @@
         </is>
       </c>
       <c r="K994" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L994" t="n">
         <v>0</v>
@@ -77220,7 +77220,7 @@
         </is>
       </c>
       <c r="K995" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L995" t="n">
         <v>0</v>
@@ -77324,7 +77324,7 @@
         </is>
       </c>
       <c r="K997" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="L997" t="n">
         <v>0</v>
@@ -77376,7 +77376,7 @@
         </is>
       </c>
       <c r="K998" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L998" t="n">
         <v>0</v>
@@ -77428,7 +77428,7 @@
         </is>
       </c>
       <c r="K999" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L999" t="n">
         <v>0</v>
@@ -77480,7 +77480,7 @@
         </is>
       </c>
       <c r="K1000" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L1000" t="n">
         <v>0</v>
@@ -77532,7 +77532,7 @@
         </is>
       </c>
       <c r="K1001" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L1001" t="n">
         <v>0</v>

--- a/Data/Output/stress_1000_enriched.xlsx
+++ b/Data/Output/stress_1000_enriched.xlsx
@@ -25461,20 +25461,6 @@
   </sheetPr>
   <dimension ref="A1:L1001"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -25584,7 +25570,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -25636,7 +25622,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -25688,7 +25674,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -25740,7 +25726,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -25792,7 +25778,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -25844,7 +25830,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -25896,7 +25882,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -25948,7 +25934,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -26000,7 +25986,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -26052,7 +26038,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -26104,7 +26090,7 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -26156,7 +26142,7 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -26208,7 +26194,7 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -26260,7 +26246,7 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -26312,7 +26298,7 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -26364,7 +26350,7 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -26416,7 +26402,7 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -26468,7 +26454,7 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -26520,7 +26506,7 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -26572,7 +26558,7 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -26624,7 +26610,7 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -26676,7 +26662,7 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -26728,7 +26714,7 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -26780,7 +26766,7 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -26832,7 +26818,7 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -26884,7 +26870,7 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -26936,7 +26922,7 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -26988,7 +26974,7 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -27040,7 +27026,7 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -27092,7 +27078,7 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -27144,7 +27130,7 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -27196,7 +27182,7 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -27248,7 +27234,7 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -27300,7 +27286,7 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -27352,7 +27338,7 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -27404,7 +27390,7 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -27456,7 +27442,7 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -27508,7 +27494,7 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -27560,7 +27546,7 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -27612,7 +27598,7 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -27664,7 +27650,7 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -27716,7 +27702,7 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -27768,7 +27754,7 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -27820,7 +27806,7 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -27872,7 +27858,7 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -27924,7 +27910,7 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -27976,7 +27962,7 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -28028,7 +28014,7 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -28080,7 +28066,7 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -28132,7 +28118,7 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -28184,7 +28170,7 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -28236,7 +28222,7 @@
         </is>
       </c>
       <c r="K53" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -28288,7 +28274,7 @@
         </is>
       </c>
       <c r="K54" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -28340,7 +28326,7 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -28392,7 +28378,7 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -28444,7 +28430,7 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -28496,7 +28482,7 @@
         </is>
       </c>
       <c r="K58" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -28548,7 +28534,7 @@
         </is>
       </c>
       <c r="K59" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -28600,7 +28586,7 @@
         </is>
       </c>
       <c r="K60" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -28652,7 +28638,7 @@
         </is>
       </c>
       <c r="K61" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -28704,7 +28690,7 @@
         </is>
       </c>
       <c r="K62" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -28756,7 +28742,7 @@
         </is>
       </c>
       <c r="K63" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -28808,7 +28794,7 @@
         </is>
       </c>
       <c r="K64" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -28860,7 +28846,7 @@
         </is>
       </c>
       <c r="K65" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -28912,7 +28898,7 @@
         </is>
       </c>
       <c r="K66" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -28964,7 +28950,7 @@
         </is>
       </c>
       <c r="K67" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -29016,7 +29002,7 @@
         </is>
       </c>
       <c r="K68" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -29068,7 +29054,7 @@
         </is>
       </c>
       <c r="K69" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -29120,7 +29106,7 @@
         </is>
       </c>
       <c r="K70" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -29172,7 +29158,7 @@
         </is>
       </c>
       <c r="K71" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
@@ -29224,7 +29210,7 @@
         </is>
       </c>
       <c r="K72" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
@@ -29276,7 +29262,7 @@
         </is>
       </c>
       <c r="K73" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -29328,7 +29314,7 @@
         </is>
       </c>
       <c r="K74" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
@@ -29380,7 +29366,7 @@
         </is>
       </c>
       <c r="K75" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -29432,7 +29418,7 @@
         </is>
       </c>
       <c r="K76" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
@@ -29484,7 +29470,7 @@
         </is>
       </c>
       <c r="K77" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -29536,7 +29522,7 @@
         </is>
       </c>
       <c r="K78" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -29588,7 +29574,7 @@
         </is>
       </c>
       <c r="K79" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
@@ -29640,7 +29626,7 @@
         </is>
       </c>
       <c r="K80" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -29692,7 +29678,7 @@
         </is>
       </c>
       <c r="K81" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -29744,7 +29730,7 @@
         </is>
       </c>
       <c r="K82" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -29796,7 +29782,7 @@
         </is>
       </c>
       <c r="K83" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -29848,7 +29834,7 @@
         </is>
       </c>
       <c r="K84" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
@@ -29900,7 +29886,7 @@
         </is>
       </c>
       <c r="K85" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -29952,7 +29938,7 @@
         </is>
       </c>
       <c r="K86" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
@@ -30004,7 +29990,7 @@
         </is>
       </c>
       <c r="K87" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -30056,7 +30042,7 @@
         </is>
       </c>
       <c r="K88" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -30108,7 +30094,7 @@
         </is>
       </c>
       <c r="K89" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
@@ -30160,7 +30146,7 @@
         </is>
       </c>
       <c r="K90" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -30212,7 +30198,7 @@
         </is>
       </c>
       <c r="K91" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L91" t="n">
         <v>0</v>
@@ -30264,7 +30250,7 @@
         </is>
       </c>
       <c r="K92" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
@@ -30316,7 +30302,7 @@
         </is>
       </c>
       <c r="K93" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
@@ -30368,7 +30354,7 @@
         </is>
       </c>
       <c r="K94" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L94" t="n">
         <v>0</v>
@@ -30420,7 +30406,7 @@
         </is>
       </c>
       <c r="K95" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L95" t="n">
         <v>0</v>
@@ -30472,7 +30458,7 @@
         </is>
       </c>
       <c r="K96" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
@@ -30524,7 +30510,7 @@
         </is>
       </c>
       <c r="K97" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
@@ -30576,7 +30562,7 @@
         </is>
       </c>
       <c r="K98" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
@@ -30628,7 +30614,7 @@
         </is>
       </c>
       <c r="K99" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
@@ -30680,7 +30666,7 @@
         </is>
       </c>
       <c r="K100" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>
@@ -30732,7 +30718,7 @@
         </is>
       </c>
       <c r="K101" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L101" t="n">
         <v>0</v>
@@ -30784,7 +30770,7 @@
         </is>
       </c>
       <c r="K102" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L102" t="n">
         <v>0</v>
@@ -30836,7 +30822,7 @@
         </is>
       </c>
       <c r="K103" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L103" t="n">
         <v>0</v>
@@ -30888,7 +30874,7 @@
         </is>
       </c>
       <c r="K104" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
@@ -30940,7 +30926,7 @@
         </is>
       </c>
       <c r="K105" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L105" t="n">
         <v>0</v>
@@ -30992,7 +30978,7 @@
         </is>
       </c>
       <c r="K106" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
@@ -31044,7 +31030,7 @@
         </is>
       </c>
       <c r="K107" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L107" t="n">
         <v>0</v>
@@ -31096,7 +31082,7 @@
         </is>
       </c>
       <c r="K108" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
@@ -31148,7 +31134,7 @@
         </is>
       </c>
       <c r="K109" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
@@ -31200,7 +31186,7 @@
         </is>
       </c>
       <c r="K110" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L110" t="n">
         <v>0</v>
@@ -31252,7 +31238,7 @@
         </is>
       </c>
       <c r="K111" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L111" t="n">
         <v>0</v>
@@ -31304,7 +31290,7 @@
         </is>
       </c>
       <c r="K112" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
@@ -31356,7 +31342,7 @@
         </is>
       </c>
       <c r="K113" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
@@ -31408,7 +31394,7 @@
         </is>
       </c>
       <c r="K114" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
@@ -31460,7 +31446,7 @@
         </is>
       </c>
       <c r="K115" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L115" t="n">
         <v>0</v>
@@ -31512,7 +31498,7 @@
         </is>
       </c>
       <c r="K116" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
@@ -31564,7 +31550,7 @@
         </is>
       </c>
       <c r="K117" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
@@ -31616,7 +31602,7 @@
         </is>
       </c>
       <c r="K118" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
@@ -31668,7 +31654,7 @@
         </is>
       </c>
       <c r="K119" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
@@ -31720,7 +31706,7 @@
         </is>
       </c>
       <c r="K120" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L120" t="n">
         <v>0</v>
@@ -31772,7 +31758,7 @@
         </is>
       </c>
       <c r="K121" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L121" t="n">
         <v>0</v>
@@ -31824,7 +31810,7 @@
         </is>
       </c>
       <c r="K122" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L122" t="n">
         <v>0</v>
@@ -31876,7 +31862,7 @@
         </is>
       </c>
       <c r="K123" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="L123" t="n">
         <v>0</v>
@@ -31928,7 +31914,7 @@
         </is>
       </c>
       <c r="K124" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
@@ -31980,7 +31966,7 @@
         </is>
       </c>
       <c r="K125" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="L125" t="n">
         <v>0</v>
@@ -32032,7 +32018,7 @@
         </is>
       </c>
       <c r="K126" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="L126" t="n">
         <v>0</v>
@@ -32084,7 +32070,7 @@
         </is>
       </c>
       <c r="K127" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="L127" t="n">
         <v>0</v>
@@ -32136,7 +32122,7 @@
         </is>
       </c>
       <c r="K128" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="L128" t="n">
         <v>0</v>
@@ -32188,7 +32174,7 @@
         </is>
       </c>
       <c r="K129" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="L129" t="n">
         <v>0</v>
@@ -32240,7 +32226,7 @@
         </is>
       </c>
       <c r="K130" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="L130" t="n">
         <v>0</v>
@@ -32292,7 +32278,7 @@
         </is>
       </c>
       <c r="K131" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="L131" t="n">
         <v>0</v>
@@ -32344,7 +32330,7 @@
         </is>
       </c>
       <c r="K132" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="L132" t="n">
         <v>0</v>
@@ -32396,7 +32382,7 @@
         </is>
       </c>
       <c r="K133" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L133" t="n">
         <v>0</v>
@@ -32448,7 +32434,7 @@
         </is>
       </c>
       <c r="K134" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L134" t="n">
         <v>0</v>
@@ -32500,7 +32486,7 @@
         </is>
       </c>
       <c r="K135" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L135" t="n">
         <v>0</v>
@@ -32552,7 +32538,7 @@
         </is>
       </c>
       <c r="K136" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L136" t="n">
         <v>0</v>
@@ -32604,7 +32590,7 @@
         </is>
       </c>
       <c r="K137" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L137" t="n">
         <v>0</v>
@@ -32656,7 +32642,7 @@
         </is>
       </c>
       <c r="K138" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L138" t="n">
         <v>0</v>
@@ -32708,7 +32694,7 @@
         </is>
       </c>
       <c r="K139" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
@@ -32760,7 +32746,7 @@
         </is>
       </c>
       <c r="K140" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
@@ -32812,7 +32798,7 @@
         </is>
       </c>
       <c r="K141" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
@@ -32864,7 +32850,7 @@
         </is>
       </c>
       <c r="K142" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L142" t="n">
         <v>0</v>
@@ -32916,7 +32902,7 @@
         </is>
       </c>
       <c r="K143" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L143" t="n">
         <v>0</v>
@@ -32968,7 +32954,7 @@
         </is>
       </c>
       <c r="K144" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L144" t="n">
         <v>0</v>
@@ -33020,7 +33006,7 @@
         </is>
       </c>
       <c r="K145" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L145" t="n">
         <v>0</v>
@@ -33072,7 +33058,7 @@
         </is>
       </c>
       <c r="K146" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L146" t="n">
         <v>0</v>
@@ -33124,7 +33110,7 @@
         </is>
       </c>
       <c r="K147" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L147" t="n">
         <v>0</v>
@@ -33176,7 +33162,7 @@
         </is>
       </c>
       <c r="K148" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L148" t="n">
         <v>0</v>
@@ -33228,7 +33214,7 @@
         </is>
       </c>
       <c r="K149" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L149" t="n">
         <v>0</v>
@@ -33280,7 +33266,7 @@
         </is>
       </c>
       <c r="K150" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L150" t="n">
         <v>0</v>
@@ -33332,7 +33318,7 @@
         </is>
       </c>
       <c r="K151" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="L151" t="n">
         <v>0</v>
@@ -33384,7 +33370,7 @@
         </is>
       </c>
       <c r="K152" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L152" t="n">
         <v>0</v>
@@ -33436,7 +33422,7 @@
         </is>
       </c>
       <c r="K153" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="L153" t="n">
         <v>0</v>
@@ -33488,7 +33474,7 @@
         </is>
       </c>
       <c r="K154" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="L154" t="n">
         <v>0</v>
@@ -33540,7 +33526,7 @@
         </is>
       </c>
       <c r="K155" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="L155" t="n">
         <v>0</v>
@@ -33592,7 +33578,7 @@
         </is>
       </c>
       <c r="K156" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="L156" t="n">
         <v>0</v>
@@ -33644,7 +33630,7 @@
         </is>
       </c>
       <c r="K157" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L157" t="n">
         <v>0</v>
@@ -33696,7 +33682,7 @@
         </is>
       </c>
       <c r="K158" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="L158" t="n">
         <v>0</v>
@@ -33748,7 +33734,7 @@
         </is>
       </c>
       <c r="K159" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L159" t="n">
         <v>0</v>
@@ -33800,7 +33786,7 @@
         </is>
       </c>
       <c r="K160" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L160" t="n">
         <v>0</v>
@@ -33852,7 +33838,7 @@
         </is>
       </c>
       <c r="K161" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L161" t="n">
         <v>0</v>
@@ -33904,7 +33890,7 @@
         </is>
       </c>
       <c r="K162" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L162" t="n">
         <v>0</v>
@@ -33956,7 +33942,7 @@
         </is>
       </c>
       <c r="K163" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L163" t="n">
         <v>0</v>
@@ -34008,7 +33994,7 @@
         </is>
       </c>
       <c r="K164" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L164" t="n">
         <v>0</v>
@@ -34060,7 +34046,7 @@
         </is>
       </c>
       <c r="K165" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L165" t="n">
         <v>0</v>
@@ -34112,7 +34098,7 @@
         </is>
       </c>
       <c r="K166" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L166" t="n">
         <v>0</v>
@@ -34164,7 +34150,7 @@
         </is>
       </c>
       <c r="K167" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L167" t="n">
         <v>0</v>
@@ -34216,7 +34202,7 @@
         </is>
       </c>
       <c r="K168" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L168" t="n">
         <v>0</v>
@@ -34268,7 +34254,7 @@
         </is>
       </c>
       <c r="K169" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L169" t="n">
         <v>0</v>
@@ -34320,7 +34306,7 @@
         </is>
       </c>
       <c r="K170" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L170" t="n">
         <v>0</v>
@@ -34372,7 +34358,7 @@
         </is>
       </c>
       <c r="K171" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L171" t="n">
         <v>0</v>
@@ -34424,7 +34410,7 @@
         </is>
       </c>
       <c r="K172" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L172" t="n">
         <v>0</v>
@@ -34476,7 +34462,7 @@
         </is>
       </c>
       <c r="K173" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L173" t="n">
         <v>0</v>
@@ -34528,7 +34514,7 @@
         </is>
       </c>
       <c r="K174" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L174" t="n">
         <v>0</v>
@@ -34580,7 +34566,7 @@
         </is>
       </c>
       <c r="K175" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L175" t="n">
         <v>0</v>
@@ -34632,7 +34618,7 @@
         </is>
       </c>
       <c r="K176" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L176" t="n">
         <v>0</v>
@@ -34684,7 +34670,7 @@
         </is>
       </c>
       <c r="K177" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L177" t="n">
         <v>0</v>
@@ -34736,7 +34722,7 @@
         </is>
       </c>
       <c r="K178" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L178" t="n">
         <v>0</v>
@@ -34788,7 +34774,7 @@
         </is>
       </c>
       <c r="K179" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L179" t="n">
         <v>0</v>
@@ -34840,7 +34826,7 @@
         </is>
       </c>
       <c r="K180" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L180" t="n">
         <v>0</v>
@@ -34892,7 +34878,7 @@
         </is>
       </c>
       <c r="K181" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L181" t="n">
         <v>0</v>
@@ -34944,7 +34930,7 @@
         </is>
       </c>
       <c r="K182" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L182" t="n">
         <v>0</v>
@@ -34996,7 +34982,7 @@
         </is>
       </c>
       <c r="K183" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L183" t="n">
         <v>0</v>
@@ -35048,7 +35034,7 @@
         </is>
       </c>
       <c r="K184" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L184" t="n">
         <v>0</v>
@@ -35100,7 +35086,7 @@
         </is>
       </c>
       <c r="K185" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L185" t="n">
         <v>0</v>
@@ -35152,7 +35138,7 @@
         </is>
       </c>
       <c r="K186" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L186" t="n">
         <v>0</v>
@@ -35204,7 +35190,7 @@
         </is>
       </c>
       <c r="K187" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L187" t="n">
         <v>0</v>
@@ -35256,7 +35242,7 @@
         </is>
       </c>
       <c r="K188" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L188" t="n">
         <v>0</v>
@@ -35308,7 +35294,7 @@
         </is>
       </c>
       <c r="K189" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L189" t="n">
         <v>0</v>
@@ -35360,7 +35346,7 @@
         </is>
       </c>
       <c r="K190" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L190" t="n">
         <v>0</v>
@@ -35412,7 +35398,7 @@
         </is>
       </c>
       <c r="K191" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L191" t="n">
         <v>0</v>
@@ -35464,7 +35450,7 @@
         </is>
       </c>
       <c r="K192" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L192" t="n">
         <v>0</v>
@@ -35516,7 +35502,7 @@
         </is>
       </c>
       <c r="K193" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L193" t="n">
         <v>0</v>
@@ -35568,7 +35554,7 @@
         </is>
       </c>
       <c r="K194" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L194" t="n">
         <v>0</v>
@@ -35620,7 +35606,7 @@
         </is>
       </c>
       <c r="K195" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L195" t="n">
         <v>0</v>
@@ -35672,7 +35658,7 @@
         </is>
       </c>
       <c r="K196" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L196" t="n">
         <v>0</v>
@@ -35724,7 +35710,7 @@
         </is>
       </c>
       <c r="K197" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L197" t="n">
         <v>0</v>
@@ -35776,7 +35762,7 @@
         </is>
       </c>
       <c r="K198" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L198" t="n">
         <v>0</v>
@@ -35828,7 +35814,7 @@
         </is>
       </c>
       <c r="K199" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L199" t="n">
         <v>0</v>
@@ -35880,7 +35866,7 @@
         </is>
       </c>
       <c r="K200" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L200" t="n">
         <v>0</v>
@@ -35932,7 +35918,7 @@
         </is>
       </c>
       <c r="K201" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L201" t="n">
         <v>0</v>
@@ -35984,7 +35970,7 @@
         </is>
       </c>
       <c r="K202" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L202" t="n">
         <v>0</v>
@@ -36036,7 +36022,7 @@
         </is>
       </c>
       <c r="K203" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L203" t="n">
         <v>0</v>
@@ -36088,7 +36074,7 @@
         </is>
       </c>
       <c r="K204" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L204" t="n">
         <v>0</v>
@@ -36140,7 +36126,7 @@
         </is>
       </c>
       <c r="K205" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L205" t="n">
         <v>0</v>
@@ -36192,7 +36178,7 @@
         </is>
       </c>
       <c r="K206" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L206" t="n">
         <v>0</v>
@@ -36244,7 +36230,7 @@
         </is>
       </c>
       <c r="K207" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L207" t="n">
         <v>0</v>
@@ -36296,7 +36282,7 @@
         </is>
       </c>
       <c r="K208" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="L208" t="n">
         <v>0</v>
@@ -36348,7 +36334,7 @@
         </is>
       </c>
       <c r="K209" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="L209" t="n">
         <v>0</v>
@@ -36400,7 +36386,7 @@
         </is>
       </c>
       <c r="K210" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="L210" t="n">
         <v>0</v>
@@ -36452,7 +36438,7 @@
         </is>
       </c>
       <c r="K211" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="L211" t="n">
         <v>0</v>
@@ -36504,7 +36490,7 @@
         </is>
       </c>
       <c r="K212" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="L212" t="n">
         <v>0</v>
@@ -36556,7 +36542,7 @@
         </is>
       </c>
       <c r="K213" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="L213" t="n">
         <v>0</v>
@@ -36608,7 +36594,7 @@
         </is>
       </c>
       <c r="K214" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L214" t="n">
         <v>0</v>
@@ -36660,7 +36646,7 @@
         </is>
       </c>
       <c r="K215" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="L215" t="n">
         <v>0</v>
@@ -36712,7 +36698,7 @@
         </is>
       </c>
       <c r="K216" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="L216" t="n">
         <v>0</v>
@@ -36764,7 +36750,7 @@
         </is>
       </c>
       <c r="K217" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L217" t="n">
         <v>0</v>
@@ -36816,7 +36802,7 @@
         </is>
       </c>
       <c r="K218" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L218" t="n">
         <v>0</v>
@@ -36868,7 +36854,7 @@
         </is>
       </c>
       <c r="K219" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L219" t="n">
         <v>0</v>
@@ -36920,7 +36906,7 @@
         </is>
       </c>
       <c r="K220" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L220" t="n">
         <v>0</v>
@@ -36972,7 +36958,7 @@
         </is>
       </c>
       <c r="K221" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L221" t="n">
         <v>0</v>
@@ -37024,7 +37010,7 @@
         </is>
       </c>
       <c r="K222" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L222" t="n">
         <v>0</v>
@@ -37076,7 +37062,7 @@
         </is>
       </c>
       <c r="K223" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L223" t="n">
         <v>0</v>
@@ -37128,7 +37114,7 @@
         </is>
       </c>
       <c r="K224" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L224" t="n">
         <v>0</v>
@@ -37180,7 +37166,7 @@
         </is>
       </c>
       <c r="K225" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L225" t="n">
         <v>0</v>
@@ -37232,7 +37218,7 @@
         </is>
       </c>
       <c r="K226" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L226" t="n">
         <v>0</v>
@@ -37284,7 +37270,7 @@
         </is>
       </c>
       <c r="K227" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L227" t="n">
         <v>0</v>
@@ -37336,7 +37322,7 @@
         </is>
       </c>
       <c r="K228" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L228" t="n">
         <v>0</v>
@@ -37388,7 +37374,7 @@
         </is>
       </c>
       <c r="K229" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L229" t="n">
         <v>0</v>
@@ -37440,7 +37426,7 @@
         </is>
       </c>
       <c r="K230" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L230" t="n">
         <v>0</v>
@@ -37492,7 +37478,7 @@
         </is>
       </c>
       <c r="K231" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L231" t="n">
         <v>0</v>
@@ -37544,7 +37530,7 @@
         </is>
       </c>
       <c r="K232" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L232" t="n">
         <v>0</v>
@@ -37596,7 +37582,7 @@
         </is>
       </c>
       <c r="K233" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L233" t="n">
         <v>0</v>
@@ -37648,7 +37634,7 @@
         </is>
       </c>
       <c r="K234" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L234" t="n">
         <v>0</v>
@@ -37700,7 +37686,7 @@
         </is>
       </c>
       <c r="K235" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L235" t="n">
         <v>0</v>
@@ -37752,7 +37738,7 @@
         </is>
       </c>
       <c r="K236" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L236" t="n">
         <v>0</v>
@@ -37804,7 +37790,7 @@
         </is>
       </c>
       <c r="K237" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L237" t="n">
         <v>0</v>
@@ -37856,7 +37842,7 @@
         </is>
       </c>
       <c r="K238" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L238" t="n">
         <v>0</v>
@@ -37908,7 +37894,7 @@
         </is>
       </c>
       <c r="K239" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="L239" t="n">
         <v>0</v>
@@ -37960,7 +37946,7 @@
         </is>
       </c>
       <c r="K240" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L240" t="n">
         <v>0</v>
@@ -38012,7 +37998,7 @@
         </is>
       </c>
       <c r="K241" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L241" t="n">
         <v>0</v>
@@ -38064,7 +38050,7 @@
         </is>
       </c>
       <c r="K242" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L242" t="n">
         <v>0</v>
@@ -38116,7 +38102,7 @@
         </is>
       </c>
       <c r="K243" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="L243" t="n">
         <v>0</v>
@@ -38168,7 +38154,7 @@
         </is>
       </c>
       <c r="K244" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="L244" t="n">
         <v>0</v>
@@ -38220,7 +38206,7 @@
         </is>
       </c>
       <c r="K245" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="L245" t="n">
         <v>0</v>
@@ -38272,7 +38258,7 @@
         </is>
       </c>
       <c r="K246" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="L246" t="n">
         <v>0</v>
@@ -38324,7 +38310,7 @@
         </is>
       </c>
       <c r="K247" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="L247" t="n">
         <v>0</v>
@@ -38376,7 +38362,7 @@
         </is>
       </c>
       <c r="K248" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="L248" t="n">
         <v>0</v>
@@ -38428,7 +38414,7 @@
         </is>
       </c>
       <c r="K249" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="L249" t="n">
         <v>0</v>
@@ -38480,7 +38466,7 @@
         </is>
       </c>
       <c r="K250" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="L250" t="n">
         <v>0</v>
@@ -38532,7 +38518,7 @@
         </is>
       </c>
       <c r="K251" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="L251" t="n">
         <v>0</v>
@@ -38584,7 +38570,7 @@
         </is>
       </c>
       <c r="K252" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="L252" t="n">
         <v>0</v>
@@ -38636,7 +38622,7 @@
         </is>
       </c>
       <c r="K253" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="L253" t="n">
         <v>0</v>
@@ -38688,7 +38674,7 @@
         </is>
       </c>
       <c r="K254" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="L254" t="n">
         <v>0</v>
@@ -38740,7 +38726,7 @@
         </is>
       </c>
       <c r="K255" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="L255" t="n">
         <v>0</v>
@@ -38792,7 +38778,7 @@
         </is>
       </c>
       <c r="K256" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L256" t="n">
         <v>0</v>
@@ -38844,7 +38830,7 @@
         </is>
       </c>
       <c r="K257" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="L257" t="n">
         <v>0</v>
@@ -38896,7 +38882,7 @@
         </is>
       </c>
       <c r="K258" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="L258" t="n">
         <v>0</v>
@@ -38948,7 +38934,7 @@
         </is>
       </c>
       <c r="K259" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="L259" t="n">
         <v>0</v>
@@ -39000,7 +38986,7 @@
         </is>
       </c>
       <c r="K260" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="L260" t="n">
         <v>0</v>
@@ -39052,7 +39038,7 @@
         </is>
       </c>
       <c r="K261" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L261" t="n">
         <v>0</v>
@@ -39104,7 +39090,7 @@
         </is>
       </c>
       <c r="K262" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="L262" t="n">
         <v>0</v>
@@ -39156,7 +39142,7 @@
         </is>
       </c>
       <c r="K263" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="L263" t="n">
         <v>0</v>
@@ -39208,7 +39194,7 @@
         </is>
       </c>
       <c r="K264" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L264" t="n">
         <v>0</v>
@@ -39260,7 +39246,7 @@
         </is>
       </c>
       <c r="K265" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="L265" t="n">
         <v>0</v>
@@ -39312,7 +39298,7 @@
         </is>
       </c>
       <c r="K266" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="L266" t="n">
         <v>0</v>
@@ -39364,7 +39350,7 @@
         </is>
       </c>
       <c r="K267" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L267" t="n">
         <v>0</v>
@@ -39416,7 +39402,7 @@
         </is>
       </c>
       <c r="K268" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L268" t="n">
         <v>0</v>
@@ -39468,7 +39454,7 @@
         </is>
       </c>
       <c r="K269" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L269" t="n">
         <v>0</v>
@@ -39520,7 +39506,7 @@
         </is>
       </c>
       <c r="K270" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="L270" t="n">
         <v>0</v>
@@ -39572,7 +39558,7 @@
         </is>
       </c>
       <c r="K271" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L271" t="n">
         <v>0</v>
@@ -39624,7 +39610,7 @@
         </is>
       </c>
       <c r="K272" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L272" t="n">
         <v>0</v>
@@ -39676,7 +39662,7 @@
         </is>
       </c>
       <c r="K273" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L273" t="n">
         <v>0</v>
@@ -39728,7 +39714,7 @@
         </is>
       </c>
       <c r="K274" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="L274" t="n">
         <v>0</v>
@@ -39780,7 +39766,7 @@
         </is>
       </c>
       <c r="K275" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="L275" t="n">
         <v>0</v>
@@ -39832,7 +39818,7 @@
         </is>
       </c>
       <c r="K276" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="L276" t="n">
         <v>0</v>
@@ -39884,7 +39870,7 @@
         </is>
       </c>
       <c r="K277" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="L277" t="n">
         <v>0</v>
@@ -39936,7 +39922,7 @@
         </is>
       </c>
       <c r="K278" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="L278" t="n">
         <v>0</v>
@@ -39988,7 +39974,7 @@
         </is>
       </c>
       <c r="K279" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="L279" t="n">
         <v>0</v>
@@ -40040,7 +40026,7 @@
         </is>
       </c>
       <c r="K280" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L280" t="n">
         <v>0</v>
@@ -40092,7 +40078,7 @@
         </is>
       </c>
       <c r="K281" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="L281" t="n">
         <v>0</v>
@@ -40144,7 +40130,7 @@
         </is>
       </c>
       <c r="K282" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="L282" t="n">
         <v>0</v>
@@ -40196,7 +40182,7 @@
         </is>
       </c>
       <c r="K283" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L283" t="n">
         <v>0</v>
@@ -40248,7 +40234,7 @@
         </is>
       </c>
       <c r="K284" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="L284" t="n">
         <v>0</v>
@@ -40300,7 +40286,7 @@
         </is>
       </c>
       <c r="K285" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="L285" t="n">
         <v>0</v>
@@ -40352,7 +40338,7 @@
         </is>
       </c>
       <c r="K286" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="L286" t="n">
         <v>0</v>
@@ -40404,7 +40390,7 @@
         </is>
       </c>
       <c r="K287" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L287" t="n">
         <v>0</v>
@@ -40456,7 +40442,7 @@
         </is>
       </c>
       <c r="K288" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L288" t="n">
         <v>0</v>
@@ -40508,7 +40494,7 @@
         </is>
       </c>
       <c r="K289" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L289" t="n">
         <v>0</v>
@@ -40560,7 +40546,7 @@
         </is>
       </c>
       <c r="K290" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="L290" t="n">
         <v>0</v>
@@ -40612,7 +40598,7 @@
         </is>
       </c>
       <c r="K291" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L291" t="n">
         <v>0</v>
@@ -40664,7 +40650,7 @@
         </is>
       </c>
       <c r="K292" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="L292" t="n">
         <v>0</v>
@@ -40716,7 +40702,7 @@
         </is>
       </c>
       <c r="K293" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="L293" t="n">
         <v>0</v>
@@ -40768,7 +40754,7 @@
         </is>
       </c>
       <c r="K294" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="L294" t="n">
         <v>0</v>
@@ -40820,7 +40806,7 @@
         </is>
       </c>
       <c r="K295" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="L295" t="n">
         <v>0</v>
@@ -40872,7 +40858,7 @@
         </is>
       </c>
       <c r="K296" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="L296" t="n">
         <v>0</v>
@@ -40924,7 +40910,7 @@
         </is>
       </c>
       <c r="K297" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="L297" t="n">
         <v>0</v>
@@ -40976,7 +40962,7 @@
         </is>
       </c>
       <c r="K298" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="L298" t="n">
         <v>0</v>
@@ -41028,7 +41014,7 @@
         </is>
       </c>
       <c r="K299" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="L299" t="n">
         <v>0</v>
@@ -41080,7 +41066,7 @@
         </is>
       </c>
       <c r="K300" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="L300" t="n">
         <v>0</v>
@@ -41132,7 +41118,7 @@
         </is>
       </c>
       <c r="K301" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="L301" t="n">
         <v>0</v>
@@ -41184,7 +41170,7 @@
         </is>
       </c>
       <c r="K302" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="L302" t="n">
         <v>0</v>
@@ -41236,7 +41222,7 @@
         </is>
       </c>
       <c r="K303" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="L303" t="n">
         <v>0</v>
@@ -41288,7 +41274,7 @@
         </is>
       </c>
       <c r="K304" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="L304" t="n">
         <v>0</v>
@@ -41340,7 +41326,7 @@
         </is>
       </c>
       <c r="K305" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="L305" t="n">
         <v>0</v>
@@ -41392,7 +41378,7 @@
         </is>
       </c>
       <c r="K306" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="L306" t="n">
         <v>0</v>
@@ -41444,7 +41430,7 @@
         </is>
       </c>
       <c r="K307" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="L307" t="n">
         <v>0</v>
@@ -41496,7 +41482,7 @@
         </is>
       </c>
       <c r="K308" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="L308" t="n">
         <v>0</v>
@@ -41548,7 +41534,7 @@
         </is>
       </c>
       <c r="K309" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="L309" t="n">
         <v>0</v>
@@ -41600,7 +41586,7 @@
         </is>
       </c>
       <c r="K310" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="L310" t="n">
         <v>0</v>
@@ -41652,7 +41638,7 @@
         </is>
       </c>
       <c r="K311" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="L311" t="n">
         <v>0</v>
@@ -41704,7 +41690,7 @@
         </is>
       </c>
       <c r="K312" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="L312" t="n">
         <v>0</v>
@@ -41756,7 +41742,7 @@
         </is>
       </c>
       <c r="K313" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="L313" t="n">
         <v>0</v>
@@ -41808,7 +41794,7 @@
         </is>
       </c>
       <c r="K314" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="L314" t="n">
         <v>0</v>
@@ -41860,7 +41846,7 @@
         </is>
       </c>
       <c r="K315" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="L315" t="n">
         <v>0</v>
@@ -41912,7 +41898,7 @@
         </is>
       </c>
       <c r="K316" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="L316" t="n">
         <v>0</v>
@@ -41964,7 +41950,7 @@
         </is>
       </c>
       <c r="K317" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="L317" t="n">
         <v>0</v>
@@ -42016,7 +42002,7 @@
         </is>
       </c>
       <c r="K318" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L318" t="n">
         <v>0</v>
@@ -42068,7 +42054,7 @@
         </is>
       </c>
       <c r="K319" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L319" t="n">
         <v>0</v>
@@ -42120,7 +42106,7 @@
         </is>
       </c>
       <c r="K320" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="L320" t="n">
         <v>0</v>
@@ -42172,7 +42158,7 @@
         </is>
       </c>
       <c r="K321" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="L321" t="n">
         <v>0</v>
@@ -42224,7 +42210,7 @@
         </is>
       </c>
       <c r="K322" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="L322" t="n">
         <v>0</v>
@@ -42276,7 +42262,7 @@
         </is>
       </c>
       <c r="K323" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="L323" t="n">
         <v>0</v>
@@ -42328,7 +42314,7 @@
         </is>
       </c>
       <c r="K324" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="L324" t="n">
         <v>0</v>
@@ -42380,7 +42366,7 @@
         </is>
       </c>
       <c r="K325" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="L325" t="n">
         <v>0</v>
@@ -42432,7 +42418,7 @@
         </is>
       </c>
       <c r="K326" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="L326" t="n">
         <v>0</v>
@@ -42484,7 +42470,7 @@
         </is>
       </c>
       <c r="K327" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="L327" t="n">
         <v>0</v>
@@ -42536,7 +42522,7 @@
         </is>
       </c>
       <c r="K328" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="L328" t="n">
         <v>0</v>
@@ -42588,7 +42574,7 @@
         </is>
       </c>
       <c r="K329" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="L329" t="n">
         <v>0</v>
@@ -42640,7 +42626,7 @@
         </is>
       </c>
       <c r="K330" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="L330" t="n">
         <v>0</v>
@@ -42692,7 +42678,7 @@
         </is>
       </c>
       <c r="K331" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="L331" t="n">
         <v>0</v>
@@ -42744,7 +42730,7 @@
         </is>
       </c>
       <c r="K332" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="L332" t="n">
         <v>0</v>
@@ -42796,7 +42782,7 @@
         </is>
       </c>
       <c r="K333" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="L333" t="n">
         <v>0</v>
@@ -42848,7 +42834,7 @@
         </is>
       </c>
       <c r="K334" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="L334" t="n">
         <v>0</v>
@@ -42900,7 +42886,7 @@
         </is>
       </c>
       <c r="K335" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="L335" t="n">
         <v>0</v>
@@ -42952,7 +42938,7 @@
         </is>
       </c>
       <c r="K336" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="L336" t="n">
         <v>0</v>
@@ -43004,7 +42990,7 @@
         </is>
       </c>
       <c r="K337" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="L337" t="n">
         <v>0</v>
@@ -43056,7 +43042,7 @@
         </is>
       </c>
       <c r="K338" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="L338" t="n">
         <v>0</v>
@@ -43108,7 +43094,7 @@
         </is>
       </c>
       <c r="K339" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="L339" t="n">
         <v>0</v>
@@ -43160,7 +43146,7 @@
         </is>
       </c>
       <c r="K340" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="L340" t="n">
         <v>0</v>
@@ -43212,7 +43198,7 @@
         </is>
       </c>
       <c r="K341" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="L341" t="n">
         <v>0</v>
@@ -43264,7 +43250,7 @@
         </is>
       </c>
       <c r="K342" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="L342" t="n">
         <v>0</v>
@@ -43316,7 +43302,7 @@
         </is>
       </c>
       <c r="K343" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="L343" t="n">
         <v>0</v>
@@ -43368,7 +43354,7 @@
         </is>
       </c>
       <c r="K344" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="L344" t="n">
         <v>0</v>
@@ -43420,7 +43406,7 @@
         </is>
       </c>
       <c r="K345" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="L345" t="n">
         <v>0</v>
@@ -43472,7 +43458,7 @@
         </is>
       </c>
       <c r="K346" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="L346" t="n">
         <v>0</v>
@@ -43524,7 +43510,7 @@
         </is>
       </c>
       <c r="K347" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="L347" t="n">
         <v>0</v>
@@ -43576,7 +43562,7 @@
         </is>
       </c>
       <c r="K348" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="L348" t="n">
         <v>0</v>
@@ -43628,7 +43614,7 @@
         </is>
       </c>
       <c r="K349" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="L349" t="n">
         <v>0</v>
@@ -43680,7 +43666,7 @@
         </is>
       </c>
       <c r="K350" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="L350" t="n">
         <v>0</v>
@@ -43732,7 +43718,7 @@
         </is>
       </c>
       <c r="K351" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="L351" t="n">
         <v>0</v>
@@ -43784,7 +43770,7 @@
         </is>
       </c>
       <c r="K352" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="L352" t="n">
         <v>0</v>
@@ -43836,7 +43822,7 @@
         </is>
       </c>
       <c r="K353" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="L353" t="n">
         <v>0</v>
@@ -43888,7 +43874,7 @@
         </is>
       </c>
       <c r="K354" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="L354" t="n">
         <v>0</v>
@@ -43940,7 +43926,7 @@
         </is>
       </c>
       <c r="K355" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="L355" t="n">
         <v>0</v>
@@ -43992,7 +43978,7 @@
         </is>
       </c>
       <c r="K356" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="L356" t="n">
         <v>0</v>
@@ -44044,7 +44030,7 @@
         </is>
       </c>
       <c r="K357" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L357" t="n">
         <v>0</v>
@@ -44096,7 +44082,7 @@
         </is>
       </c>
       <c r="K358" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L358" t="n">
         <v>0</v>
@@ -44148,7 +44134,7 @@
         </is>
       </c>
       <c r="K359" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L359" t="n">
         <v>0</v>
@@ -44200,7 +44186,7 @@
         </is>
       </c>
       <c r="K360" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="L360" t="n">
         <v>0</v>
@@ -44252,7 +44238,7 @@
         </is>
       </c>
       <c r="K361" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="L361" t="n">
         <v>0</v>
@@ -44304,7 +44290,7 @@
         </is>
       </c>
       <c r="K362" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="L362" t="n">
         <v>0</v>
@@ -44356,7 +44342,7 @@
         </is>
       </c>
       <c r="K363" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="L363" t="n">
         <v>0</v>
@@ -44408,7 +44394,7 @@
         </is>
       </c>
       <c r="K364" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="L364" t="n">
         <v>0</v>
@@ -44460,7 +44446,7 @@
         </is>
       </c>
       <c r="K365" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="L365" t="n">
         <v>0</v>
@@ -44512,7 +44498,7 @@
         </is>
       </c>
       <c r="K366" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="L366" t="n">
         <v>0</v>
@@ -44564,7 +44550,7 @@
         </is>
       </c>
       <c r="K367" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="L367" t="n">
         <v>0</v>
@@ -44616,7 +44602,7 @@
         </is>
       </c>
       <c r="K368" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="L368" t="n">
         <v>0</v>
@@ -44668,7 +44654,7 @@
         </is>
       </c>
       <c r="K369" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="L369" t="n">
         <v>0</v>
@@ -44720,7 +44706,7 @@
         </is>
       </c>
       <c r="K370" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="L370" t="n">
         <v>0</v>
@@ -44772,7 +44758,7 @@
         </is>
       </c>
       <c r="K371" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="L371" t="n">
         <v>0</v>
@@ -44824,7 +44810,7 @@
         </is>
       </c>
       <c r="K372" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="L372" t="n">
         <v>0</v>
@@ -44876,7 +44862,7 @@
         </is>
       </c>
       <c r="K373" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="L373" t="n">
         <v>0</v>
@@ -44928,7 +44914,7 @@
         </is>
       </c>
       <c r="K374" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="L374" t="n">
         <v>0</v>
@@ -44980,7 +44966,7 @@
         </is>
       </c>
       <c r="K375" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="L375" t="n">
         <v>0</v>
@@ -45032,7 +45018,7 @@
         </is>
       </c>
       <c r="K376" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="L376" t="n">
         <v>0</v>
@@ -45084,7 +45070,7 @@
         </is>
       </c>
       <c r="K377" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="L377" t="n">
         <v>0</v>
@@ -45136,7 +45122,7 @@
         </is>
       </c>
       <c r="K378" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="L378" t="n">
         <v>0</v>
@@ -45188,7 +45174,7 @@
         </is>
       </c>
       <c r="K379" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="L379" t="n">
         <v>0</v>
@@ -45240,7 +45226,7 @@
         </is>
       </c>
       <c r="K380" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="L380" t="n">
         <v>0</v>
@@ -45292,7 +45278,7 @@
         </is>
       </c>
       <c r="K381" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="L381" t="n">
         <v>0</v>
@@ -45344,7 +45330,7 @@
         </is>
       </c>
       <c r="K382" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="L382" t="n">
         <v>0</v>
@@ -45396,7 +45382,7 @@
         </is>
       </c>
       <c r="K383" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="L383" t="n">
         <v>0</v>
@@ -45448,7 +45434,7 @@
         </is>
       </c>
       <c r="K384" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="L384" t="n">
         <v>0</v>
@@ -45500,7 +45486,7 @@
         </is>
       </c>
       <c r="K385" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="L385" t="n">
         <v>0</v>
@@ -45552,7 +45538,7 @@
         </is>
       </c>
       <c r="K386" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="L386" t="n">
         <v>0</v>
@@ -45604,7 +45590,7 @@
         </is>
       </c>
       <c r="K387" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="L387" t="n">
         <v>0</v>
@@ -45656,7 +45642,7 @@
         </is>
       </c>
       <c r="K388" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="L388" t="n">
         <v>0</v>
@@ -45708,7 +45694,7 @@
         </is>
       </c>
       <c r="K389" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="L389" t="n">
         <v>0</v>
@@ -45760,7 +45746,7 @@
         </is>
       </c>
       <c r="K390" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="L390" t="n">
         <v>0</v>
@@ -45812,7 +45798,7 @@
         </is>
       </c>
       <c r="K391" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="L391" t="n">
         <v>0</v>
@@ -45864,7 +45850,7 @@
         </is>
       </c>
       <c r="K392" t="n">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="L392" t="n">
         <v>0</v>
@@ -45916,7 +45902,7 @@
         </is>
       </c>
       <c r="K393" t="n">
-        <v>233</v>
+        <v>0</v>
       </c>
       <c r="L393" t="n">
         <v>0</v>
@@ -45968,7 +45954,7 @@
         </is>
       </c>
       <c r="K394" t="n">
-        <v>227</v>
+        <v>0</v>
       </c>
       <c r="L394" t="n">
         <v>0</v>
@@ -46020,7 +46006,7 @@
         </is>
       </c>
       <c r="K395" t="n">
-        <v>243</v>
+        <v>0</v>
       </c>
       <c r="L395" t="n">
         <v>0</v>
@@ -46072,7 +46058,7 @@
         </is>
       </c>
       <c r="K396" t="n">
-        <v>205</v>
+        <v>0</v>
       </c>
       <c r="L396" t="n">
         <v>0</v>
@@ -46124,7 +46110,7 @@
         </is>
       </c>
       <c r="K397" t="n">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="L397" t="n">
         <v>0</v>
@@ -46176,7 +46162,7 @@
         </is>
       </c>
       <c r="K398" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="L398" t="n">
         <v>0</v>
@@ -46228,7 +46214,7 @@
         </is>
       </c>
       <c r="K399" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="L399" t="n">
         <v>0</v>
@@ -46280,7 +46266,7 @@
         </is>
       </c>
       <c r="K400" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="L400" t="n">
         <v>0</v>
@@ -46332,7 +46318,7 @@
         </is>
       </c>
       <c r="K401" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="L401" t="n">
         <v>0</v>
@@ -46384,7 +46370,7 @@
         </is>
       </c>
       <c r="K402" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="L402" t="n">
         <v>0</v>
@@ -46436,7 +46422,7 @@
         </is>
       </c>
       <c r="K403" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="L403" t="n">
         <v>0</v>
@@ -46488,7 +46474,7 @@
         </is>
       </c>
       <c r="K404" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="L404" t="n">
         <v>0</v>
@@ -46540,7 +46526,7 @@
         </is>
       </c>
       <c r="K405" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="L405" t="n">
         <v>0</v>
@@ -46592,7 +46578,7 @@
         </is>
       </c>
       <c r="K406" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="L406" t="n">
         <v>0</v>
@@ -46644,7 +46630,7 @@
         </is>
       </c>
       <c r="K407" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="L407" t="n">
         <v>0</v>
@@ -46696,7 +46682,7 @@
         </is>
       </c>
       <c r="K408" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="L408" t="n">
         <v>0</v>
@@ -46748,7 +46734,7 @@
         </is>
       </c>
       <c r="K409" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="L409" t="n">
         <v>0</v>
@@ -46800,7 +46786,7 @@
         </is>
       </c>
       <c r="K410" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="L410" t="n">
         <v>0</v>
@@ -46852,7 +46838,7 @@
         </is>
       </c>
       <c r="K411" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="L411" t="n">
         <v>0</v>
@@ -46904,7 +46890,7 @@
         </is>
       </c>
       <c r="K412" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="L412" t="n">
         <v>0</v>
@@ -46956,7 +46942,7 @@
         </is>
       </c>
       <c r="K413" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="L413" t="n">
         <v>0</v>
@@ -47008,7 +46994,7 @@
         </is>
       </c>
       <c r="K414" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="L414" t="n">
         <v>0</v>
@@ -47060,7 +47046,7 @@
         </is>
       </c>
       <c r="K415" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="L415" t="n">
         <v>0</v>
@@ -47112,7 +47098,7 @@
         </is>
       </c>
       <c r="K416" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="L416" t="n">
         <v>0</v>
@@ -47164,7 +47150,7 @@
         </is>
       </c>
       <c r="K417" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="L417" t="n">
         <v>0</v>
@@ -47216,7 +47202,7 @@
         </is>
       </c>
       <c r="K418" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="L418" t="n">
         <v>0</v>
@@ -47268,7 +47254,7 @@
         </is>
       </c>
       <c r="K419" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="L419" t="n">
         <v>0</v>
@@ -47320,7 +47306,7 @@
         </is>
       </c>
       <c r="K420" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="L420" t="n">
         <v>0</v>
@@ -47372,7 +47358,7 @@
         </is>
       </c>
       <c r="K421" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="L421" t="n">
         <v>0</v>
@@ -47424,7 +47410,7 @@
         </is>
       </c>
       <c r="K422" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="L422" t="n">
         <v>0</v>
@@ -47476,7 +47462,7 @@
         </is>
       </c>
       <c r="K423" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="L423" t="n">
         <v>0</v>
@@ -47528,7 +47514,7 @@
         </is>
       </c>
       <c r="K424" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="L424" t="n">
         <v>0</v>
@@ -47580,7 +47566,7 @@
         </is>
       </c>
       <c r="K425" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="L425" t="n">
         <v>0</v>
@@ -47632,7 +47618,7 @@
         </is>
       </c>
       <c r="K426" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="L426" t="n">
         <v>0</v>
@@ -47684,7 +47670,7 @@
         </is>
       </c>
       <c r="K427" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="L427" t="n">
         <v>0</v>
@@ -47736,7 +47722,7 @@
         </is>
       </c>
       <c r="K428" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="L428" t="n">
         <v>0</v>
@@ -47788,7 +47774,7 @@
         </is>
       </c>
       <c r="K429" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="L429" t="n">
         <v>0</v>
@@ -47840,7 +47826,7 @@
         </is>
       </c>
       <c r="K430" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="L430" t="n">
         <v>0</v>
@@ -47892,7 +47878,7 @@
         </is>
       </c>
       <c r="K431" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="L431" t="n">
         <v>0</v>
@@ -47944,7 +47930,7 @@
         </is>
       </c>
       <c r="K432" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="L432" t="n">
         <v>0</v>
@@ -47996,7 +47982,7 @@
         </is>
       </c>
       <c r="K433" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="L433" t="n">
         <v>0</v>
@@ -48048,7 +48034,7 @@
         </is>
       </c>
       <c r="K434" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="L434" t="n">
         <v>0</v>
@@ -48100,7 +48086,7 @@
         </is>
       </c>
       <c r="K435" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="L435" t="n">
         <v>0</v>
@@ -48152,7 +48138,7 @@
         </is>
       </c>
       <c r="K436" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="L436" t="n">
         <v>0</v>
@@ -48204,7 +48190,7 @@
         </is>
       </c>
       <c r="K437" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="L437" t="n">
         <v>0</v>
@@ -48256,7 +48242,7 @@
         </is>
       </c>
       <c r="K438" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="L438" t="n">
         <v>0</v>
@@ -48308,7 +48294,7 @@
         </is>
       </c>
       <c r="K439" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="L439" t="n">
         <v>0</v>
@@ -48360,7 +48346,7 @@
         </is>
       </c>
       <c r="K440" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="L440" t="n">
         <v>0</v>
@@ -48412,7 +48398,7 @@
         </is>
       </c>
       <c r="K441" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="L441" t="n">
         <v>0</v>
@@ -48464,7 +48450,7 @@
         </is>
       </c>
       <c r="K442" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="L442" t="n">
         <v>0</v>
@@ -48516,7 +48502,7 @@
         </is>
       </c>
       <c r="K443" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="L443" t="n">
         <v>0</v>
@@ -48568,7 +48554,7 @@
         </is>
       </c>
       <c r="K444" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="L444" t="n">
         <v>0</v>
@@ -48620,7 +48606,7 @@
         </is>
       </c>
       <c r="K445" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="L445" t="n">
         <v>0</v>
@@ -48672,7 +48658,7 @@
         </is>
       </c>
       <c r="K446" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="L446" t="n">
         <v>0</v>
@@ -48724,7 +48710,7 @@
         </is>
       </c>
       <c r="K447" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="L447" t="n">
         <v>0</v>
@@ -48776,7 +48762,7 @@
         </is>
       </c>
       <c r="K448" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="L448" t="n">
         <v>0</v>
@@ -48828,7 +48814,7 @@
         </is>
       </c>
       <c r="K449" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="L449" t="n">
         <v>0</v>
@@ -48880,7 +48866,7 @@
         </is>
       </c>
       <c r="K450" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="L450" t="n">
         <v>0</v>
@@ -48932,7 +48918,7 @@
         </is>
       </c>
       <c r="K451" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="L451" t="n">
         <v>0</v>
@@ -48984,7 +48970,7 @@
         </is>
       </c>
       <c r="K452" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="L452" t="n">
         <v>0</v>
@@ -49036,7 +49022,7 @@
         </is>
       </c>
       <c r="K453" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="L453" t="n">
         <v>0</v>
@@ -49088,7 +49074,7 @@
         </is>
       </c>
       <c r="K454" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="L454" t="n">
         <v>0</v>
@@ -49140,7 +49126,7 @@
         </is>
       </c>
       <c r="K455" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="L455" t="n">
         <v>0</v>
@@ -49192,7 +49178,7 @@
         </is>
       </c>
       <c r="K456" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="L456" t="n">
         <v>0</v>
@@ -49244,7 +49230,7 @@
         </is>
       </c>
       <c r="K457" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="L457" t="n">
         <v>0</v>
@@ -49296,7 +49282,7 @@
         </is>
       </c>
       <c r="K458" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="L458" t="n">
         <v>0</v>
@@ -49348,7 +49334,7 @@
         </is>
       </c>
       <c r="K459" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="L459" t="n">
         <v>0</v>
@@ -49400,7 +49386,7 @@
         </is>
       </c>
       <c r="K460" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="L460" t="n">
         <v>0</v>
@@ -49452,7 +49438,7 @@
         </is>
       </c>
       <c r="K461" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="L461" t="n">
         <v>0</v>
@@ -49504,7 +49490,7 @@
         </is>
       </c>
       <c r="K462" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="L462" t="n">
         <v>0</v>
@@ -49556,7 +49542,7 @@
         </is>
       </c>
       <c r="K463" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="L463" t="n">
         <v>0</v>
@@ -49608,7 +49594,7 @@
         </is>
       </c>
       <c r="K464" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="L464" t="n">
         <v>0</v>
@@ -49660,7 +49646,7 @@
         </is>
       </c>
       <c r="K465" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="L465" t="n">
         <v>0</v>
@@ -49712,7 +49698,7 @@
         </is>
       </c>
       <c r="K466" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="L466" t="n">
         <v>0</v>
@@ -49764,7 +49750,7 @@
         </is>
       </c>
       <c r="K467" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="L467" t="n">
         <v>0</v>
@@ -49816,7 +49802,7 @@
         </is>
       </c>
       <c r="K468" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="L468" t="n">
         <v>0</v>
@@ -49868,7 +49854,7 @@
         </is>
       </c>
       <c r="K469" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="L469" t="n">
         <v>0</v>
@@ -49920,7 +49906,7 @@
         </is>
       </c>
       <c r="K470" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="L470" t="n">
         <v>0</v>
@@ -49972,7 +49958,7 @@
         </is>
       </c>
       <c r="K471" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="L471" t="n">
         <v>0</v>
@@ -50024,7 +50010,7 @@
         </is>
       </c>
       <c r="K472" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="L472" t="n">
         <v>0</v>
@@ -50076,7 +50062,7 @@
         </is>
       </c>
       <c r="K473" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="L473" t="n">
         <v>0</v>
@@ -50128,7 +50114,7 @@
         </is>
       </c>
       <c r="K474" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="L474" t="n">
         <v>0</v>
@@ -50180,7 +50166,7 @@
         </is>
       </c>
       <c r="K475" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="L475" t="n">
         <v>0</v>
@@ -50232,7 +50218,7 @@
         </is>
       </c>
       <c r="K476" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="L476" t="n">
         <v>0</v>
@@ -50284,7 +50270,7 @@
         </is>
       </c>
       <c r="K477" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="L477" t="n">
         <v>0</v>
@@ -50336,7 +50322,7 @@
         </is>
       </c>
       <c r="K478" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="L478" t="n">
         <v>0</v>
@@ -50388,7 +50374,7 @@
         </is>
       </c>
       <c r="K479" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="L479" t="n">
         <v>0</v>
@@ -50440,7 +50426,7 @@
         </is>
       </c>
       <c r="K480" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="L480" t="n">
         <v>0</v>
@@ -50492,7 +50478,7 @@
         </is>
       </c>
       <c r="K481" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="L481" t="n">
         <v>0</v>
@@ -50544,7 +50530,7 @@
         </is>
       </c>
       <c r="K482" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="L482" t="n">
         <v>0</v>
@@ -50596,7 +50582,7 @@
         </is>
       </c>
       <c r="K483" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="L483" t="n">
         <v>0</v>
@@ -50648,7 +50634,7 @@
         </is>
       </c>
       <c r="K484" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="L484" t="n">
         <v>0</v>
@@ -50700,7 +50686,7 @@
         </is>
       </c>
       <c r="K485" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="L485" t="n">
         <v>0</v>
@@ -50752,7 +50738,7 @@
         </is>
       </c>
       <c r="K486" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="L486" t="n">
         <v>0</v>
@@ -50804,7 +50790,7 @@
         </is>
       </c>
       <c r="K487" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="L487" t="n">
         <v>0</v>
@@ -50856,7 +50842,7 @@
         </is>
       </c>
       <c r="K488" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="L488" t="n">
         <v>0</v>
@@ -50908,7 +50894,7 @@
         </is>
       </c>
       <c r="K489" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="L489" t="n">
         <v>0</v>
@@ -50960,7 +50946,7 @@
         </is>
       </c>
       <c r="K490" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="L490" t="n">
         <v>0</v>
@@ -51012,7 +50998,7 @@
         </is>
       </c>
       <c r="K491" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="L491" t="n">
         <v>0</v>
@@ -51064,7 +51050,7 @@
         </is>
       </c>
       <c r="K492" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="L492" t="n">
         <v>0</v>
@@ -51116,7 +51102,7 @@
         </is>
       </c>
       <c r="K493" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="L493" t="n">
         <v>0</v>
@@ -51168,7 +51154,7 @@
         </is>
       </c>
       <c r="K494" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="L494" t="n">
         <v>0</v>
@@ -51220,7 +51206,7 @@
         </is>
       </c>
       <c r="K495" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="L495" t="n">
         <v>0</v>
@@ -51272,7 +51258,7 @@
         </is>
       </c>
       <c r="K496" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L496" t="n">
         <v>0</v>
@@ -51324,7 +51310,7 @@
         </is>
       </c>
       <c r="K497" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L497" t="n">
         <v>0</v>
@@ -51376,7 +51362,7 @@
         </is>
       </c>
       <c r="K498" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L498" t="n">
         <v>0</v>
@@ -51428,7 +51414,7 @@
         </is>
       </c>
       <c r="K499" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L499" t="n">
         <v>0</v>
@@ -51480,7 +51466,7 @@
         </is>
       </c>
       <c r="K500" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="L500" t="n">
         <v>0</v>
@@ -51532,7 +51518,7 @@
         </is>
       </c>
       <c r="K501" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="L501" t="n">
         <v>0</v>
@@ -51584,7 +51570,7 @@
         </is>
       </c>
       <c r="K502" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="L502" t="n">
         <v>0</v>
@@ -51636,7 +51622,7 @@
         </is>
       </c>
       <c r="K503" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="L503" t="n">
         <v>0</v>
@@ -51688,7 +51674,7 @@
         </is>
       </c>
       <c r="K504" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="L504" t="n">
         <v>0</v>
@@ -51740,7 +51726,7 @@
         </is>
       </c>
       <c r="K505" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="L505" t="n">
         <v>0</v>
@@ -51792,7 +51778,7 @@
         </is>
       </c>
       <c r="K506" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="L506" t="n">
         <v>0</v>
@@ -51844,7 +51830,7 @@
         </is>
       </c>
       <c r="K507" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="L507" t="n">
         <v>0</v>
@@ -51896,7 +51882,7 @@
         </is>
       </c>
       <c r="K508" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="L508" t="n">
         <v>0</v>
@@ -51948,7 +51934,7 @@
         </is>
       </c>
       <c r="K509" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L509" t="n">
         <v>0</v>
@@ -52000,7 +51986,7 @@
         </is>
       </c>
       <c r="K510" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L510" t="n">
         <v>0</v>
@@ -52052,7 +52038,7 @@
         </is>
       </c>
       <c r="K511" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L511" t="n">
         <v>0</v>
@@ -52104,7 +52090,7 @@
         </is>
       </c>
       <c r="K512" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L512" t="n">
         <v>0</v>
@@ -52156,7 +52142,7 @@
         </is>
       </c>
       <c r="K513" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L513" t="n">
         <v>0</v>
@@ -52208,7 +52194,7 @@
         </is>
       </c>
       <c r="K514" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="L514" t="n">
         <v>0</v>
@@ -52260,7 +52246,7 @@
         </is>
       </c>
       <c r="K515" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="L515" t="n">
         <v>0</v>
@@ -52312,7 +52298,7 @@
         </is>
       </c>
       <c r="K516" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L516" t="n">
         <v>0</v>
@@ -52364,7 +52350,7 @@
         </is>
       </c>
       <c r="K517" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L517" t="n">
         <v>0</v>
@@ -52416,7 +52402,7 @@
         </is>
       </c>
       <c r="K518" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="L518" t="n">
         <v>0</v>
@@ -52468,7 +52454,7 @@
         </is>
       </c>
       <c r="K519" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="L519" t="n">
         <v>0</v>
@@ -52520,7 +52506,7 @@
         </is>
       </c>
       <c r="K520" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="L520" t="n">
         <v>0</v>
@@ -52572,7 +52558,7 @@
         </is>
       </c>
       <c r="K521" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="L521" t="n">
         <v>0</v>
@@ -52624,7 +52610,7 @@
         </is>
       </c>
       <c r="K522" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L522" t="n">
         <v>0</v>
@@ -52676,7 +52662,7 @@
         </is>
       </c>
       <c r="K523" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="L523" t="n">
         <v>0</v>
@@ -52728,7 +52714,7 @@
         </is>
       </c>
       <c r="K524" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="L524" t="n">
         <v>0</v>
@@ -52780,7 +52766,7 @@
         </is>
       </c>
       <c r="K525" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="L525" t="n">
         <v>0</v>
@@ -52832,7 +52818,7 @@
         </is>
       </c>
       <c r="K526" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L526" t="n">
         <v>0</v>
@@ -52884,7 +52870,7 @@
         </is>
       </c>
       <c r="K527" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L527" t="n">
         <v>0</v>
@@ -52936,7 +52922,7 @@
         </is>
       </c>
       <c r="K528" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="L528" t="n">
         <v>0</v>
@@ -52988,7 +52974,7 @@
         </is>
       </c>
       <c r="K529" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="L529" t="n">
         <v>0</v>
@@ -53040,7 +53026,7 @@
         </is>
       </c>
       <c r="K530" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="L530" t="n">
         <v>0</v>
@@ -53092,7 +53078,7 @@
         </is>
       </c>
       <c r="K531" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="L531" t="n">
         <v>0</v>
@@ -53144,7 +53130,7 @@
         </is>
       </c>
       <c r="K532" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="L532" t="n">
         <v>0</v>
@@ -53196,7 +53182,7 @@
         </is>
       </c>
       <c r="K533" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="L533" t="n">
         <v>0</v>
@@ -53248,7 +53234,7 @@
         </is>
       </c>
       <c r="K534" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="L534" t="n">
         <v>0</v>
@@ -53300,7 +53286,7 @@
         </is>
       </c>
       <c r="K535" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="L535" t="n">
         <v>0</v>
@@ -53352,7 +53338,7 @@
         </is>
       </c>
       <c r="K536" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="L536" t="n">
         <v>0</v>
@@ -53404,7 +53390,7 @@
         </is>
       </c>
       <c r="K537" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="L537" t="n">
         <v>0</v>
@@ -53456,7 +53442,7 @@
         </is>
       </c>
       <c r="K538" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="L538" t="n">
         <v>0</v>
@@ -53508,7 +53494,7 @@
         </is>
       </c>
       <c r="K539" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="L539" t="n">
         <v>0</v>
@@ -53560,7 +53546,7 @@
         </is>
       </c>
       <c r="K540" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="L540" t="n">
         <v>0</v>
@@ -53612,7 +53598,7 @@
         </is>
       </c>
       <c r="K541" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="L541" t="n">
         <v>0</v>
@@ -53664,7 +53650,7 @@
         </is>
       </c>
       <c r="K542" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="L542" t="n">
         <v>0</v>
@@ -53716,7 +53702,7 @@
         </is>
       </c>
       <c r="K543" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="L543" t="n">
         <v>0</v>
@@ -53768,7 +53754,7 @@
         </is>
       </c>
       <c r="K544" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="L544" t="n">
         <v>0</v>
@@ -53820,7 +53806,7 @@
         </is>
       </c>
       <c r="K545" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="L545" t="n">
         <v>0</v>
@@ -53872,7 +53858,7 @@
         </is>
       </c>
       <c r="K546" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="L546" t="n">
         <v>0</v>
@@ -53924,7 +53910,7 @@
         </is>
       </c>
       <c r="K547" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="L547" t="n">
         <v>0</v>
@@ -53976,7 +53962,7 @@
         </is>
       </c>
       <c r="K548" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="L548" t="n">
         <v>0</v>
@@ -54028,7 +54014,7 @@
         </is>
       </c>
       <c r="K549" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="L549" t="n">
         <v>0</v>
@@ -54080,7 +54066,7 @@
         </is>
       </c>
       <c r="K550" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="L550" t="n">
         <v>0</v>
@@ -54132,7 +54118,7 @@
         </is>
       </c>
       <c r="K551" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="L551" t="n">
         <v>0</v>
@@ -54184,7 +54170,7 @@
         </is>
       </c>
       <c r="K552" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="L552" t="n">
         <v>0</v>
@@ -54236,7 +54222,7 @@
         </is>
       </c>
       <c r="K553" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="L553" t="n">
         <v>0</v>
@@ -54288,7 +54274,7 @@
         </is>
       </c>
       <c r="K554" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="L554" t="n">
         <v>0</v>
@@ -54340,7 +54326,7 @@
         </is>
       </c>
       <c r="K555" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="L555" t="n">
         <v>0</v>
@@ -54392,7 +54378,7 @@
         </is>
       </c>
       <c r="K556" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="L556" t="n">
         <v>0</v>
@@ -54444,7 +54430,7 @@
         </is>
       </c>
       <c r="K557" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="L557" t="n">
         <v>0</v>
@@ -54496,7 +54482,7 @@
         </is>
       </c>
       <c r="K558" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="L558" t="n">
         <v>0</v>
@@ -54548,7 +54534,7 @@
         </is>
       </c>
       <c r="K559" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="L559" t="n">
         <v>0</v>
@@ -54600,7 +54586,7 @@
         </is>
       </c>
       <c r="K560" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="L560" t="n">
         <v>0</v>
@@ -54652,7 +54638,7 @@
         </is>
       </c>
       <c r="K561" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="L561" t="n">
         <v>0</v>
@@ -54704,7 +54690,7 @@
         </is>
       </c>
       <c r="K562" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="L562" t="n">
         <v>0</v>
@@ -54756,7 +54742,7 @@
         </is>
       </c>
       <c r="K563" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="L563" t="n">
         <v>0</v>
@@ -54808,7 +54794,7 @@
         </is>
       </c>
       <c r="K564" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L564" t="n">
         <v>0</v>
@@ -54860,7 +54846,7 @@
         </is>
       </c>
       <c r="K565" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L565" t="n">
         <v>0</v>
@@ -54912,7 +54898,7 @@
         </is>
       </c>
       <c r="K566" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L566" t="n">
         <v>0</v>
@@ -54964,7 +54950,7 @@
         </is>
       </c>
       <c r="K567" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L567" t="n">
         <v>0</v>
@@ -55016,7 +55002,7 @@
         </is>
       </c>
       <c r="K568" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="L568" t="n">
         <v>0</v>
@@ -55068,7 +55054,7 @@
         </is>
       </c>
       <c r="K569" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="L569" t="n">
         <v>0</v>
@@ -55120,7 +55106,7 @@
         </is>
       </c>
       <c r="K570" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L570" t="n">
         <v>0</v>
@@ -55172,7 +55158,7 @@
         </is>
       </c>
       <c r="K571" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L571" t="n">
         <v>0</v>
@@ -55224,7 +55210,7 @@
         </is>
       </c>
       <c r="K572" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L572" t="n">
         <v>0</v>
@@ -55276,7 +55262,7 @@
         </is>
       </c>
       <c r="K573" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L573" t="n">
         <v>0</v>
@@ -55328,7 +55314,7 @@
         </is>
       </c>
       <c r="K574" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L574" t="n">
         <v>0</v>
@@ -55380,7 +55366,7 @@
         </is>
       </c>
       <c r="K575" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L575" t="n">
         <v>0</v>
@@ -55432,7 +55418,7 @@
         </is>
       </c>
       <c r="K576" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L576" t="n">
         <v>0</v>
@@ -55484,7 +55470,7 @@
         </is>
       </c>
       <c r="K577" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L577" t="n">
         <v>0</v>
@@ -55536,7 +55522,7 @@
         </is>
       </c>
       <c r="K578" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L578" t="n">
         <v>0</v>
@@ -55588,7 +55574,7 @@
         </is>
       </c>
       <c r="K579" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L579" t="n">
         <v>0</v>
@@ -55640,7 +55626,7 @@
         </is>
       </c>
       <c r="K580" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L580" t="n">
         <v>0</v>
@@ -55692,7 +55678,7 @@
         </is>
       </c>
       <c r="K581" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L581" t="n">
         <v>0</v>
@@ -55744,7 +55730,7 @@
         </is>
       </c>
       <c r="K582" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L582" t="n">
         <v>0</v>
@@ -55796,7 +55782,7 @@
         </is>
       </c>
       <c r="K583" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L583" t="n">
         <v>0</v>
@@ -55848,7 +55834,7 @@
         </is>
       </c>
       <c r="K584" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L584" t="n">
         <v>0</v>
@@ -55900,7 +55886,7 @@
         </is>
       </c>
       <c r="K585" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L585" t="n">
         <v>0</v>
@@ -55952,7 +55938,7 @@
         </is>
       </c>
       <c r="K586" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L586" t="n">
         <v>0</v>
@@ -56004,7 +55990,7 @@
         </is>
       </c>
       <c r="K587" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L587" t="n">
         <v>0</v>
@@ -56056,7 +56042,7 @@
         </is>
       </c>
       <c r="K588" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L588" t="n">
         <v>0</v>
@@ -56108,7 +56094,7 @@
         </is>
       </c>
       <c r="K589" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L589" t="n">
         <v>0</v>
@@ -56160,7 +56146,7 @@
         </is>
       </c>
       <c r="K590" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L590" t="n">
         <v>0</v>
@@ -56212,7 +56198,7 @@
         </is>
       </c>
       <c r="K591" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L591" t="n">
         <v>0</v>
@@ -56264,7 +56250,7 @@
         </is>
       </c>
       <c r="K592" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L592" t="n">
         <v>0</v>
@@ -56316,7 +56302,7 @@
         </is>
       </c>
       <c r="K593" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L593" t="n">
         <v>0</v>
@@ -56368,7 +56354,7 @@
         </is>
       </c>
       <c r="K594" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L594" t="n">
         <v>0</v>
@@ -56420,7 +56406,7 @@
         </is>
       </c>
       <c r="K595" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L595" t="n">
         <v>0</v>
@@ -56472,7 +56458,7 @@
         </is>
       </c>
       <c r="K596" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L596" t="n">
         <v>0</v>
@@ -56524,7 +56510,7 @@
         </is>
       </c>
       <c r="K597" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L597" t="n">
         <v>0</v>
@@ -56576,7 +56562,7 @@
         </is>
       </c>
       <c r="K598" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L598" t="n">
         <v>0</v>
@@ -56628,7 +56614,7 @@
         </is>
       </c>
       <c r="K599" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L599" t="n">
         <v>0</v>
@@ -56680,7 +56666,7 @@
         </is>
       </c>
       <c r="K600" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L600" t="n">
         <v>0</v>
@@ -56732,7 +56718,7 @@
         </is>
       </c>
       <c r="K601" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L601" t="n">
         <v>0</v>
@@ -56784,7 +56770,7 @@
         </is>
       </c>
       <c r="K602" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L602" t="n">
         <v>0</v>
@@ -56836,7 +56822,7 @@
         </is>
       </c>
       <c r="K603" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L603" t="n">
         <v>0</v>
@@ -56888,7 +56874,7 @@
         </is>
       </c>
       <c r="K604" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L604" t="n">
         <v>0</v>
@@ -56940,7 +56926,7 @@
         </is>
       </c>
       <c r="K605" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L605" t="n">
         <v>0</v>
@@ -56992,7 +56978,7 @@
         </is>
       </c>
       <c r="K606" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L606" t="n">
         <v>0</v>
@@ -57044,7 +57030,7 @@
         </is>
       </c>
       <c r="K607" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L607" t="n">
         <v>0</v>
@@ -57096,7 +57082,7 @@
         </is>
       </c>
       <c r="K608" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L608" t="n">
         <v>0</v>
@@ -57148,7 +57134,7 @@
         </is>
       </c>
       <c r="K609" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L609" t="n">
         <v>0</v>
@@ -57200,7 +57186,7 @@
         </is>
       </c>
       <c r="K610" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L610" t="n">
         <v>0</v>
@@ -57252,7 +57238,7 @@
         </is>
       </c>
       <c r="K611" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L611" t="n">
         <v>0</v>
@@ -57304,7 +57290,7 @@
         </is>
       </c>
       <c r="K612" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L612" t="n">
         <v>0</v>
@@ -57356,7 +57342,7 @@
         </is>
       </c>
       <c r="K613" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L613" t="n">
         <v>0</v>
@@ -57408,7 +57394,7 @@
         </is>
       </c>
       <c r="K614" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L614" t="n">
         <v>0</v>
@@ -57460,7 +57446,7 @@
         </is>
       </c>
       <c r="K615" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L615" t="n">
         <v>0</v>
@@ -57512,7 +57498,7 @@
         </is>
       </c>
       <c r="K616" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L616" t="n">
         <v>0</v>
@@ -57564,7 +57550,7 @@
         </is>
       </c>
       <c r="K617" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L617" t="n">
         <v>0</v>
@@ -57616,7 +57602,7 @@
         </is>
       </c>
       <c r="K618" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L618" t="n">
         <v>0</v>
@@ -57668,7 +57654,7 @@
         </is>
       </c>
       <c r="K619" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L619" t="n">
         <v>0</v>
@@ -57720,7 +57706,7 @@
         </is>
       </c>
       <c r="K620" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L620" t="n">
         <v>0</v>
@@ -57772,7 +57758,7 @@
         </is>
       </c>
       <c r="K621" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L621" t="n">
         <v>0</v>
@@ -57824,7 +57810,7 @@
         </is>
       </c>
       <c r="K622" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L622" t="n">
         <v>0</v>
@@ -57876,7 +57862,7 @@
         </is>
       </c>
       <c r="K623" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L623" t="n">
         <v>0</v>
@@ -57928,7 +57914,7 @@
         </is>
       </c>
       <c r="K624" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L624" t="n">
         <v>0</v>
@@ -57980,7 +57966,7 @@
         </is>
       </c>
       <c r="K625" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L625" t="n">
         <v>0</v>
@@ -58032,7 +58018,7 @@
         </is>
       </c>
       <c r="K626" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L626" t="n">
         <v>0</v>
@@ -58084,7 +58070,7 @@
         </is>
       </c>
       <c r="K627" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L627" t="n">
         <v>0</v>
@@ -58136,7 +58122,7 @@
         </is>
       </c>
       <c r="K628" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L628" t="n">
         <v>0</v>
@@ -58188,7 +58174,7 @@
         </is>
       </c>
       <c r="K629" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="L629" t="n">
         <v>0</v>
@@ -58240,7 +58226,7 @@
         </is>
       </c>
       <c r="K630" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="L630" t="n">
         <v>0</v>
@@ -58292,7 +58278,7 @@
         </is>
       </c>
       <c r="K631" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="L631" t="n">
         <v>0</v>
@@ -58344,7 +58330,7 @@
         </is>
       </c>
       <c r="K632" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L632" t="n">
         <v>0</v>
@@ -58396,7 +58382,7 @@
         </is>
       </c>
       <c r="K633" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="L633" t="n">
         <v>0</v>
@@ -58448,7 +58434,7 @@
         </is>
       </c>
       <c r="K634" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="L634" t="n">
         <v>0</v>
@@ -58500,7 +58486,7 @@
         </is>
       </c>
       <c r="K635" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="L635" t="n">
         <v>0</v>
@@ -58552,7 +58538,7 @@
         </is>
       </c>
       <c r="K636" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L636" t="n">
         <v>0</v>
@@ -58604,7 +58590,7 @@
         </is>
       </c>
       <c r="K637" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L637" t="n">
         <v>0</v>
@@ -58656,7 +58642,7 @@
         </is>
       </c>
       <c r="K638" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L638" t="n">
         <v>0</v>
@@ -58708,7 +58694,7 @@
         </is>
       </c>
       <c r="K639" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L639" t="n">
         <v>0</v>
@@ -58760,7 +58746,7 @@
         </is>
       </c>
       <c r="K640" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L640" t="n">
         <v>0</v>
@@ -58812,7 +58798,7 @@
         </is>
       </c>
       <c r="K641" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L641" t="n">
         <v>0</v>
@@ -58864,7 +58850,7 @@
         </is>
       </c>
       <c r="K642" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L642" t="n">
         <v>0</v>
@@ -58916,7 +58902,7 @@
         </is>
       </c>
       <c r="K643" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L643" t="n">
         <v>0</v>
@@ -58968,7 +58954,7 @@
         </is>
       </c>
       <c r="K644" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L644" t="n">
         <v>0</v>
@@ -59020,7 +59006,7 @@
         </is>
       </c>
       <c r="K645" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L645" t="n">
         <v>0</v>
@@ -59072,7 +59058,7 @@
         </is>
       </c>
       <c r="K646" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L646" t="n">
         <v>0</v>
@@ -59124,7 +59110,7 @@
         </is>
       </c>
       <c r="K647" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="L647" t="n">
         <v>0</v>
@@ -59176,7 +59162,7 @@
         </is>
       </c>
       <c r="K648" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="L648" t="n">
         <v>0</v>
@@ -59228,7 +59214,7 @@
         </is>
       </c>
       <c r="K649" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L649" t="n">
         <v>0</v>
@@ -59280,7 +59266,7 @@
         </is>
       </c>
       <c r="K650" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L650" t="n">
         <v>0</v>
@@ -59332,7 +59318,7 @@
         </is>
       </c>
       <c r="K651" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L651" t="n">
         <v>0</v>
@@ -59384,7 +59370,7 @@
         </is>
       </c>
       <c r="K652" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L652" t="n">
         <v>0</v>
@@ -59436,7 +59422,7 @@
         </is>
       </c>
       <c r="K653" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L653" t="n">
         <v>0</v>
@@ -59488,7 +59474,7 @@
         </is>
       </c>
       <c r="K654" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L654" t="n">
         <v>0</v>
@@ -59540,7 +59526,7 @@
         </is>
       </c>
       <c r="K655" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L655" t="n">
         <v>0</v>
@@ -59592,7 +59578,7 @@
         </is>
       </c>
       <c r="K656" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L656" t="n">
         <v>0</v>
@@ -59644,7 +59630,7 @@
         </is>
       </c>
       <c r="K657" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L657" t="n">
         <v>0</v>
@@ -59696,7 +59682,7 @@
         </is>
       </c>
       <c r="K658" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L658" t="n">
         <v>0</v>
@@ -59748,7 +59734,7 @@
         </is>
       </c>
       <c r="K659" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L659" t="n">
         <v>0</v>
@@ -59800,7 +59786,7 @@
         </is>
       </c>
       <c r="K660" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L660" t="n">
         <v>0</v>
@@ -59852,7 +59838,7 @@
         </is>
       </c>
       <c r="K661" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L661" t="n">
         <v>0</v>
@@ -59904,7 +59890,7 @@
         </is>
       </c>
       <c r="K662" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L662" t="n">
         <v>0</v>
@@ -59956,7 +59942,7 @@
         </is>
       </c>
       <c r="K663" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L663" t="n">
         <v>0</v>
@@ -60008,7 +59994,7 @@
         </is>
       </c>
       <c r="K664" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L664" t="n">
         <v>0</v>
@@ -60060,7 +60046,7 @@
         </is>
       </c>
       <c r="K665" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L665" t="n">
         <v>0</v>
@@ -60112,7 +60098,7 @@
         </is>
       </c>
       <c r="K666" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L666" t="n">
         <v>0</v>
@@ -60164,7 +60150,7 @@
         </is>
       </c>
       <c r="K667" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L667" t="n">
         <v>0</v>
@@ -60216,7 +60202,7 @@
         </is>
       </c>
       <c r="K668" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L668" t="n">
         <v>0</v>
@@ -60268,7 +60254,7 @@
         </is>
       </c>
       <c r="K669" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L669" t="n">
         <v>0</v>
@@ -60320,7 +60306,7 @@
         </is>
       </c>
       <c r="K670" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L670" t="n">
         <v>0</v>
@@ -60372,7 +60358,7 @@
         </is>
       </c>
       <c r="K671" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L671" t="n">
         <v>0</v>
@@ -60424,7 +60410,7 @@
         </is>
       </c>
       <c r="K672" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L672" t="n">
         <v>0</v>
@@ -60476,7 +60462,7 @@
         </is>
       </c>
       <c r="K673" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L673" t="n">
         <v>0</v>
@@ -60528,7 +60514,7 @@
         </is>
       </c>
       <c r="K674" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L674" t="n">
         <v>0</v>
@@ -60580,7 +60566,7 @@
         </is>
       </c>
       <c r="K675" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L675" t="n">
         <v>0</v>
@@ -60632,7 +60618,7 @@
         </is>
       </c>
       <c r="K676" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L676" t="n">
         <v>0</v>
@@ -60684,7 +60670,7 @@
         </is>
       </c>
       <c r="K677" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L677" t="n">
         <v>0</v>
@@ -60736,7 +60722,7 @@
         </is>
       </c>
       <c r="K678" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L678" t="n">
         <v>0</v>
@@ -60788,7 +60774,7 @@
         </is>
       </c>
       <c r="K679" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L679" t="n">
         <v>0</v>
@@ -60840,7 +60826,7 @@
         </is>
       </c>
       <c r="K680" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L680" t="n">
         <v>0</v>
@@ -60892,7 +60878,7 @@
         </is>
       </c>
       <c r="K681" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L681" t="n">
         <v>0</v>
@@ -60944,7 +60930,7 @@
         </is>
       </c>
       <c r="K682" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L682" t="n">
         <v>0</v>
@@ -60996,7 +60982,7 @@
         </is>
       </c>
       <c r="K683" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L683" t="n">
         <v>0</v>
@@ -61048,7 +61034,7 @@
         </is>
       </c>
       <c r="K684" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L684" t="n">
         <v>0</v>
@@ -61100,7 +61086,7 @@
         </is>
       </c>
       <c r="K685" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L685" t="n">
         <v>0</v>
@@ -61152,7 +61138,7 @@
         </is>
       </c>
       <c r="K686" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L686" t="n">
         <v>0</v>
@@ -61204,7 +61190,7 @@
         </is>
       </c>
       <c r="K687" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L687" t="n">
         <v>0</v>
@@ -61256,7 +61242,7 @@
         </is>
       </c>
       <c r="K688" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L688" t="n">
         <v>0</v>
@@ -61308,7 +61294,7 @@
         </is>
       </c>
       <c r="K689" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L689" t="n">
         <v>0</v>
@@ -61360,7 +61346,7 @@
         </is>
       </c>
       <c r="K690" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L690" t="n">
         <v>0</v>
@@ -61412,7 +61398,7 @@
         </is>
       </c>
       <c r="K691" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L691" t="n">
         <v>0</v>
@@ -61464,7 +61450,7 @@
         </is>
       </c>
       <c r="K692" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L692" t="n">
         <v>0</v>
@@ -61516,7 +61502,7 @@
         </is>
       </c>
       <c r="K693" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L693" t="n">
         <v>0</v>
@@ -61568,7 +61554,7 @@
         </is>
       </c>
       <c r="K694" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L694" t="n">
         <v>0</v>
@@ -61620,7 +61606,7 @@
         </is>
       </c>
       <c r="K695" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L695" t="n">
         <v>0</v>
@@ -61672,7 +61658,7 @@
         </is>
       </c>
       <c r="K696" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L696" t="n">
         <v>0</v>
@@ -61724,7 +61710,7 @@
         </is>
       </c>
       <c r="K697" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L697" t="n">
         <v>0</v>
@@ -61776,7 +61762,7 @@
         </is>
       </c>
       <c r="K698" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L698" t="n">
         <v>0</v>
@@ -61828,7 +61814,7 @@
         </is>
       </c>
       <c r="K699" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L699" t="n">
         <v>0</v>
@@ -61880,7 +61866,7 @@
         </is>
       </c>
       <c r="K700" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L700" t="n">
         <v>0</v>
@@ -61932,7 +61918,7 @@
         </is>
       </c>
       <c r="K701" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L701" t="n">
         <v>0</v>
@@ -61984,7 +61970,7 @@
         </is>
       </c>
       <c r="K702" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L702" t="n">
         <v>0</v>
@@ -62036,7 +62022,7 @@
         </is>
       </c>
       <c r="K703" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L703" t="n">
         <v>0</v>
@@ -62088,7 +62074,7 @@
         </is>
       </c>
       <c r="K704" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L704" t="n">
         <v>0</v>
@@ -62140,7 +62126,7 @@
         </is>
       </c>
       <c r="K705" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L705" t="n">
         <v>0</v>
@@ -62192,7 +62178,7 @@
         </is>
       </c>
       <c r="K706" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L706" t="n">
         <v>0</v>
@@ -62244,7 +62230,7 @@
         </is>
       </c>
       <c r="K707" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L707" t="n">
         <v>0</v>
@@ -62296,7 +62282,7 @@
         </is>
       </c>
       <c r="K708" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L708" t="n">
         <v>0</v>
@@ -62348,7 +62334,7 @@
         </is>
       </c>
       <c r="K709" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L709" t="n">
         <v>0</v>
@@ -62400,7 +62386,7 @@
         </is>
       </c>
       <c r="K710" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L710" t="n">
         <v>0</v>
@@ -62452,7 +62438,7 @@
         </is>
       </c>
       <c r="K711" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L711" t="n">
         <v>0</v>
@@ -62504,7 +62490,7 @@
         </is>
       </c>
       <c r="K712" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L712" t="n">
         <v>0</v>
@@ -62556,7 +62542,7 @@
         </is>
       </c>
       <c r="K713" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L713" t="n">
         <v>0</v>
@@ -62608,7 +62594,7 @@
         </is>
       </c>
       <c r="K714" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L714" t="n">
         <v>0</v>
@@ -62660,7 +62646,7 @@
         </is>
       </c>
       <c r="K715" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L715" t="n">
         <v>0</v>
@@ -62712,7 +62698,7 @@
         </is>
       </c>
       <c r="K716" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L716" t="n">
         <v>0</v>
@@ -62764,7 +62750,7 @@
         </is>
       </c>
       <c r="K717" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L717" t="n">
         <v>0</v>
@@ -62816,7 +62802,7 @@
         </is>
       </c>
       <c r="K718" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L718" t="n">
         <v>0</v>
@@ -62868,7 +62854,7 @@
         </is>
       </c>
       <c r="K719" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L719" t="n">
         <v>0</v>
@@ -62920,7 +62906,7 @@
         </is>
       </c>
       <c r="K720" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L720" t="n">
         <v>0</v>
@@ -62972,7 +62958,7 @@
         </is>
       </c>
       <c r="K721" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L721" t="n">
         <v>0</v>
@@ -63024,7 +63010,7 @@
         </is>
       </c>
       <c r="K722" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L722" t="n">
         <v>0</v>
@@ -63076,7 +63062,7 @@
         </is>
       </c>
       <c r="K723" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L723" t="n">
         <v>0</v>
@@ -63128,7 +63114,7 @@
         </is>
       </c>
       <c r="K724" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L724" t="n">
         <v>0</v>
@@ -63180,7 +63166,7 @@
         </is>
       </c>
       <c r="K725" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L725" t="n">
         <v>0</v>
@@ -63232,7 +63218,7 @@
         </is>
       </c>
       <c r="K726" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L726" t="n">
         <v>0</v>
@@ -63284,7 +63270,7 @@
         </is>
       </c>
       <c r="K727" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L727" t="n">
         <v>0</v>
@@ -63336,7 +63322,7 @@
         </is>
       </c>
       <c r="K728" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L728" t="n">
         <v>0</v>
@@ -63388,7 +63374,7 @@
         </is>
       </c>
       <c r="K729" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L729" t="n">
         <v>0</v>
@@ -63440,7 +63426,7 @@
         </is>
       </c>
       <c r="K730" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L730" t="n">
         <v>0</v>
@@ -63492,7 +63478,7 @@
         </is>
       </c>
       <c r="K731" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L731" t="n">
         <v>0</v>
@@ -63544,7 +63530,7 @@
         </is>
       </c>
       <c r="K732" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L732" t="n">
         <v>0</v>
@@ -63596,7 +63582,7 @@
         </is>
       </c>
       <c r="K733" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L733" t="n">
         <v>0</v>
@@ -63648,7 +63634,7 @@
         </is>
       </c>
       <c r="K734" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L734" t="n">
         <v>0</v>
@@ -63700,7 +63686,7 @@
         </is>
       </c>
       <c r="K735" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L735" t="n">
         <v>0</v>
@@ -63752,7 +63738,7 @@
         </is>
       </c>
       <c r="K736" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L736" t="n">
         <v>0</v>
@@ -63804,7 +63790,7 @@
         </is>
       </c>
       <c r="K737" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L737" t="n">
         <v>0</v>
@@ -63856,7 +63842,7 @@
         </is>
       </c>
       <c r="K738" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L738" t="n">
         <v>0</v>
@@ -63908,7 +63894,7 @@
         </is>
       </c>
       <c r="K739" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L739" t="n">
         <v>0</v>
@@ -63960,7 +63946,7 @@
         </is>
       </c>
       <c r="K740" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="L740" t="n">
         <v>0</v>
@@ -64012,7 +63998,7 @@
         </is>
       </c>
       <c r="K741" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L741" t="n">
         <v>0</v>
@@ -64064,7 +64050,7 @@
         </is>
       </c>
       <c r="K742" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="L742" t="n">
         <v>0</v>
@@ -64116,7 +64102,7 @@
         </is>
       </c>
       <c r="K743" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="L743" t="n">
         <v>0</v>
@@ -64168,7 +64154,7 @@
         </is>
       </c>
       <c r="K744" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L744" t="n">
         <v>0</v>
@@ -64220,7 +64206,7 @@
         </is>
       </c>
       <c r="K745" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L745" t="n">
         <v>0</v>
@@ -64272,7 +64258,7 @@
         </is>
       </c>
       <c r="K746" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="L746" t="n">
         <v>0</v>
@@ -64324,7 +64310,7 @@
         </is>
       </c>
       <c r="K747" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L747" t="n">
         <v>0</v>
@@ -64376,7 +64362,7 @@
         </is>
       </c>
       <c r="K748" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="L748" t="n">
         <v>0</v>
@@ -64428,7 +64414,7 @@
         </is>
       </c>
       <c r="K749" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L749" t="n">
         <v>0</v>
@@ -64480,7 +64466,7 @@
         </is>
       </c>
       <c r="K750" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L750" t="n">
         <v>0</v>
@@ -64532,7 +64518,7 @@
         </is>
       </c>
       <c r="K751" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L751" t="n">
         <v>0</v>
@@ -64584,7 +64570,7 @@
         </is>
       </c>
       <c r="K752" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L752" t="n">
         <v>0</v>
@@ -64636,7 +64622,7 @@
         </is>
       </c>
       <c r="K753" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L753" t="n">
         <v>0</v>
@@ -64688,7 +64674,7 @@
         </is>
       </c>
       <c r="K754" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L754" t="n">
         <v>0</v>
@@ -64740,7 +64726,7 @@
         </is>
       </c>
       <c r="K755" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L755" t="n">
         <v>0</v>
@@ -64792,7 +64778,7 @@
         </is>
       </c>
       <c r="K756" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L756" t="n">
         <v>0</v>
@@ -64844,7 +64830,7 @@
         </is>
       </c>
       <c r="K757" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L757" t="n">
         <v>0</v>
@@ -64896,7 +64882,7 @@
         </is>
       </c>
       <c r="K758" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L758" t="n">
         <v>0</v>
@@ -64948,7 +64934,7 @@
         </is>
       </c>
       <c r="K759" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L759" t="n">
         <v>0</v>
@@ -65000,7 +64986,7 @@
         </is>
       </c>
       <c r="K760" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L760" t="n">
         <v>0</v>
@@ -65052,7 +65038,7 @@
         </is>
       </c>
       <c r="K761" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L761" t="n">
         <v>0</v>
@@ -65104,7 +65090,7 @@
         </is>
       </c>
       <c r="K762" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L762" t="n">
         <v>0</v>
@@ -65156,7 +65142,7 @@
         </is>
       </c>
       <c r="K763" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L763" t="n">
         <v>0</v>
@@ -65208,7 +65194,7 @@
         </is>
       </c>
       <c r="K764" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L764" t="n">
         <v>0</v>
@@ -65260,7 +65246,7 @@
         </is>
       </c>
       <c r="K765" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L765" t="n">
         <v>0</v>
@@ -65312,7 +65298,7 @@
         </is>
       </c>
       <c r="K766" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L766" t="n">
         <v>0</v>
@@ -65364,7 +65350,7 @@
         </is>
       </c>
       <c r="K767" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L767" t="n">
         <v>0</v>
@@ -65416,7 +65402,7 @@
         </is>
       </c>
       <c r="K768" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L768" t="n">
         <v>0</v>
@@ -65468,7 +65454,7 @@
         </is>
       </c>
       <c r="K769" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L769" t="n">
         <v>0</v>
@@ -65520,7 +65506,7 @@
         </is>
       </c>
       <c r="K770" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L770" t="n">
         <v>0</v>
@@ -65572,7 +65558,7 @@
         </is>
       </c>
       <c r="K771" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L771" t="n">
         <v>0</v>
@@ -65624,7 +65610,7 @@
         </is>
       </c>
       <c r="K772" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L772" t="n">
         <v>0</v>
@@ -65676,7 +65662,7 @@
         </is>
       </c>
       <c r="K773" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L773" t="n">
         <v>0</v>
@@ -65728,7 +65714,7 @@
         </is>
       </c>
       <c r="K774" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L774" t="n">
         <v>0</v>
@@ -65780,7 +65766,7 @@
         </is>
       </c>
       <c r="K775" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L775" t="n">
         <v>0</v>
@@ -65832,7 +65818,7 @@
         </is>
       </c>
       <c r="K776" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L776" t="n">
         <v>0</v>
@@ -65884,7 +65870,7 @@
         </is>
       </c>
       <c r="K777" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L777" t="n">
         <v>0</v>
@@ -65936,7 +65922,7 @@
         </is>
       </c>
       <c r="K778" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L778" t="n">
         <v>0</v>
@@ -65988,7 +65974,7 @@
         </is>
       </c>
       <c r="K779" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L779" t="n">
         <v>0</v>
@@ -66040,7 +66026,7 @@
         </is>
       </c>
       <c r="K780" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L780" t="n">
         <v>0</v>
@@ -66092,7 +66078,7 @@
         </is>
       </c>
       <c r="K781" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L781" t="n">
         <v>0</v>
@@ -66144,7 +66130,7 @@
         </is>
       </c>
       <c r="K782" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L782" t="n">
         <v>0</v>
@@ -66196,7 +66182,7 @@
         </is>
       </c>
       <c r="K783" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L783" t="n">
         <v>0</v>
@@ -66248,7 +66234,7 @@
         </is>
       </c>
       <c r="K784" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="L784" t="n">
         <v>0</v>
@@ -66300,7 +66286,7 @@
         </is>
       </c>
       <c r="K785" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="L785" t="n">
         <v>0</v>
@@ -66352,7 +66338,7 @@
         </is>
       </c>
       <c r="K786" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L786" t="n">
         <v>0</v>
@@ -66404,7 +66390,7 @@
         </is>
       </c>
       <c r="K787" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L787" t="n">
         <v>0</v>
@@ -66456,7 +66442,7 @@
         </is>
       </c>
       <c r="K788" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L788" t="n">
         <v>0</v>
@@ -66508,7 +66494,7 @@
         </is>
       </c>
       <c r="K789" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L789" t="n">
         <v>0</v>
@@ -66560,7 +66546,7 @@
         </is>
       </c>
       <c r="K790" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L790" t="n">
         <v>0</v>
@@ -66612,7 +66598,7 @@
         </is>
       </c>
       <c r="K791" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L791" t="n">
         <v>0</v>
@@ -66664,7 +66650,7 @@
         </is>
       </c>
       <c r="K792" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L792" t="n">
         <v>0</v>
@@ -66716,7 +66702,7 @@
         </is>
       </c>
       <c r="K793" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L793" t="n">
         <v>0</v>
@@ -66768,7 +66754,7 @@
         </is>
       </c>
       <c r="K794" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L794" t="n">
         <v>0</v>
@@ -66820,7 +66806,7 @@
         </is>
       </c>
       <c r="K795" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L795" t="n">
         <v>0</v>
@@ -66872,7 +66858,7 @@
         </is>
       </c>
       <c r="K796" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L796" t="n">
         <v>0</v>
@@ -66924,7 +66910,7 @@
         </is>
       </c>
       <c r="K797" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L797" t="n">
         <v>0</v>
@@ -66976,7 +66962,7 @@
         </is>
       </c>
       <c r="K798" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L798" t="n">
         <v>0</v>
@@ -67028,7 +67014,7 @@
         </is>
       </c>
       <c r="K799" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L799" t="n">
         <v>0</v>
@@ -67080,7 +67066,7 @@
         </is>
       </c>
       <c r="K800" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L800" t="n">
         <v>0</v>
@@ -67132,7 +67118,7 @@
         </is>
       </c>
       <c r="K801" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L801" t="n">
         <v>0</v>
@@ -67184,7 +67170,7 @@
         </is>
       </c>
       <c r="K802" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L802" t="n">
         <v>0</v>
@@ -67236,7 +67222,7 @@
         </is>
       </c>
       <c r="K803" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L803" t="n">
         <v>0</v>
@@ -67288,7 +67274,7 @@
         </is>
       </c>
       <c r="K804" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L804" t="n">
         <v>0</v>
@@ -67340,7 +67326,7 @@
         </is>
       </c>
       <c r="K805" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L805" t="n">
         <v>0</v>
@@ -67392,7 +67378,7 @@
         </is>
       </c>
       <c r="K806" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L806" t="n">
         <v>0</v>
@@ -67444,7 +67430,7 @@
         </is>
       </c>
       <c r="K807" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L807" t="n">
         <v>0</v>
@@ -67496,7 +67482,7 @@
         </is>
       </c>
       <c r="K808" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L808" t="n">
         <v>0</v>
@@ -67548,7 +67534,7 @@
         </is>
       </c>
       <c r="K809" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L809" t="n">
         <v>0</v>
@@ -67600,7 +67586,7 @@
         </is>
       </c>
       <c r="K810" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L810" t="n">
         <v>0</v>
@@ -67652,7 +67638,7 @@
         </is>
       </c>
       <c r="K811" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L811" t="n">
         <v>0</v>
@@ -67704,7 +67690,7 @@
         </is>
       </c>
       <c r="K812" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L812" t="n">
         <v>0</v>
@@ -67756,7 +67742,7 @@
         </is>
       </c>
       <c r="K813" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L813" t="n">
         <v>0</v>
@@ -67808,7 +67794,7 @@
         </is>
       </c>
       <c r="K814" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L814" t="n">
         <v>0</v>
@@ -67860,7 +67846,7 @@
         </is>
       </c>
       <c r="K815" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L815" t="n">
         <v>0</v>
@@ -67912,7 +67898,7 @@
         </is>
       </c>
       <c r="K816" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L816" t="n">
         <v>0</v>
@@ -67964,7 +67950,7 @@
         </is>
       </c>
       <c r="K817" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L817" t="n">
         <v>0</v>
@@ -68016,7 +68002,7 @@
         </is>
       </c>
       <c r="K818" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L818" t="n">
         <v>0</v>
@@ -68068,7 +68054,7 @@
         </is>
       </c>
       <c r="K819" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L819" t="n">
         <v>0</v>
@@ -68120,7 +68106,7 @@
         </is>
       </c>
       <c r="K820" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L820" t="n">
         <v>0</v>
@@ -68172,7 +68158,7 @@
         </is>
       </c>
       <c r="K821" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L821" t="n">
         <v>0</v>
@@ -68224,7 +68210,7 @@
         </is>
       </c>
       <c r="K822" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L822" t="n">
         <v>0</v>
@@ -68276,7 +68262,7 @@
         </is>
       </c>
       <c r="K823" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L823" t="n">
         <v>0</v>
@@ -68328,7 +68314,7 @@
         </is>
       </c>
       <c r="K824" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L824" t="n">
         <v>0</v>
@@ -68380,7 +68366,7 @@
         </is>
       </c>
       <c r="K825" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L825" t="n">
         <v>0</v>
@@ -68432,7 +68418,7 @@
         </is>
       </c>
       <c r="K826" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L826" t="n">
         <v>0</v>
@@ -68484,7 +68470,7 @@
         </is>
       </c>
       <c r="K827" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L827" t="n">
         <v>0</v>
@@ -68536,7 +68522,7 @@
         </is>
       </c>
       <c r="K828" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L828" t="n">
         <v>0</v>
@@ -68588,7 +68574,7 @@
         </is>
       </c>
       <c r="K829" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L829" t="n">
         <v>0</v>
@@ -68640,7 +68626,7 @@
         </is>
       </c>
       <c r="K830" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L830" t="n">
         <v>0</v>
@@ -68692,7 +68678,7 @@
         </is>
       </c>
       <c r="K831" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L831" t="n">
         <v>0</v>
@@ -68744,7 +68730,7 @@
         </is>
       </c>
       <c r="K832" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L832" t="n">
         <v>0</v>
@@ -68796,7 +68782,7 @@
         </is>
       </c>
       <c r="K833" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L833" t="n">
         <v>0</v>
@@ -68848,7 +68834,7 @@
         </is>
       </c>
       <c r="K834" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="L834" t="n">
         <v>0</v>
@@ -68900,7 +68886,7 @@
         </is>
       </c>
       <c r="K835" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L835" t="n">
         <v>0</v>
@@ -68952,7 +68938,7 @@
         </is>
       </c>
       <c r="K836" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="L836" t="n">
         <v>0</v>
@@ -69004,7 +68990,7 @@
         </is>
       </c>
       <c r="K837" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="L837" t="n">
         <v>0</v>
@@ -69056,7 +69042,7 @@
         </is>
       </c>
       <c r="K838" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="L838" t="n">
         <v>0</v>
@@ -69108,7 +69094,7 @@
         </is>
       </c>
       <c r="K839" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="L839" t="n">
         <v>0</v>
@@ -69160,7 +69146,7 @@
         </is>
       </c>
       <c r="K840" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L840" t="n">
         <v>0</v>
@@ -69212,7 +69198,7 @@
         </is>
       </c>
       <c r="K841" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L841" t="n">
         <v>0</v>
@@ -69264,7 +69250,7 @@
         </is>
       </c>
       <c r="K842" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L842" t="n">
         <v>0</v>
@@ -69316,7 +69302,7 @@
         </is>
       </c>
       <c r="K843" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L843" t="n">
         <v>0</v>
@@ -69368,7 +69354,7 @@
         </is>
       </c>
       <c r="K844" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L844" t="n">
         <v>0</v>
@@ -69420,7 +69406,7 @@
         </is>
       </c>
       <c r="K845" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L845" t="n">
         <v>0</v>
@@ -69472,7 +69458,7 @@
         </is>
       </c>
       <c r="K846" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L846" t="n">
         <v>0</v>
@@ -69524,7 +69510,7 @@
         </is>
       </c>
       <c r="K847" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L847" t="n">
         <v>0</v>
@@ -69576,7 +69562,7 @@
         </is>
       </c>
       <c r="K848" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L848" t="n">
         <v>0</v>
@@ -69628,7 +69614,7 @@
         </is>
       </c>
       <c r="K849" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L849" t="n">
         <v>0</v>
@@ -69680,7 +69666,7 @@
         </is>
       </c>
       <c r="K850" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L850" t="n">
         <v>0</v>
@@ -69732,7 +69718,7 @@
         </is>
       </c>
       <c r="K851" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L851" t="n">
         <v>0</v>
@@ -69784,7 +69770,7 @@
         </is>
       </c>
       <c r="K852" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L852" t="n">
         <v>0</v>
@@ -69836,7 +69822,7 @@
         </is>
       </c>
       <c r="K853" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L853" t="n">
         <v>0</v>
@@ -69888,7 +69874,7 @@
         </is>
       </c>
       <c r="K854" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L854" t="n">
         <v>0</v>
@@ -69940,7 +69926,7 @@
         </is>
       </c>
       <c r="K855" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="L855" t="n">
         <v>0</v>
@@ -69992,7 +69978,7 @@
         </is>
       </c>
       <c r="K856" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="L856" t="n">
         <v>0</v>
@@ -70044,7 +70030,7 @@
         </is>
       </c>
       <c r="K857" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="L857" t="n">
         <v>0</v>
@@ -70096,7 +70082,7 @@
         </is>
       </c>
       <c r="K858" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="L858" t="n">
         <v>0</v>
@@ -70148,7 +70134,7 @@
         </is>
       </c>
       <c r="K859" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="L859" t="n">
         <v>0</v>
@@ -70200,7 +70186,7 @@
         </is>
       </c>
       <c r="K860" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="L860" t="n">
         <v>0</v>
@@ -70252,7 +70238,7 @@
         </is>
       </c>
       <c r="K861" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="L861" t="n">
         <v>0</v>
@@ -70304,7 +70290,7 @@
         </is>
       </c>
       <c r="K862" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="L862" t="n">
         <v>0</v>
@@ -70356,7 +70342,7 @@
         </is>
       </c>
       <c r="K863" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="L863" t="n">
         <v>0</v>
@@ -70408,7 +70394,7 @@
         </is>
       </c>
       <c r="K864" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="L864" t="n">
         <v>0</v>
@@ -70460,7 +70446,7 @@
         </is>
       </c>
       <c r="K865" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="L865" t="n">
         <v>0</v>
@@ -70512,7 +70498,7 @@
         </is>
       </c>
       <c r="K866" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="L866" t="n">
         <v>0</v>
@@ -70564,7 +70550,7 @@
         </is>
       </c>
       <c r="K867" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="L867" t="n">
         <v>0</v>
@@ -70616,7 +70602,7 @@
         </is>
       </c>
       <c r="K868" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="L868" t="n">
         <v>0</v>
@@ -70668,7 +70654,7 @@
         </is>
       </c>
       <c r="K869" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L869" t="n">
         <v>0</v>
@@ -70720,7 +70706,7 @@
         </is>
       </c>
       <c r="K870" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="L870" t="n">
         <v>0</v>
@@ -70772,7 +70758,7 @@
         </is>
       </c>
       <c r="K871" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L871" t="n">
         <v>0</v>
@@ -70824,7 +70810,7 @@
         </is>
       </c>
       <c r="K872" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="L872" t="n">
         <v>0</v>
@@ -70876,7 +70862,7 @@
         </is>
       </c>
       <c r="K873" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L873" t="n">
         <v>0</v>
@@ -70928,7 +70914,7 @@
         </is>
       </c>
       <c r="K874" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L874" t="n">
         <v>0</v>
@@ -70980,7 +70966,7 @@
         </is>
       </c>
       <c r="K875" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L875" t="n">
         <v>0</v>
@@ -71032,7 +71018,7 @@
         </is>
       </c>
       <c r="K876" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L876" t="n">
         <v>0</v>
@@ -71084,7 +71070,7 @@
         </is>
       </c>
       <c r="K877" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L877" t="n">
         <v>0</v>
@@ -71136,7 +71122,7 @@
         </is>
       </c>
       <c r="K878" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L878" t="n">
         <v>0</v>
@@ -71188,7 +71174,7 @@
         </is>
       </c>
       <c r="K879" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L879" t="n">
         <v>0</v>
@@ -71240,7 +71226,7 @@
         </is>
       </c>
       <c r="K880" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L880" t="n">
         <v>0</v>
@@ -71292,7 +71278,7 @@
         </is>
       </c>
       <c r="K881" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="L881" t="n">
         <v>0</v>
@@ -71344,7 +71330,7 @@
         </is>
       </c>
       <c r="K882" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L882" t="n">
         <v>0</v>
@@ -71396,7 +71382,7 @@
         </is>
       </c>
       <c r="K883" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L883" t="n">
         <v>0</v>
@@ -71448,7 +71434,7 @@
         </is>
       </c>
       <c r="K884" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L884" t="n">
         <v>0</v>
@@ -71500,7 +71486,7 @@
         </is>
       </c>
       <c r="K885" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L885" t="n">
         <v>0</v>
@@ -71552,7 +71538,7 @@
         </is>
       </c>
       <c r="K886" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L886" t="n">
         <v>0</v>
@@ -71604,7 +71590,7 @@
         </is>
       </c>
       <c r="K887" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L887" t="n">
         <v>0</v>
@@ -71656,7 +71642,7 @@
         </is>
       </c>
       <c r="K888" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L888" t="n">
         <v>0</v>
@@ -71708,7 +71694,7 @@
         </is>
       </c>
       <c r="K889" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L889" t="n">
         <v>0</v>
@@ -71760,7 +71746,7 @@
         </is>
       </c>
       <c r="K890" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="L890" t="n">
         <v>0</v>
@@ -71812,7 +71798,7 @@
         </is>
       </c>
       <c r="K891" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L891" t="n">
         <v>0</v>
@@ -71864,7 +71850,7 @@
         </is>
       </c>
       <c r="K892" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L892" t="n">
         <v>0</v>
@@ -71916,7 +71902,7 @@
         </is>
       </c>
       <c r="K893" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L893" t="n">
         <v>0</v>
@@ -71968,7 +71954,7 @@
         </is>
       </c>
       <c r="K894" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="L894" t="n">
         <v>0</v>
@@ -72020,7 +72006,7 @@
         </is>
       </c>
       <c r="K895" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L895" t="n">
         <v>0</v>
@@ -72072,7 +72058,7 @@
         </is>
       </c>
       <c r="K896" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="L896" t="n">
         <v>0</v>
@@ -72124,7 +72110,7 @@
         </is>
       </c>
       <c r="K897" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="L897" t="n">
         <v>0</v>
@@ -72176,7 +72162,7 @@
         </is>
       </c>
       <c r="K898" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="L898" t="n">
         <v>0</v>
@@ -72228,7 +72214,7 @@
         </is>
       </c>
       <c r="K899" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L899" t="n">
         <v>0</v>
@@ -72280,7 +72266,7 @@
         </is>
       </c>
       <c r="K900" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L900" t="n">
         <v>0</v>
@@ -72332,7 +72318,7 @@
         </is>
       </c>
       <c r="K901" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L901" t="n">
         <v>0</v>
@@ -72384,7 +72370,7 @@
         </is>
       </c>
       <c r="K902" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L902" t="n">
         <v>0</v>
@@ -72436,7 +72422,7 @@
         </is>
       </c>
       <c r="K903" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L903" t="n">
         <v>0</v>
@@ -72488,7 +72474,7 @@
         </is>
       </c>
       <c r="K904" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L904" t="n">
         <v>0</v>
@@ -72540,7 +72526,7 @@
         </is>
       </c>
       <c r="K905" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L905" t="n">
         <v>0</v>
@@ -72592,7 +72578,7 @@
         </is>
       </c>
       <c r="K906" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L906" t="n">
         <v>0</v>
@@ -72644,7 +72630,7 @@
         </is>
       </c>
       <c r="K907" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L907" t="n">
         <v>0</v>
@@ -72696,7 +72682,7 @@
         </is>
       </c>
       <c r="K908" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L908" t="n">
         <v>0</v>
@@ -72748,7 +72734,7 @@
         </is>
       </c>
       <c r="K909" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L909" t="n">
         <v>0</v>
@@ -72800,7 +72786,7 @@
         </is>
       </c>
       <c r="K910" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L910" t="n">
         <v>0</v>
@@ -72852,7 +72838,7 @@
         </is>
       </c>
       <c r="K911" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L911" t="n">
         <v>0</v>
@@ -72904,7 +72890,7 @@
         </is>
       </c>
       <c r="K912" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L912" t="n">
         <v>0</v>
@@ -72956,7 +72942,7 @@
         </is>
       </c>
       <c r="K913" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L913" t="n">
         <v>0</v>
@@ -73008,7 +72994,7 @@
         </is>
       </c>
       <c r="K914" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L914" t="n">
         <v>0</v>
@@ -73060,7 +73046,7 @@
         </is>
       </c>
       <c r="K915" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L915" t="n">
         <v>0</v>
@@ -73112,7 +73098,7 @@
         </is>
       </c>
       <c r="K916" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="L916" t="n">
         <v>0</v>
@@ -73164,7 +73150,7 @@
         </is>
       </c>
       <c r="K917" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="L917" t="n">
         <v>0</v>
@@ -73216,7 +73202,7 @@
         </is>
       </c>
       <c r="K918" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L918" t="n">
         <v>0</v>
@@ -73268,7 +73254,7 @@
         </is>
       </c>
       <c r="K919" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L919" t="n">
         <v>0</v>
@@ -73320,7 +73306,7 @@
         </is>
       </c>
       <c r="K920" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="L920" t="n">
         <v>0</v>
@@ -73372,7 +73358,7 @@
         </is>
       </c>
       <c r="K921" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L921" t="n">
         <v>0</v>
@@ -73424,7 +73410,7 @@
         </is>
       </c>
       <c r="K922" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L922" t="n">
         <v>0</v>
@@ -73476,7 +73462,7 @@
         </is>
       </c>
       <c r="K923" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L923" t="n">
         <v>0</v>
@@ -73528,7 +73514,7 @@
         </is>
       </c>
       <c r="K924" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L924" t="n">
         <v>0</v>
@@ -73580,7 +73566,7 @@
         </is>
       </c>
       <c r="K925" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L925" t="n">
         <v>0</v>
@@ -73632,7 +73618,7 @@
         </is>
       </c>
       <c r="K926" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L926" t="n">
         <v>0</v>
@@ -73684,7 +73670,7 @@
         </is>
       </c>
       <c r="K927" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L927" t="n">
         <v>0</v>
@@ -73736,7 +73722,7 @@
         </is>
       </c>
       <c r="K928" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L928" t="n">
         <v>0</v>
@@ -73788,7 +73774,7 @@
         </is>
       </c>
       <c r="K929" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L929" t="n">
         <v>0</v>
@@ -73840,7 +73826,7 @@
         </is>
       </c>
       <c r="K930" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L930" t="n">
         <v>0</v>
@@ -73892,7 +73878,7 @@
         </is>
       </c>
       <c r="K931" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L931" t="n">
         <v>0</v>
@@ -73944,7 +73930,7 @@
         </is>
       </c>
       <c r="K932" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L932" t="n">
         <v>0</v>
@@ -73996,7 +73982,7 @@
         </is>
       </c>
       <c r="K933" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L933" t="n">
         <v>0</v>
@@ -74048,7 +74034,7 @@
         </is>
       </c>
       <c r="K934" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L934" t="n">
         <v>0</v>
@@ -74100,7 +74086,7 @@
         </is>
       </c>
       <c r="K935" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L935" t="n">
         <v>0</v>
@@ -74152,7 +74138,7 @@
         </is>
       </c>
       <c r="K936" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L936" t="n">
         <v>0</v>
@@ -74204,7 +74190,7 @@
         </is>
       </c>
       <c r="K937" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L937" t="n">
         <v>0</v>
@@ -74256,7 +74242,7 @@
         </is>
       </c>
       <c r="K938" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L938" t="n">
         <v>0</v>
@@ -74308,7 +74294,7 @@
         </is>
       </c>
       <c r="K939" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L939" t="n">
         <v>0</v>
@@ -74360,7 +74346,7 @@
         </is>
       </c>
       <c r="K940" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L940" t="n">
         <v>0</v>
@@ -74412,7 +74398,7 @@
         </is>
       </c>
       <c r="K941" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L941" t="n">
         <v>0</v>
@@ -74464,7 +74450,7 @@
         </is>
       </c>
       <c r="K942" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L942" t="n">
         <v>0</v>
@@ -74516,7 +74502,7 @@
         </is>
       </c>
       <c r="K943" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L943" t="n">
         <v>0</v>
@@ -74568,7 +74554,7 @@
         </is>
       </c>
       <c r="K944" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L944" t="n">
         <v>0</v>
@@ -74620,7 +74606,7 @@
         </is>
       </c>
       <c r="K945" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="L945" t="n">
         <v>0</v>
@@ -74672,7 +74658,7 @@
         </is>
       </c>
       <c r="K946" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="L946" t="n">
         <v>0</v>
@@ -74724,7 +74710,7 @@
         </is>
       </c>
       <c r="K947" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="L947" t="n">
         <v>0</v>
@@ -74776,7 +74762,7 @@
         </is>
       </c>
       <c r="K948" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L948" t="n">
         <v>0</v>
@@ -74828,7 +74814,7 @@
         </is>
       </c>
       <c r="K949" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L949" t="n">
         <v>0</v>
@@ -74880,7 +74866,7 @@
         </is>
       </c>
       <c r="K950" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L950" t="n">
         <v>0</v>
@@ -74932,7 +74918,7 @@
         </is>
       </c>
       <c r="K951" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L951" t="n">
         <v>0</v>
@@ -74984,7 +74970,7 @@
         </is>
       </c>
       <c r="K952" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="L952" t="n">
         <v>0</v>
@@ -75036,7 +75022,7 @@
         </is>
       </c>
       <c r="K953" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="L953" t="n">
         <v>0</v>
@@ -75088,7 +75074,7 @@
         </is>
       </c>
       <c r="K954" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L954" t="n">
         <v>0</v>
@@ -75140,7 +75126,7 @@
         </is>
       </c>
       <c r="K955" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="L955" t="n">
         <v>0</v>
@@ -75192,7 +75178,7 @@
         </is>
       </c>
       <c r="K956" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="L956" t="n">
         <v>0</v>
@@ -75244,7 +75230,7 @@
         </is>
       </c>
       <c r="K957" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L957" t="n">
         <v>0</v>
@@ -75296,7 +75282,7 @@
         </is>
       </c>
       <c r="K958" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L958" t="n">
         <v>0</v>
@@ -75348,7 +75334,7 @@
         </is>
       </c>
       <c r="K959" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L959" t="n">
         <v>0</v>
@@ -75400,7 +75386,7 @@
         </is>
       </c>
       <c r="K960" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="L960" t="n">
         <v>0</v>
@@ -75452,7 +75438,7 @@
         </is>
       </c>
       <c r="K961" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="L961" t="n">
         <v>0</v>
@@ -75504,7 +75490,7 @@
         </is>
       </c>
       <c r="K962" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L962" t="n">
         <v>0</v>
@@ -75556,7 +75542,7 @@
         </is>
       </c>
       <c r="K963" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L963" t="n">
         <v>0</v>
@@ -75608,7 +75594,7 @@
         </is>
       </c>
       <c r="K964" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="L964" t="n">
         <v>0</v>
@@ -75660,7 +75646,7 @@
         </is>
       </c>
       <c r="K965" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L965" t="n">
         <v>0</v>
@@ -75712,7 +75698,7 @@
         </is>
       </c>
       <c r="K966" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L966" t="n">
         <v>0</v>
@@ -75764,7 +75750,7 @@
         </is>
       </c>
       <c r="K967" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L967" t="n">
         <v>0</v>
@@ -75816,7 +75802,7 @@
         </is>
       </c>
       <c r="K968" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L968" t="n">
         <v>0</v>
@@ -75868,7 +75854,7 @@
         </is>
       </c>
       <c r="K969" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L969" t="n">
         <v>0</v>
@@ -75920,7 +75906,7 @@
         </is>
       </c>
       <c r="K970" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L970" t="n">
         <v>0</v>
@@ -75972,7 +75958,7 @@
         </is>
       </c>
       <c r="K971" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L971" t="n">
         <v>0</v>
@@ -76024,7 +76010,7 @@
         </is>
       </c>
       <c r="K972" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L972" t="n">
         <v>0</v>
@@ -76076,7 +76062,7 @@
         </is>
       </c>
       <c r="K973" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="L973" t="n">
         <v>0</v>
@@ -76128,7 +76114,7 @@
         </is>
       </c>
       <c r="K974" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L974" t="n">
         <v>0</v>
@@ -76180,7 +76166,7 @@
         </is>
       </c>
       <c r="K975" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L975" t="n">
         <v>0</v>
@@ -76232,7 +76218,7 @@
         </is>
       </c>
       <c r="K976" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L976" t="n">
         <v>0</v>
@@ -76284,7 +76270,7 @@
         </is>
       </c>
       <c r="K977" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L977" t="n">
         <v>0</v>
@@ -76336,7 +76322,7 @@
         </is>
       </c>
       <c r="K978" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="L978" t="n">
         <v>0</v>
@@ -76388,7 +76374,7 @@
         </is>
       </c>
       <c r="K979" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L979" t="n">
         <v>0</v>
@@ -76440,7 +76426,7 @@
         </is>
       </c>
       <c r="K980" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L980" t="n">
         <v>0</v>
@@ -76492,7 +76478,7 @@
         </is>
       </c>
       <c r="K981" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="L981" t="n">
         <v>0</v>
@@ -76544,7 +76530,7 @@
         </is>
       </c>
       <c r="K982" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L982" t="n">
         <v>0</v>
@@ -76596,7 +76582,7 @@
         </is>
       </c>
       <c r="K983" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L983" t="n">
         <v>0</v>
@@ -76648,7 +76634,7 @@
         </is>
       </c>
       <c r="K984" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L984" t="n">
         <v>0</v>
@@ -76700,7 +76686,7 @@
         </is>
       </c>
       <c r="K985" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L985" t="n">
         <v>0</v>
@@ -76752,7 +76738,7 @@
         </is>
       </c>
       <c r="K986" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="L986" t="n">
         <v>0</v>
@@ -76804,7 +76790,7 @@
         </is>
       </c>
       <c r="K987" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="L987" t="n">
         <v>0</v>
@@ -76856,7 +76842,7 @@
         </is>
       </c>
       <c r="K988" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="L988" t="n">
         <v>0</v>
@@ -76908,7 +76894,7 @@
         </is>
       </c>
       <c r="K989" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="L989" t="n">
         <v>0</v>
@@ -76960,7 +76946,7 @@
         </is>
       </c>
       <c r="K990" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="L990" t="n">
         <v>0</v>
@@ -77012,7 +76998,7 @@
         </is>
       </c>
       <c r="K991" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L991" t="n">
         <v>0</v>
@@ -77064,7 +77050,7 @@
         </is>
       </c>
       <c r="K992" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L992" t="n">
         <v>0</v>
@@ -77116,7 +77102,7 @@
         </is>
       </c>
       <c r="K993" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L993" t="n">
         <v>0</v>
@@ -77168,7 +77154,7 @@
         </is>
       </c>
       <c r="K994" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L994" t="n">
         <v>0</v>
@@ -77220,7 +77206,7 @@
         </is>
       </c>
       <c r="K995" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L995" t="n">
         <v>0</v>
@@ -77272,7 +77258,7 @@
         </is>
       </c>
       <c r="K996" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="L996" t="n">
         <v>0</v>
@@ -77324,7 +77310,7 @@
         </is>
       </c>
       <c r="K997" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="L997" t="n">
         <v>0</v>
@@ -77376,7 +77362,7 @@
         </is>
       </c>
       <c r="K998" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="L998" t="n">
         <v>0</v>
@@ -77428,7 +77414,7 @@
         </is>
       </c>
       <c r="K999" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="L999" t="n">
         <v>0</v>
@@ -77480,7 +77466,7 @@
         </is>
       </c>
       <c r="K1000" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L1000" t="n">
         <v>0</v>
@@ -77532,7 +77518,7 @@
         </is>
       </c>
       <c r="K1001" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L1001" t="n">
         <v>0</v>
